--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,13 +397,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:H65"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
-    <col min="2" max="2" width="45.83203125" customWidth="1"/>
-    <col min="3" max="3" width="120.83203125" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="5" max="5" width="18.83203125" customWidth="1"/>
+    <col min="2" max="2" width="8.83203125" customWidth="1"/>
+    <col min="3" max="3" width="45.83203125" customWidth="1"/>
+    <col min="4" max="4" width="120.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
+    <col min="6" max="6" width="16.83203125" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" customWidth="1"/>
+    <col min="8" max="8" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -411,32 +414,41 @@
         <v>Date</v>
       </c>
       <c r="B1" t="str">
+        <v>Time</v>
+      </c>
+      <c r="C1" t="str">
         <v>Screen / File</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>Change Description</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>Type</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>Category</v>
+      </c>
+      <c r="G1" t="str">
         <v>Agent</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Status</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
         <v>2026-04-27</v>
       </c>
-      <c r="B2" t="str">
+      <c r="C2" t="str">
         <v>src/index.css</v>
       </c>
-      <c r="C2" t="str">
+      <c r="D2" t="str">
         <v>Complete CSS overhaul: gradient .btn-primary, card default box-shadow, page fade-in animation on screen mount, drag-handle-aware .bottom-nav with gradient active pill, new keyframes (pageFadeIn, shimmer, celebrate, confettiBurst, staggerIn, float), .skeleton shimmer loading class, .score-bar-track/.score-bar-fill for contact score bars, .tier-card and .message-preview for greeting editor, stagger-1–5 entrance delay classes, desktop background gradient, backdrop blur for modals</v>
       </c>
-      <c r="D2" t="str">
-        <v>improvement</v>
-      </c>
       <c r="E2" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="G2" t="str">
         <v>Main</v>
       </c>
     </row>
@@ -444,16 +456,16 @@
       <c r="A3" t="str">
         <v>2026-04-27</v>
       </c>
-      <c r="B3" t="str">
+      <c r="C3" t="str">
         <v>src/data/themes.ts</v>
       </c>
-      <c r="C3" t="str">
+      <c r="D3" t="str">
         <v>Made all 6 themes more vibrant: ocean secondary #06B6D4, forest secondary #4ADE80, sunset primary #F97316 + secondary #FBBF24, purple primary #8B5CF6 + secondary #C084FC, rose primary #F43F5E + secondary #FB7185, midnight primary #818CF8 + secondary #A5B4FC + darker background #080818. Stronger shadow opacities (0.16–0.22).</v>
       </c>
-      <c r="D3" t="str">
-        <v>improvement</v>
-      </c>
       <c r="E3" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="G3" t="str">
         <v>Main</v>
       </c>
     </row>
@@ -461,16 +473,16 @@
       <c r="A4" t="str">
         <v>2026-04-27</v>
       </c>
-      <c r="B4" t="str">
+      <c r="C4" t="str">
         <v>src/components/ContactCard.tsx</v>
       </c>
-      <c r="C4" t="str">
+      <c r="D4" t="str">
         <v>Replaced solid avatar background with 10-option gradient palette (name-hashed). Added urgency-tinted card background glow. Added horizontal score progress bar (.score-bar-track/.score-bar-fill) below contact info. Added staggerIndex prop for staggered list entrance animations. Urgency badge now uses colored pill instead of Badge component.</v>
       </c>
-      <c r="D4" t="str">
-        <v>improvement</v>
-      </c>
       <c r="E4" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="G4" t="str">
         <v>Main</v>
       </c>
     </row>
@@ -478,16 +490,16 @@
       <c r="A5" t="str">
         <v>2026-04-27</v>
       </c>
-      <c r="B5" t="str">
+      <c r="C5" t="str">
         <v>src/components/HolidayCard.tsx</v>
       </c>
-      <c r="C5" t="str">
+      <c r="D5" t="str">
         <v>Compact view: gradient-tinted background + left color border using holiday.color. Badge turns solid holiday-color on "Today". Full view: gradient color header strip with white text, emoji gets animate-float class, body text moved below header. Added hexToRgb helper for rgba tinting. Added staggerIndex prop.</v>
       </c>
-      <c r="D5" t="str">
-        <v>improvement</v>
-      </c>
       <c r="E5" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="G5" t="str">
         <v>Main</v>
       </c>
     </row>
@@ -495,16 +507,16 @@
       <c r="A6" t="str">
         <v>2026-04-27</v>
       </c>
-      <c r="B6" t="str">
+      <c r="C6" t="str">
         <v>src/components/Navigation.tsx</v>
       </c>
-      <c r="C6" t="str">
+      <c r="D6" t="str">
         <v>BottomNav: active item gets gradient mini-pill background div + drop-shadow on icon, uses useTheme() for gradient colors, active label gets font-bold. PageHeader: font upgraded to font-extrabold tracking-tight. Back button has active:scale-90 press effect.</v>
       </c>
-      <c r="D6" t="str">
-        <v>improvement</v>
-      </c>
       <c r="E6" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="G6" t="str">
         <v>Main</v>
       </c>
     </row>
@@ -512,16 +524,16 @@
       <c r="A7" t="str">
         <v>2026-04-27</v>
       </c>
-      <c r="B7" t="str">
+      <c r="C7" t="str">
         <v>src/screens/DashboardScreen.tsx</v>
       </c>
-      <c r="C7" t="str">
+      <c r="D7" t="str">
         <v>Added "Today's Highlights" section showing today's holiday and birthday cards with color-tinted gradient backgrounds. Enhanced welcome hero with decorative circles and font-extrabold heading. Gradient FAB button with theme colors. Stats cards now have gradient icon circles. Tomorrow holiday preview card at bottom. All contact/holiday lists receive staggerIndex for entrance animations.</v>
       </c>
-      <c r="D7" t="str">
+      <c r="E7" t="str">
         <v>feature</v>
       </c>
-      <c r="E7" t="str">
+      <c r="G7" t="str">
         <v>Main</v>
       </c>
     </row>
@@ -529,16 +541,16 @@
       <c r="A8" t="str">
         <v>2026-04-27</v>
       </c>
-      <c r="B8" t="str">
+      <c r="C8" t="str">
         <v>src/screens/GreetingEditorScreen.tsx</v>
       </c>
-      <c r="C8" t="str">
+      <c r="D8" t="str">
         <v>Full screen redesign. Added 3-tier visual selector (Casual 😊 / Professional 💼 / VIP 👑) as side-by-side .tier-card buttons with tier-color borders and glow. Added live message preview in chat-bubble style (.message-preview) with RTL support for Hebrew. Added character count display (color changes at 75%/90% of 500). Added signature line toggle (pen icon) with input and preview text. Added collapsible advanced tone/dropdown. Celebration confetti on copy. Editor header shows active tier emoji and contact first name.</v>
       </c>
-      <c r="D8" t="str">
+      <c r="E8" t="str">
         <v>feature</v>
       </c>
-      <c r="E8" t="str">
+      <c r="G8" t="str">
         <v>Main</v>
       </c>
     </row>
@@ -546,16 +558,16 @@
       <c r="A9" t="str">
         <v>2026-04-27</v>
       </c>
-      <c r="B9" t="str">
+      <c r="C9" t="str">
         <v>src/services/greetingService.ts</v>
       </c>
-      <c r="C9" t="str">
+      <c r="D9" t="str">
         <v>Enriched all tone templates with emoji. Hebrew templates rewritten for authentic Israeli casual voice (not translated English). VIP templates now premium-letter quality with 🌹. Friendly Hebrew: expressions like "עלית לי בראש", "סתם חשבתי עליך". Birthday greetings expanded with emoji for all languages including French and Spanish.</v>
       </c>
-      <c r="D9" t="str">
-        <v>improvement</v>
-      </c>
       <c r="E9" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="G9" t="str">
         <v>Main</v>
       </c>
     </row>
@@ -563,16 +575,16 @@
       <c r="A10" t="str">
         <v>2026-04-27</v>
       </c>
-      <c r="B10" t="str">
+      <c r="C10" t="str">
         <v>src/components/ui/Modal.tsx</v>
       </c>
-      <c r="C10" t="str">
+      <c r="D10" t="str">
         <v>Added visible drag handle bar at top (mobile UX best practice). Backdrop now uses blur(6px) + rgba(0,0,0,0.55). Added danger prop for red title text. Added aria-labelledby for accessibility. Fixed missing shadow class (was shadow-theme-xl which doesn't exist). Backdrop click still closes. ESC key support retained.</v>
       </c>
-      <c r="D10" t="str">
-        <v>improvement</v>
-      </c>
       <c r="E10" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="G10" t="str">
         <v>Main</v>
       </c>
     </row>
@@ -580,16 +592,16 @@
       <c r="A11" t="str">
         <v>2026-04-27</v>
       </c>
-      <c r="B11" t="str">
+      <c r="C11" t="str">
         <v>src/components/WhatsAppButton.tsx</v>
       </c>
-      <c r="C11" t="str">
+      <c r="D11" t="str">
         <v>Bug fix: was using hardcoded English strings instead of i18n t() keys (whatsapp_btn, whatsapp_title, whatsapp_warning, whatsapp_notice, whatsapp_preview, whatsapp_open). Replaced Button component with native button using authentic WhatsApp green gradient (#25D366→#128C7E) with green glow shadow. Modal preview improved with amber-tinted warning box.</v>
       </c>
-      <c r="D11" t="str">
+      <c r="E11" t="str">
         <v>bugfix</v>
       </c>
-      <c r="E11" t="str">
+      <c r="G11" t="str">
         <v>Main</v>
       </c>
     </row>
@@ -597,16 +609,16 @@
       <c r="A12" t="str">
         <v>2026-04-27</v>
       </c>
-      <c r="B12" t="str">
+      <c r="C12" t="str">
         <v>src/screens/ContactFormScreen.tsx</v>
       </c>
-      <c r="C12" t="str">
+      <c r="D12" t="str">
         <v>Avatar section redesigned: live gradient preview circle updates as name is typed (name-hashed gradient). Added "auto gradient" option (✦ button) alongside solid color swatches. Section headers now have colored gradient icon squares (User/Globe/BarChart2/Crown icons). Premium section gets amber left border. Save bar uses gradient fade instead of solid background. Added autoFocus on name field for new contacts. Modal uses new danger prop.</v>
       </c>
-      <c r="D12" t="str">
-        <v>improvement</v>
-      </c>
       <c r="E12" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="G12" t="str">
         <v>Main</v>
       </c>
     </row>
@@ -614,16 +626,16 @@
       <c r="A13" t="str">
         <v>2026-04-27</v>
       </c>
-      <c r="B13" t="str">
+      <c r="C13" t="str">
         <v>src/screens/WhatsNewScreen.tsx</v>
       </c>
-      <c r="C13" t="str">
+      <c r="D13" t="str">
         <v>Redesigned as vertical timeline with animated gradient connector line. Version dots styled as gradient circles (latest = primary gradient, older = muted). Hero banner at top with latest version and animate-float emoji. Change type badges now use gradient backgrounds (feature=blue-purple, improvement=green, bugfix=orange, security=purple). "Latest" pill uses theme gradient.</v>
       </c>
-      <c r="D13" t="str">
-        <v>improvement</v>
-      </c>
       <c r="E13" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="G13" t="str">
         <v>Main</v>
       </c>
     </row>
@@ -631,16 +643,16 @@
       <c r="A14" t="str">
         <v>2026-04-27</v>
       </c>
-      <c r="B14" t="str">
+      <c r="C14" t="str">
         <v>src/screens/AboutScreen.tsx</v>
       </c>
-      <c r="C14" t="str">
+      <c r="D14" t="str">
         <v>Hero section replaced with full gradient banner (primary→secondary) with floating 💌 emoji. Core values section: each value now has a gradient icon circle (Shield=purple, Globe=teal, Heart=rose, Zap=amber). Technical details table replaced with icon+pill layout for each privacy fact. Important notice uses amber-tinted box.</v>
       </c>
-      <c r="D14" t="str">
-        <v>improvement</v>
-      </c>
       <c r="E14" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="G14" t="str">
         <v>Main</v>
       </c>
     </row>
@@ -648,16 +660,16 @@
       <c r="A15" t="str">
         <v>2026-04-27</v>
       </c>
-      <c r="B15" t="str">
+      <c r="C15" t="str">
         <v>src/components/EmptyState.tsx</v>
       </c>
-      <c r="C15" t="str">
+      <c r="D15" t="str">
         <v>Icon container upgraded to large gradient circle (theme.primary→theme.secondary at 33–55% alpha) using useTheme(). Added animate-float on the icon. Title font upgraded from font-semibold to font-bold text-lg.</v>
       </c>
-      <c r="D15" t="str">
-        <v>improvement</v>
-      </c>
       <c r="E15" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="G15" t="str">
         <v>UI Agent</v>
       </c>
     </row>
@@ -665,16 +677,16 @@
       <c r="A16" t="str">
         <v>2026-04-27</v>
       </c>
-      <c r="B16" t="str">
+      <c r="C16" t="str">
         <v>src/components/ui/Badge.tsx</v>
       </c>
-      <c r="C16" t="str">
+      <c r="D16" t="str">
         <v>All badge variants now have gradient backgrounds via inline style. premium=gold gradient (#F59E0B→#F97316), success=green gradient, warning=amber gradient, danger=red gradient, info=blue gradient, neutral=surface gradient. All existing props/variants preserved.</v>
       </c>
-      <c r="D16" t="str">
-        <v>improvement</v>
-      </c>
       <c r="E16" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="G16" t="str">
         <v>UI Agent</v>
       </c>
     </row>
@@ -682,16 +694,16 @@
       <c r="A17" t="str">
         <v>2026-04-27</v>
       </c>
-      <c r="B17" t="str">
+      <c r="C17" t="str">
         <v>src/screens/OnboardingScreen.tsx</v>
       </c>
-      <c r="C17" t="str">
+      <c r="D17" t="str">
         <v>Slide icon area replaced with large w-32 h-32 gradient circle (per-slide colors, animate-float). Title and description get animate-slide-up stagger-2/3 classes. Progress dots: active dot uses theme gradient background, wider pill shape, scaleY animation. Next/Get Started button uses inline gradient matching theme.</v>
       </c>
-      <c r="D17" t="str">
-        <v>improvement</v>
-      </c>
       <c r="E17" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="G17" t="str">
         <v>UI Agent</v>
       </c>
     </row>
@@ -699,16 +711,16 @@
       <c r="A18" t="str">
         <v>2026-04-27</v>
       </c>
-      <c r="B18" t="str">
+      <c r="C18" t="str">
         <v>src/screens/ContactsScreen.tsx</v>
       </c>
-      <c r="C18" t="str">
+      <c r="D18" t="str">
         <v>Search bar gets shadow-md ring elevation. Filter chips (All/External/Internal/VIP) use theme gradient when active with shadow-sm. ContactCard receives staggerIndex={i % 5} for entrance animations. FAB uses theme gradient + hover:scale-105 / active:scale-95. Add button in header uses gradient when contacts can be added.</v>
       </c>
-      <c r="D18" t="str">
-        <v>improvement</v>
-      </c>
       <c r="E18" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="G18" t="str">
         <v>UI Agent</v>
       </c>
     </row>
@@ -716,16 +728,16 @@
       <c r="A19" t="str">
         <v>2026-04-27</v>
       </c>
-      <c r="B19" t="str">
+      <c r="C19" t="str">
         <v>src/screens/ContactDetailScreen.tsx</v>
       </c>
-      <c r="C19" t="str">
+      <c r="D19" t="str">
         <v>Profile area replaced with full-width gradient banner (theme.primary→theme.secondary). Avatar upgraded to w-20 h-20 gradient circle with ring-4 ring-white/20. Relationship score shows SVG ring arc (circumference trick) in urgency color with score number centered. Contact info rows get divide-y separation with icon badge backgrounds. Greeting action button uses native gradient button.</v>
       </c>
-      <c r="D19" t="str">
-        <v>improvement</v>
-      </c>
       <c r="E19" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="G19" t="str">
         <v>UI Agent</v>
       </c>
     </row>
@@ -733,16 +745,16 @@
       <c r="A20" t="str">
         <v>2026-04-27</v>
       </c>
-      <c r="B20" t="str">
+      <c r="C20" t="str">
         <v>src/screens/CalendarScreen.tsx</v>
       </c>
-      <c r="C20" t="str">
+      <c r="D20" t="str">
         <v>Month name shown in gradient-tinted pill. Active/today day cells use theme gradient background. Religion filter chips use religion-specific colors when active (not generic primary). "All" chip uses theme gradient when active.</v>
       </c>
-      <c r="D20" t="str">
-        <v>improvement</v>
-      </c>
       <c r="E20" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="G20" t="str">
         <v>UI Agent</v>
       </c>
     </row>
@@ -750,16 +762,16 @@
       <c r="A21" t="str">
         <v>2026-04-27</v>
       </c>
-      <c r="B21" t="str">
+      <c r="C21" t="str">
         <v>src/screens/GroupsScreen.tsx</v>
       </c>
-      <c r="C21" t="str">
+      <c r="D21" t="str">
         <v>Group cards: left border in group.color + gradient background tint using group.color. Emoji circle upgraded to w-12 h-12 with gradient. Contact/holiday counts shown as colored pill badges using group.color. Header "New" button uses theme gradient.</v>
       </c>
-      <c r="D21" t="str">
-        <v>improvement</v>
-      </c>
       <c r="E21" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="G21" t="str">
         <v>UI Agent</v>
       </c>
     </row>
@@ -767,16 +779,16 @@
       <c r="A22" t="str">
         <v>2026-04-27</v>
       </c>
-      <c r="B22" t="str">
+      <c r="C22" t="str">
         <v>src/screens/SettingsScreen.tsx</v>
       </c>
-      <c r="C22" t="str">
+      <c r="D22" t="str">
         <v>Section headers: gradient icon squares with lucide icons. Language toggle: sliding pill indicator animates between EN/HE with gradient active state. Theme picker: swatches enlarged to h-14, active theme gets checkmark overlay + glow ring shadow. Premium section: gold/amber gradient banner when active. Danger zone: red-tinted background.</v>
       </c>
-      <c r="D22" t="str">
-        <v>improvement</v>
-      </c>
       <c r="E22" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="G22" t="str">
         <v>UI Agent</v>
       </c>
     </row>
@@ -784,16 +796,16 @@
       <c r="A23" t="str">
         <v>2026-04-27</v>
       </c>
-      <c r="B23" t="str">
+      <c r="C23" t="str">
         <v>src/services/greetingService.ts</v>
       </c>
-      <c r="C23" t="str">
+      <c r="D23" t="str">
         <v>Expanded all tone/language templates to 4–7 variants each. Added HOLIDAY_SPECIFIC_BODIES lookup table with custom templates for: rosh-hashana, yom-kippur, hanukkah, passover, eid-al-fitr, eid-al-adha, christmas — each with friendly/business/formal/vip and hebrew/arabic/english variants. buildHolidayBody() now checks specific overrides first before falling back to generic logic. Added holidayBaseKey() helper to strip year suffix from holiday IDs.</v>
       </c>
-      <c r="D23" t="str">
-        <v>improvement</v>
-      </c>
       <c r="E23" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="G23" t="str">
         <v>Greeting Agent</v>
       </c>
     </row>
@@ -801,16 +813,16 @@
       <c r="A24" t="str">
         <v>2026-04-27</v>
       </c>
-      <c r="B24" t="str">
+      <c r="C24" t="str">
         <v>src/services/greetingService.ts (type fix)</v>
       </c>
-      <c r="C24" t="str">
+      <c r="D24" t="str">
         <v>Fixed TypeScript syntax error introduced by Greeting Agent: extra trailing &gt; in HOLIDAY_SPECIFIC_BODIES type annotation (Partial&lt;Record&lt;...&gt;&gt;&gt;&gt;&gt;&gt; &gt; should be &gt;&gt;&gt;&gt;&gt;&gt;). Caused 80+ cascading TS1005/TS1109 errors.</v>
       </c>
-      <c r="D24" t="str">
+      <c r="E24" t="str">
         <v>bugfix</v>
       </c>
-      <c r="E24" t="str">
+      <c r="G24" t="str">
         <v>Main</v>
       </c>
     </row>
@@ -818,16 +830,16 @@
       <c r="A25" t="str">
         <v>2026-04-27</v>
       </c>
-      <c r="B25" t="str">
+      <c r="C25" t="str">
         <v>scripts/make-changelog.js</v>
       </c>
-      <c r="C25" t="str">
+      <c r="D25" t="str">
         <v>Fixed ES module incompatibility: converted require() calls to import statements and added __dirname shim via fileURLToPath(import.meta.url). Package.json has "type":"module" which broke CommonJS require syntax.</v>
       </c>
-      <c r="D25" t="str">
+      <c r="E25" t="str">
         <v>bugfix</v>
       </c>
-      <c r="E25" t="str">
+      <c r="G25" t="str">
         <v>Main</v>
       </c>
     </row>
@@ -835,16 +847,16 @@
       <c r="A26" t="str">
         <v>2026-04-27</v>
       </c>
-      <c r="B26" t="str">
+      <c r="C26" t="str">
         <v>src/screens/HolidayDetailScreen.tsx</v>
       </c>
-      <c r="C26" t="str">
+      <c r="D26" t="str">
         <v>Full redesign. Hero: full-width gradient banner using holiday.color with animate-float emoji, white text pills for date/religion/major. Cards get holiday-colored icon headers (BookOpen, MessageCircle, Lightbulb, AlertTriangle, Users). GreetingRow: tinted lang label in holiday.color instead of plain muted. Do/Don't: green-tinted / red-tinted card backgrounds with borders. Sensitivity: amber left-border card. Related contacts: gradient avatar circles with holiday-tinted row backgrounds. Action button: full gradient in holiday.color with matching glow shadow. Added hexToRgb helper.</v>
       </c>
-      <c r="D26" t="str">
-        <v>improvement</v>
-      </c>
       <c r="E26" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="G26" t="str">
         <v>Main</v>
       </c>
     </row>
@@ -852,16 +864,16 @@
       <c r="A27" t="str">
         <v>2026-04-27</v>
       </c>
-      <c r="B27" t="str">
+      <c r="C27" t="str">
         <v>src/screens/PrivacyScreen.tsx</v>
       </c>
-      <c r="C27" t="str">
+      <c r="D27" t="str">
         <v>Complete redesign. Added gradient hero banner (theme.primary→secondary) with animate-float 🔒 emoji and privacy tagline pill. Each of the 10 sections now has a unique icon (Lock, Shield, BarChart2, Eye, MessageCircle, FileUp, WifiOff, Smartphone, RefreshCw, Mail) with a color-tinted rounded square badge. Replaced plain Card component with icon+text layout. Added footer note.</v>
       </c>
-      <c r="D27" t="str">
-        <v>improvement</v>
-      </c>
       <c r="E27" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="G27" t="str">
         <v>Main</v>
       </c>
     </row>
@@ -869,22 +881,984 @@
       <c r="A28" t="str">
         <v>2026-04-27</v>
       </c>
-      <c r="B28" t="str">
+      <c r="C28" t="str">
         <v>src/screens/TermsScreen.tsx</v>
       </c>
-      <c r="C28" t="str">
+      <c r="D28" t="str">
         <v>Complete redesign matching PrivacyScreen style. Added gradient hero with animate-float 📋 emoji. Each of the 10 sections has a unique icon (FileText, CheckCircle, AlertTriangle, MessageCircle, Calendar, CreditCard, HardDrive, Scale, Gavel, RefreshCw) with color-tinted badge. Section titles now font-extrabold.</v>
       </c>
-      <c r="D28" t="str">
-        <v>improvement</v>
-      </c>
       <c r="E28" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="G28" t="str">
         <v>Main</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B29" t="str">
+        <v>00:00</v>
+      </c>
+      <c r="C29" t="str">
+        <v>src/context/AppContext.tsx</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Wrap AppContext provider value in useMemo to prevent whole-tree re-renders on every state change; simplify inline limits object literal</v>
+      </c>
+      <c r="E29" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F29" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G29" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H29" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B30" t="str">
+        <v>09:15</v>
+      </c>
+      <c r="C30" t="str">
+        <v>src/context/AppContext.tsx</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Code review iteration 2: AppContext useMemo fix verified, dependency array completeness checked, stale closure risk assessed</v>
+      </c>
+      <c r="E30" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F30" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G30" t="str">
+        <v>Agent 3</v>
+      </c>
+      <c r="H30" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B31" t="str">
+        <v>10:00</v>
+      </c>
+      <c r="C31" t="str">
+        <v>src/utils/avatarUtils.ts</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Extract getInitials+getAvatarGradient into shared avatarUtils.ts with Map cache; fix visual bug where same contact showed different avatar color on Dashboard (8 gradients) vs Contacts list (10 gradients)</v>
+      </c>
+      <c r="E31" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F31" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G31" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H31" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B32" t="str">
+        <v>10:15</v>
+      </c>
+      <c r="C32" t="str">
+        <v>src/utils/avatarUtils.ts</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Code review iteration 3: avatarUtils extraction verified correct, cache implementation checked, import paths verified across 7 files</v>
+      </c>
+      <c r="E32" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F32" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G32" t="str">
+        <v>Agent 3</v>
+      </c>
+      <c r="H32" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B33" t="str">
+        <v>09:15</v>
+      </c>
+      <c r="C33" t="str">
+        <v>src/context/AppContext.tsx</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Replace dashboardData useState+useCallback+useEffect triple with single useMemo; hoist LIMITS to module scope; eliminates double-render cycle on every contact mutation</v>
+      </c>
+      <c r="E33" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F33" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G33" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H33" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B34" t="str">
+        <v>09:45</v>
+      </c>
+      <c r="C34" t="str">
+        <v>src/context/AppContext.tsx</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Code review iteration 4: double-render fix verified, useMemo dep array checked, refreshDashboard no-op stub safety confirmed</v>
+      </c>
+      <c r="E34" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F34" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G34" t="str">
+        <v>Agent 3</v>
+      </c>
+      <c r="H34" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B35" t="str">
+        <v>00:00</v>
+      </c>
+      <c r="C35" t="str">
+        <v>src/services/storageService.ts</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Wrap all JSON.parse(localStorage.getItem()) calls in try/catch with console.warn fallback to prevent app crash on corrupted storage</v>
+      </c>
+      <c r="E35" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F35" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G35" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H35" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B36" t="str">
+        <v>10:00</v>
+      </c>
+      <c r="C36" t="str">
+        <v>src/services/storageService.ts</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Code review iteration 1: storageService fix verified correct, all callers handle null safely. Identified AppContext inline value object causing whole-tree re-renders on every state change.</v>
+      </c>
+      <c r="E36" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F36" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G36" t="str">
+        <v>Agent 3</v>
+      </c>
+      <c r="H36" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B37" t="str">
+        <v>00:00</v>
+      </c>
+      <c r="C37" t="str">
+        <v>src/components/HolidayCard.tsx</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Add useT() i18n to HolidayCard: replace hardcoded Today/Tomorrow/Passed/days strings with t() keys — Hebrew users now see localized badge labels</v>
+      </c>
+      <c r="E37" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F37" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G37" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H37" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B38" t="str">
+        <v>HH:MM</v>
+      </c>
+      <c r="C38" t="str">
+        <v>src/components/HolidayCard.tsx</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Code review iteration 5: HolidayCard i18n fix verified, all 6 strings replaced, both EN/HE keys confirmed present, RTL layout checked</v>
+      </c>
+      <c r="E38" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F38" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G38" t="str">
+        <v>Agent 3</v>
+      </c>
+      <c r="H38" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B39" t="str">
+        <v>00:00</v>
+      </c>
+      <c r="C39" t="str">
+        <v>build</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Agent 5 build check iteration 5: fixed 17 lint errors across 9 files — removed unused imports (Gift/DashboardScreen, Card/GroupsScreen, Button/OnboardingScreen, Button/BirthdayCenterScreen, Button+navigate/BirthdayGreetingEditorScreen, Select/ImportContactsScreen), moved Math.random() from render to useState initializer in ContactFormScreen, moved Date.now() from render to useState initializer in ContactDetailScreen, added eslint-disable comments for react-refresh/only-export-components in LanguageContext+ThemeContext, and suppressed react-hooks/set-state-in-effect for intentional sync effects in GreetingEditorScreen+BirthdayGreetingEditorScreen</v>
+      </c>
+      <c r="E39" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F39" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G39" t="str">
+        <v>Agent 5</v>
+      </c>
+      <c r="H39" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B40" t="str">
+        <v>10:00</v>
+      </c>
+      <c r="C40" t="str">
+        <v>9 files (DashboardScreen, ContactDetailScreen, ContactFormScreen, GreetingEditorScreen, GroupsScreen, OnboardingScreen, BirthdayCenterScreen, BirthdayGreetingEditorScreen, ImportContactsScreen)</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Agent 5 lint sweep: fixed 17 lint errors across 9 files — removed unused imports (Gift, Card, Button, Select, navigate), moved Date.now()/Math.random() out of render into useState initializers, added eslint-disable for intentional hook patterns (react-refresh/only-export-components, setState-in-effect)</v>
+      </c>
+      <c r="E40" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F40" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G40" t="str">
+        <v>Agent 5</v>
+      </c>
+      <c r="H40" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B41" t="str">
+        <v>00:00</v>
+      </c>
+      <c r="C41" t="str">
+        <v>build</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Agent 5 build+lint check iteration 6: clean — no errors or warnings, no stale deps, no missing cleanups, no `as any` casts found in ContactDetailScreen, ContactFormScreen, or AppContext</v>
+      </c>
+      <c r="E41" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F41" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G41" t="str">
+        <v>Agent 5</v>
+      </c>
+      <c r="H41" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B42" t="str">
+        <v>HH:MM</v>
+      </c>
+      <c r="C42" t="str">
+        <v>src/screens/GreetingEditorScreen.tsx</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Fix i18n: remove labelHe manual hack from TIERS, replace 7 hardcoded English strings with t() keys, add missing greeting_tier/greeting_advanced_tone/greeting_add_signature keys to i18n/index.ts</v>
+      </c>
+      <c r="E42" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F42" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G42" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H42" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B43" t="str">
+        <v>HH:MM</v>
+      </c>
+      <c r="C43" t="str">
+        <v>src/components/MediaAttachmentPicker.tsx + 2 files</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Fix 4 review findings: correct mic error message, add 2MB image size guard, clear mediaAttachment on regenerate, document coupon security limitation</v>
+      </c>
+      <c r="E43" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F43" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G43" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H43" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B44" t="str">
+        <v>HH:MM</v>
+      </c>
+      <c r="C44" t="str">
+        <v>src/screens/GreetingEditorScreen.tsx</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Code review iteration 6: i18n fix verified, all 11 keys present in both locales, labelKey type-safe, Hebrew translations semantically reviewed</v>
+      </c>
+      <c r="E44" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F44" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G44" t="str">
+        <v>Agent 3</v>
+      </c>
+      <c r="H44" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B45" t="str">
+        <v>HH:MM</v>
+      </c>
+      <c r="C45" t="str">
+        <v>src/components/MediaAttachmentPicker.tsx</v>
+      </c>
+      <c r="D45" t="str">
+        <v>New premium component: image upload via FileReader + voice recording via MediaRecorder (60s), base64 preview, premium lock state</v>
+      </c>
+      <c r="E45" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F45" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G45" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H45" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B46" t="str">
+        <v>HH:MM</v>
+      </c>
+      <c r="C46" t="str">
+        <v>src/screens/GreetingEditorScreen.tsx</v>
+      </c>
+      <c r="D46" t="str">
+        <v>Integrate MediaAttachmentPicker — attach image or voice recording to any greeting (Premium)</v>
+      </c>
+      <c r="E46" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F46" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G46" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H46" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B47" t="str">
+        <v>HH:MM</v>
+      </c>
+      <c r="C47" t="str">
+        <v>src/components/WhatsAppButton.tsx</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Show media attachment preview in WhatsApp modal with save-to-device download link and attach-manually hint</v>
+      </c>
+      <c r="E47" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F47" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G47" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H47" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B48" t="str">
+        <v>HH:MM</v>
+      </c>
+      <c r="C48" t="str">
+        <v>src/screens/UpgradeScreen.tsx</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Add coupon code section: collapsible input with success/error states. Valid codes: NEVERMISS1/WELCOME2025/ISRAEL30 give 1 month free Premium. Auto-uppercases input, prevents reuse via localStorage.</v>
+      </c>
+      <c r="E48" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F48" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G48" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H48" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B49" t="str">
+        <v>HH:MM</v>
+      </c>
+      <c r="C49" t="str">
+        <v>src/screens/SettingsScreen.tsx</v>
+      </c>
+      <c r="D49" t="str">
+        <v>Show 'Premium active until [date]' row with Calendar icon when premium activated via coupon (premiumExpiresAt is set)</v>
+      </c>
+      <c r="E49" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F49" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G49" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H49" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B50" t="str">
+        <v>HH:MM</v>
+      </c>
+      <c r="C50" t="str">
+        <v>src/screens/GroupsScreen.tsx</v>
+      </c>
+      <c r="D50" t="str">
+        <v>Add holiday assignment to group modal: searchable holiday list with checkboxes, premium-gated, saves to group.holidayIds</v>
+      </c>
+      <c r="E50" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F50" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G50" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H50" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B51" t="str">
+        <v>HH:MM</v>
+      </c>
+      <c r="C51" t="str">
+        <v>src/screens/DashboardScreen.tsx</v>
+      </c>
+      <c r="D51" t="str">
+        <v>Add group holiday alert section: upcoming holidays in 14-day window for groups with assigned holidays, contact count, Send to group button</v>
+      </c>
+      <c r="E51" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F51" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G51" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H51" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B52" t="str">
+        <v>HH:MM</v>
+      </c>
+      <c r="C52" t="str">
+        <v>build</v>
+      </c>
+      <c r="D52" t="str">
+        <v>Agent 5 build+lint check after 3-feature sprint: fixed 2 issues in MediaAttachmentPicker — (1) handleStopRecording used before declaration (moved above auto-stop useEffect), (2) setState called synchronously inside effect (moved 60s auto-stop logic into setInterval callback instead)</v>
+      </c>
+      <c r="E52" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F52" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G52" t="str">
+        <v>Agent 5</v>
+      </c>
+      <c r="H52" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B53" t="str">
+        <v>HH:MM</v>
+      </c>
+      <c r="C53" t="str">
+        <v>src/components/MediaAttachmentPicker.tsx + 6 files</v>
+      </c>
+      <c r="D53" t="str">
+        <v>Code review: 3-feature sprint — Greeting Media, Group Holiday Assignment, Coupon System. Full correctness + security + UX audit.</v>
+      </c>
+      <c r="E53" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F53" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G53" t="str">
+        <v>Agent 3</v>
+      </c>
+      <c r="H53" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B54" t="str">
+        <v>00:00</v>
+      </c>
+      <c r="C54" t="str">
+        <v>src/screens/CalendarScreen.tsx</v>
+      </c>
+      <c r="D54" t="str">
+        <v>Fix holiday color dot keys from index to h.id to prevent React mis-reconciliation when navigating months</v>
+      </c>
+      <c r="E54" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F54" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G54" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H54" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B55" t="str">
+        <v>00:05</v>
+      </c>
+      <c r="C55" t="str">
+        <v>src/screens/premium/ImportContactsScreen.tsx</v>
+      </c>
+      <c r="D55" t="str">
+        <v>Replace console.error calls in handleFile and handleImport catch blocks with importError state; surface errors to user via red banner with AlertCircle icon</v>
+      </c>
+      <c r="E55" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F55" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G55" t="str">
+        <v>Agent 5</v>
+      </c>
+      <c r="H55" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B56" t="str">
+        <v>21:42</v>
+      </c>
+      <c r="C56" t="str">
+        <v>src/screens/CalendarScreen.tsx, src/screens/premium/ImportContactsScreen.tsx</v>
+      </c>
+      <c r="D56" t="str">
+        <v>Reviewed CalendarScreen key fix + ImportContacts error handling — SHIP both. h.id verified on Holiday type and all data entries; importError state covers all paths. New findings: key={i} on day-header row (low), setImporting not in finally (low), importError not cleared on Back nav (low).</v>
+      </c>
+      <c r="E56" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F56" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G56" t="str">
+        <v>Agent 3</v>
+      </c>
+      <c r="H56" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B57" t="str">
+        <v>00:00</v>
+      </c>
+      <c r="C57" t="str">
+        <v>src/components/ContactCard.tsx</v>
+      </c>
+      <c r="D57" t="str">
+        <v>Replace non-interactive &lt;div&gt; root with &lt;button type="button"&gt; to give ContactCard full keyboard focusability, Enter/Space activation, and native ARIA button semantics (WCAG 2.1.1 / 4.1.2)</v>
+      </c>
+      <c r="E57" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F57" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G57" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H57" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B58" t="str">
+        <v>00:00</v>
+      </c>
+      <c r="C58" t="str">
+        <v>build</v>
+      </c>
+      <c r="D58" t="str">
+        <v>Build and lint clean — no errors or warnings. Scanned CalendarScreen.tsx and ImportContactsScreen.tsx: no console.error, unhandled .catch(), or TODO patterns found.</v>
+      </c>
+      <c r="E58" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F58" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G58" t="str">
+        <v>Agent 5</v>
+      </c>
+      <c r="H58" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B59" t="str">
+        <v>00:01</v>
+      </c>
+      <c r="C59" t="str">
+        <v>src/components/ContactCard.tsx</v>
+      </c>
+      <c r="D59" t="str">
+        <v>Reviewed ContactCard button accessibility fix — APPROVED with 3 follow-up findings: no :focus-visible ring on .card-interactive (WCAG 2.4.7 gap, medium priority), verbose AT accessible name (add aria-label={contact.name}, low), decorative icons missing aria-hidden (low). Core div→button conversion is correct: Tailwind preflight resets all button defaults before card class overrides, w-full restores block width, text-left prevents center-alignment, type=button guards against form submission.</v>
+      </c>
+      <c r="E59" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F59" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G59" t="str">
+        <v>Agent 3</v>
+      </c>
+      <c r="H59" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B60" t="str">
+        <v>00:00</v>
+      </c>
+      <c r="C60" t="str">
+        <v>src/index.css</v>
+      </c>
+      <c r="D60" t="str">
+        <v>Add :focus-visible ring to .card-interactive for WCAG 2.4.7 compliance</v>
+      </c>
+      <c r="E60" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F60" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G60" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H60" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B61" t="str">
+        <v>00:00</v>
+      </c>
+      <c r="C61" t="str">
+        <v>build</v>
+      </c>
+      <c r="D61" t="str">
+        <v>Build and lint clean — no issues found. ContactCard.tsx &lt;button&gt; refactor verified: type="button" present, no nested interactive elements, w-full/text-left classes compatible, TypeScript compiles without errors.</v>
+      </c>
+      <c r="E61" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F61" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G61" t="str">
+        <v>Agent 5</v>
+      </c>
+      <c r="H61" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B62" t="str">
+        <v>10:30</v>
+      </c>
+      <c r="C62" t="str">
+        <v>src/index.css</v>
+      </c>
+      <c r="D62" t="str">
+        <v>Reviewed .card-interactive:focus-visible ring — SHIPPED. Rule placement correct, selector well-scoped, var(--color-primary) defined in all 6 themes (marginal contrast in sunset/midnight noted as FINDING 67A). outline-offset: 2px correct — no layout impact. Forced-colors gap identified (FINDING 69). New findings: card-interactive on &lt;div&gt; in Dashboard/Groups still keyboard-unreachable (FINDING 67); .btn/.bottom-nav-item/.tier-card lack :focus-visible (FINDING 69-70).</v>
+      </c>
+      <c r="E62" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F62" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G62" t="str">
+        <v>Agent 3</v>
+      </c>
+      <c r="H62" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B63" t="str">
+        <v>00:00</v>
+      </c>
+      <c r="C63" t="str">
+        <v>src/services/communicationService.ts</v>
+      </c>
+      <c r="D63" t="str">
+        <v>Fix WhatsApp URL builder: normalize Israeli local phone numbers (052-xxx → 972xx) to valid E.164 format</v>
+      </c>
+      <c r="E63" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F63" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G63" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H63" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B64" t="str">
+        <v>22:09</v>
+      </c>
+      <c r="C64" t="str">
+        <v>build</v>
+      </c>
+      <c r="D64" t="str">
+        <v>Build and lint clean — no issues found after adding .card-interactive:focus-visible CSS rule in src/index.css</v>
+      </c>
+      <c r="E64" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F64" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G64" t="str">
+        <v>Agent 5</v>
+      </c>
+      <c r="H64" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B65" t="str">
+        <v>22:10</v>
+      </c>
+      <c r="C65" t="str">
+        <v>src/services/communicationService.ts</v>
+      </c>
+      <c r="D65" t="str">
+        <v>Reviewed WhatsApp phone normalization fix — CORRECT for all standard Israeli formats (mobile 05X, landlines 03/02/04/08); new findings: 00-prefix international numbers not normalized (FINDING 71), empty phone defensive return missing (FINDING 72), execCommand fallback deprecated (FINDING 73)</v>
+      </c>
+      <c r="E65" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F65" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G65" t="str">
+        <v>Agent 3</v>
+      </c>
+      <c r="H65" t="str">
+        <v>done</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E28"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H65"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H65"/>
+  <dimension ref="A1:H81"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -1856,9 +1856,425 @@
         <v>done</v>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B66" t="str">
+        <v>10:00</v>
+      </c>
+      <c r="C66" t="str">
+        <v>src/integrations/supabase/client.ts, src/integrations/payment/payme.ts, src/integrations/ai/claudeClient.ts</v>
+      </c>
+      <c r="D66" t="str">
+        <v>BUG-030: Add eslint-disable-next-line no-unused-vars to stub parameters (_userId, _req) in integration files to fix lint errors</v>
+      </c>
+      <c r="E66" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F66" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G66" t="str">
+        <v>Agent 5</v>
+      </c>
+      <c r="H66" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B67" t="str">
+        <v>10:30</v>
+      </c>
+      <c r="C67" t="str">
+        <v>src/screens/SettingsScreen.tsx</v>
+      </c>
+      <c r="D67" t="str">
+        <v>BUG-031: Language toggle indicator invisible when Hebrew selected. Moved width/borderRadius from Tailwind arbitrary-value class (w-[calc(50%-4px)]) to inline style — Tailwind stripped the spaces in calc() generating invalid CSS</v>
+      </c>
+      <c r="E67" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F67" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G67" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H67" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B68" t="str">
+        <v>11:00</v>
+      </c>
+      <c r="C68" t="str">
+        <v>src/components/WhatsAppButton.tsx</v>
+      </c>
+      <c r="D68" t="str">
+        <v>Add automatic image copy to clipboard on WhatsApp button click; Hebrew popup with paste instructions; close button; stores image as base64 canvas snapshot</v>
+      </c>
+      <c r="E68" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F68" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G68" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H68" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B69" t="str">
+        <v>11:00</v>
+      </c>
+      <c r="C69" t="str">
+        <v>src/services/communicationService.ts</v>
+      </c>
+      <c r="D69" t="str">
+        <v>BUG-032/033/034: Fix double 00-prefix in WhatsApp URL builder; add guard for empty phone string; remove deprecated execCommand clipboard fallback</v>
+      </c>
+      <c r="E69" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F69" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G69" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H69" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B70" t="str">
+        <v>11:30</v>
+      </c>
+      <c r="C70" t="str">
+        <v>src/screens/CalendarScreen.tsx</v>
+      </c>
+      <c r="D70" t="str">
+        <v>Add @hebcal/core Hebrew date (gematria) to every calendar cell; Rosh Chodesh shows month name; Hebrew month names in pill badge</v>
+      </c>
+      <c r="E70" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F70" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G70" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H70" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B71" t="str">
+        <v>11:30</v>
+      </c>
+      <c r="C71" t="str">
+        <v>src/i18n/index.ts</v>
+      </c>
+      <c r="D71" t="str">
+        <v>Add 3 i18n keys: whatsapp_image_ready_title, whatsapp_image_paste_hint, whatsapp_image_paste_steps (EN + HE)</v>
+      </c>
+      <c r="E71" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F71" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G71" t="str">
+        <v>Foundation-Agent</v>
+      </c>
+      <c r="H71" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B72" t="str">
+        <v>12:00</v>
+      </c>
+      <c r="C72" t="str">
+        <v>AGENTS.md</v>
+      </c>
+      <c r="D72" t="str">
+        <v>Create AGENTS.md — documentation of all 8 agent definitions, roles, and iteration action logs</v>
+      </c>
+      <c r="E72" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F72" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G72" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H72" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B73" t="str">
+        <v>15:00</v>
+      </c>
+      <c r="C73" t="str">
+        <v>src/i18n/index.ts</v>
+      </c>
+      <c r="D73" t="str">
+        <v>Add 20 i18n keys: urgency_critical/high/medium/low, go_back, action_wish_birthday_today/days, action_wish_holiday_days, action_reconnect_days, action_checkin, action_followup, holiday_major, holiday_moreContacts (EN + HE)</v>
+      </c>
+      <c r="E73" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F73" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G73" t="str">
+        <v>Foundation-Agent</v>
+      </c>
+      <c r="H73" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B74" t="str">
+        <v>15:00</v>
+      </c>
+      <c r="C74" t="str">
+        <v>src/core/scoringSystem.ts</v>
+      </c>
+      <c r="D74" t="str">
+        <v>BUG-020: Fix getBirthdayDaysUntil using date-fns differenceInCalendarDays — prevents wrong result on DST change days</v>
+      </c>
+      <c r="E74" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F74" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G74" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H74" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B75" t="str">
+        <v>15:00</v>
+      </c>
+      <c r="C75" t="str">
+        <v>src/components/Navigation.tsx, src/screens/ContactDetailScreen.tsx, src/screens/HolidayDetailScreen.tsx, src/screens/DashboardScreen.tsx, src/screens/GroupsScreen.tsx, src/components/ui/Modal.tsx, src/screens/premium/ImportContactsScreen.tsx, src/components/ContactCard.tsx, src/index.css</v>
+      </c>
+      <c r="D75" t="str">
+        <v>BUG-036 / FINDINGS 25A/20/23/28A/30B/60/66/67/69: aria-labels localized, urgency/frequency labels translated, group+dashboard cards converted to &lt;button&gt;, .btn:focus-visible ring added, setImporting in finally, decorative icon aria-hidden</v>
+      </c>
+      <c r="E75" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F75" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G75" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H75" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B76" t="str">
+        <v>15:00</v>
+      </c>
+      <c r="C76" t="str">
+        <v>src/screens/SettingsScreen.tsx, src/screens/UpgradeScreen.tsx</v>
+      </c>
+      <c r="D76" t="str">
+        <v>SECURITY: Wrap Danger Zone section and demo premium activation button in import.meta.env.DEV — both are completely tree-shaken from production builds by rolldown</v>
+      </c>
+      <c r="E76" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F76" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G76" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H76" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B77" t="str">
+        <v>16:00</v>
+      </c>
+      <c r="C77" t="str">
+        <v>src/utils/hebrewDateUtils.ts</v>
+      </c>
+      <c r="D77" t="str">
+        <v>Create hebrewDateUtils.ts — getHebrewDateStr(isoDate) converts Gregorian ISO date to Hebrew gematria string (e.g. ד׳ באייר תשפ״ו); uses local-time Date construction to avoid UTC timezone shifts</v>
+      </c>
+      <c r="E77" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F77" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G77" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H77" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B78" t="str">
+        <v>16:00</v>
+      </c>
+      <c r="C78" t="str">
+        <v>src/data/holidays.ts</v>
+      </c>
+      <c r="D78" t="str">
+        <v>BUG-037: Yom HaAtzmaut 2026 was hardcoded as 2026-04-29 (wrong by 8 days); replaced with runtime computation via HebrewCalendar.getHolidaysForYearArray(5786, true) from @hebcal/core; correct date is 2026-04-21 (ד׳ באייר תשפ״ו)</v>
+      </c>
+      <c r="E78" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F78" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G78" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H78" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B79" t="str">
+        <v>16:00</v>
+      </c>
+      <c r="C79" t="str">
+        <v>src/components/HolidayCard.tsx, src/screens/HolidayDetailScreen.tsx</v>
+      </c>
+      <c r="D79" t="str">
+        <v>Add Hebrew date badge (gematria format) to HolidayCard compact/full views and HolidayDetailScreen hero banner for all dateType === "hebrew" holidays</v>
+      </c>
+      <c r="E79" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F79" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G79" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H79" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B80" t="str">
+        <v>17:00</v>
+      </c>
+      <c r="C80" t="str">
+        <v>src/screens/TermsScreen.tsx</v>
+      </c>
+      <c r="D80" t="str">
+        <v>BUG-038: Terms of Service page always showed English. Root cause: SECTIONS array was at module scope — t() calls were made once on load, ignoring language changes. Fix: moved SECTIONS inside component; replaced all hardcoded strings with titleKey/bodyKey references + t() calls with as const + TranslationKey cast</v>
+      </c>
+      <c r="E80" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F80" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G80" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H80" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B81" t="str">
+        <v>17:00</v>
+      </c>
+      <c r="C81" t="str">
+        <v>src/i18n/index.ts</v>
+      </c>
+      <c r="D81" t="str">
+        <v>Add 22 i18n keys for Terms of Service: terms_lastUpdated, terms_intro, terms_s1_title/body through terms_s10_title/body — full Hebrew translations for all 10 sections (EN + HE)</v>
+      </c>
+      <c r="E81" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F81" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G81" t="str">
+        <v>Foundation-Agent</v>
+      </c>
+      <c r="H81" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H65"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H81"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H81"/>
+  <dimension ref="A1:H83"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -2272,9 +2272,61 @@
         <v>done</v>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B82" t="str">
+        <v>18:00</v>
+      </c>
+      <c r="C82" t="str">
+        <v>src/services/analyticsService.ts</v>
+      </c>
+      <c r="D82" t="str">
+        <v>Create local analytics service: getAnonymousUserId() generates/persists UUID in localStorage (nm_user_id); trackEvent(name, metadata?) stores up to 100 events FIFO in nm_events. No backend, no dashboard, zero side effects.</v>
+      </c>
+      <c r="E82" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F82" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G82" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H82" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B83" t="str">
+        <v>18:00</v>
+      </c>
+      <c r="C83" t="str">
+        <v>src/App.tsx, src/screens/ContactFormScreen.tsx, src/components/ChannelPicker.tsx, src/screens/premium/ImportContactsScreen.tsx</v>
+      </c>
+      <c r="D83" t="str">
+        <v>Add trackEvent calls for 4 events: app_open (AppShell mount), contact_created (new contact only), greeting_sent (with channel metadata), contacts_imported (with count metadata)</v>
+      </c>
+      <c r="E83" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F83" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G83" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H83" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H81"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H83"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H83"/>
+  <dimension ref="A1:H88"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -2324,9 +2324,139 @@
         <v>done</v>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B84" t="str">
+        <v>19:00</v>
+      </c>
+      <c r="C84" t="str">
+        <v>src/screens/CalendarScreen.tsx</v>
+      </c>
+      <c r="D84" t="str">
+        <v>BUG-039: Contact birthdays never appeared in calendar. Added birthdayMap useMemo — builds Map&lt;date-string, Contact[]&gt; for visible month using hebrewBirthday (priority) or birthday. Pink dot (#EC4899) added to cell dots row. Birthday panel section added below calendar showing contact name cards for selected day / full month.</v>
+      </c>
+      <c r="E84" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F84" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G84" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H84" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B85" t="str">
+        <v>19:00</v>
+      </c>
+      <c r="C85" t="str">
+        <v>src/types/index.ts</v>
+      </c>
+      <c r="D85" t="str">
+        <v>FEATURE: Add optional hebrewBirthday?: string field to Contact interface — stored as "DD-MM" (Hebrew day-month, year-agnostic). Additive only; does not affect existing birthday field.</v>
+      </c>
+      <c r="E85" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F85" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G85" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H85" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B86" t="str">
+        <v>19:00</v>
+      </c>
+      <c r="C86" t="str">
+        <v>src/utils/hebrewDateUtils.ts</v>
+      </c>
+      <c r="D86" t="str">
+        <v>FEATURE: Add hebrewBirthdayToGregorianInCalendarYear(hebrewBirthday, gregorianYear) — converts "DD-MM" Hebrew date to Gregorian Date for a given year; tries approxHYear and approxHYear+1 to handle year boundary; returns null for invalid combos (e.g. Adar II in non-leap year)</v>
+      </c>
+      <c r="E86" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F86" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G86" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H86" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B87" t="str">
+        <v>19:00</v>
+      </c>
+      <c r="C87" t="str">
+        <v>src/screens/ContactFormScreen.tsx</v>
+      </c>
+      <c r="D87" t="str">
+        <v>FEATURE: Add Hebrew Birthday UI in premium section — shown for Judaism contacts or when hebrewBirthday already set. Two dropdowns (day 1–30, Hebrew month 1–12 with names). Derives day/month from form.hebrewBirthday via useMemo. Clear button removes the field. Saved as "DD-MM" string.</v>
+      </c>
+      <c r="E87" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F87" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G87" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H87" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B88" t="str">
+        <v>19:00</v>
+      </c>
+      <c r="C88" t="str">
+        <v>src/i18n/index.ts</v>
+      </c>
+      <c r="D88" t="str">
+        <v>Add 7 i18n keys (EN + HE): calendar_birthdays, calendar_birthdayLabel, calendar_birthdaysOn, contactForm_hebrewBirthday, contactForm_hebrewBirthdayDay, contactForm_hebrewBirthdayMonth, contactForm_hebrewBirthdayClear</v>
+      </c>
+      <c r="E88" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F88" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G88" t="str">
+        <v>Foundation-Agent</v>
+      </c>
+      <c r="H88" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H83"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H88"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H88"/>
+  <dimension ref="A1:H93"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -2454,9 +2454,139 @@
         <v>done</v>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B89" t="str">
+        <v>20:00</v>
+      </c>
+      <c r="C89" t="str">
+        <v>src/screens/GreetingEditorScreen.tsx</v>
+      </c>
+      <c r="D89" t="str">
+        <v>BL-015: Replace hardcoded tier desc strings with i18n keys (greeting_tier_*_desc). Signature placeholder via t('greeting_signature_placeholder'). BL-017: aria-label on Regenerate and Copy icon buttons. BL-018: aria-expanded on Advanced tone + Signature toggle buttons. aria-hidden on decorative icons.</v>
+      </c>
+      <c r="E89" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F89" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G89" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H89" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B90" t="str">
+        <v>20:00</v>
+      </c>
+      <c r="C90" t="str">
+        <v>src/i18n/index.ts</v>
+      </c>
+      <c r="D90" t="str">
+        <v>BL-015: Add 4 i18n keys (EN + HE): greeting_tier_casual_desc, greeting_tier_professional_desc, greeting_tier_vip_desc, greeting_signature_placeholder</v>
+      </c>
+      <c r="E90" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F90" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G90" t="str">
+        <v>Foundation-Agent</v>
+      </c>
+      <c r="H90" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B91" t="str">
+        <v>20:00</v>
+      </c>
+      <c r="C91" t="str">
+        <v>src/components/ContactCard.tsx</v>
+      </c>
+      <c r="D91" t="str">
+        <v>BL-016: Add ACTION_KEY Record&lt;SuggestedActionType, TranslationKey&gt; map. Use useT() + t(ACTION_KEY[...]) to display action label in current language instead of raw English label string.</v>
+      </c>
+      <c r="E91" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F91" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G91" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H91" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B92" t="str">
+        <v>20:00</v>
+      </c>
+      <c r="C92" t="str">
+        <v>src/screens/ContactDetailScreen.tsx</v>
+      </c>
+      <c r="D92" t="str">
+        <v>BL-017: aria-label on Edit icon button via t('contactForm_edit'). BL-041: Add celebration feedback on Mark as Contacted — 6 emoji particle burst (.animate-particle with --tx/--ty CSS vars), Web Audio oscillator ping (880→1200Hz ramp, 0.4s), haptic navigator.vibrate(40). Respects prefers-reduced-motion. useState celebrating moved before early return to comply with hooks rules.</v>
+      </c>
+      <c r="E92" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F92" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G92" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H92" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B93" t="str">
+        <v>20:00</v>
+      </c>
+      <c r="C93" t="str">
+        <v>src/index.css</v>
+      </c>
+      <c r="D93" t="str">
+        <v>BL-041: Add @keyframes particleBurst (translate + scale to 0 + opacity fade driven by --tx/--ty CSS custom properties) and .animate-particle utility class (1.2s ease-out forwards).</v>
+      </c>
+      <c r="E93" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F93" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G93" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H93" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H88"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H93"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H93"/>
+  <dimension ref="A1:H95"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -2584,9 +2584,61 @@
         <v>done</v>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B94" t="str">
+        <v>20:30</v>
+      </c>
+      <c r="C94" t="str">
+        <v>agent_state/iteration_log.md</v>
+      </c>
+      <c r="D94" t="str">
+        <v>BUG-040 fix: reconstructed iterations 13–17 from changelog_queue.json. All 5 entries appended: iter 13 (Hebrew date display + BUG-037), iter 14 (BUG-038 Terms fix), iter 15 (analytics foundation), iter 16 (BUG-039 birthday calendar + Hebrew birthday feature), iter 17 (BL-015/016/017/018/041 i18n + accessibility + celebration). Agent 2/3 columns marked TBD where source files have no entries. Log is now continuous 0–17.</v>
+      </c>
+      <c r="E94" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F94" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G94" t="str">
+        <v>Agent 4</v>
+      </c>
+      <c r="H94" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B95" t="str">
+        <v>20:30</v>
+      </c>
+      <c r="C95" t="str">
+        <v>BUG_REPORT.md</v>
+      </c>
+      <c r="D95" t="str">
+        <v>Added BUG-040 entry: iteration_log.md missing iterations 13–17. Marked fixed.</v>
+      </c>
+      <c r="E95" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F95" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G95" t="str">
+        <v>Agent 4</v>
+      </c>
+      <c r="H95" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H93"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H95"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H95"/>
+  <dimension ref="A1:H97"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -2636,9 +2636,61 @@
         <v>done</v>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B96" t="str">
+        <v>21:00</v>
+      </c>
+      <c r="C96" t="str">
+        <v>src/App.tsx</v>
+      </c>
+      <c r="D96" t="str">
+        <v>BL-019: Convert 13 screens to React.lazy (CalendarScreen, HolidayDetailScreen, ContactsScreen, ContactDetailScreen, ContactFormScreen, GreetingEditorScreen, GroupsScreen, SettingsScreen, UpgradeScreen, AboutScreen, PrivacyScreen, TermsScreen, WhatsNewScreen). Move Suspense fallback into WithNav so BottomNav stays visible during load. Remove now-redundant inner Suspense from 3 premium routes. Main bundle: 435 kB → 285 kB raw (-150 kB), 130 kB → 93 kB gzip (-37 kB).</v>
+      </c>
+      <c r="E96" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F96" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G96" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H96" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B97" t="str">
+        <v>21:00</v>
+      </c>
+      <c r="C97" t="str">
+        <v>src/core/scoringSystem.ts</v>
+      </c>
+      <c r="D97" t="str">
+        <v>BL-020: Add module-level scoreCache Map&lt;string, RelationshipScore&gt; keyed by `contact.id|contact.updatedAt`. calculateRelationshipScore checks cache on entry and sets result before return. Eliminates redundant scoring for unchanged contacts on every render. Stale results impossible since updatedAt is always stamped on mutation.</v>
+      </c>
+      <c r="E97" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F97" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G97" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H97" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H95"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H97"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H97"/>
+  <dimension ref="A1:H105"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -2675,22 +2675,218 @@
       <c r="D97" t="str">
         <v>BL-020: Add module-level scoreCache Map&lt;string, RelationshipScore&gt; keyed by `contact.id|contact.updatedAt`. calculateRelationshipScore checks cache on entry and sets result before return. Eliminates redundant scoring for unchanged contacts on every render. Stale results impossible since updatedAt is always stamped on mutation.</v>
       </c>
-      <c r="E97" t="str">
-        <v>improvement</v>
-      </c>
-      <c r="F97" t="str">
-        <v>code_change</v>
-      </c>
-      <c r="G97" t="str">
-        <v>Agent 1</v>
-      </c>
-      <c r="H97" t="str">
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B98" t="str">
+        <v>22:00</v>
+      </c>
+      <c r="C98" t="str">
+        <v>src/types/index.ts</v>
+      </c>
+      <c r="D98" t="str">
+        <v>BL-026: Add CelebrationType union type (Jewish|Christian|Muslim|Druze|Secular); add optional celebrationType field to Contact interface</v>
+      </c>
+      <c r="E98" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F98" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G98" t="str">
+        <v>Foundation Agent</v>
+      </c>
+      <c r="H98" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B99" t="str">
+        <v>22:00</v>
+      </c>
+      <c r="C99" t="str">
+        <v>src/i18n/index.ts</v>
+      </c>
+      <c r="D99" t="str">
+        <v>BL-026+BL-023+BL-030: Add 34 i18n keys — celebrationType_* (5 values EN+HE), contactForm_celebrationType, notif_overdue/notif_overdue_body, 14 deviceContacts_* keys, premium_feat_device_contacts — all in EN and HE</v>
+      </c>
+      <c r="E99" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F99" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G99" t="str">
+        <v>Foundation Agent</v>
+      </c>
+      <c r="H99" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B100" t="str">
+        <v>22:00</v>
+      </c>
+      <c r="C100" t="str">
+        <v>src/core/scoringSystem.ts</v>
+      </c>
+      <c r="D100" t="str">
+        <v>BL-026: Add CELEBRATION_TO_RELIGION map; update getUpcomingHolidaysForContact to prefer celebrationType over religion when set, falling back to religion for existing contacts</v>
+      </c>
+      <c r="E100" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F100" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G100" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H100" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B101" t="str">
+        <v>22:00</v>
+      </c>
+      <c r="C101" t="str">
+        <v>src/screens/ContactFormScreen.tsx</v>
+      </c>
+      <c r="D101" t="str">
+        <v>BL-026: Add celebrationType Select dropdown to Cultural &amp; Language section; wire into form state and handleSave; import CelebrationType type</v>
+      </c>
+      <c r="E101" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F101" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G101" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H101" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B102" t="str">
+        <v>22:00</v>
+      </c>
+      <c r="C102" t="str">
+        <v>src/services/notificationService.ts</v>
+      </c>
+      <c r="D102" t="str">
+        <v>BL-023: Add overdue-contact reminder — fires when daysSince &gt;= 45 days with no upcoming birthday within 7 days; dedup via existing nm_notif_sent localStorage mechanism</v>
+      </c>
+      <c r="E102" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F102" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G102" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H102" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B103" t="str">
+        <v>22:00</v>
+      </c>
+      <c r="C103" t="str">
+        <v>src/screens/DeviceContactsScreen.tsx</v>
+      </c>
+      <c r="D103" t="str">
+        <v>BL-030: New screen — consent → permission request → device contact list with checkboxes → import with phone dedup. Capacitor.isNativePlatform() guard shows graceful web-only message. Imports @capacitor-community/contacts. Premium-gated via App.tsx route.</v>
+      </c>
+      <c r="E103" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F103" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G103" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H103" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B104" t="str">
+        <v>22:00</v>
+      </c>
+      <c r="C104" t="str">
+        <v>src/App.tsx</v>
+      </c>
+      <c r="D104" t="str">
+        <v>BL-030: Add DeviceContactsScreen lazy import; add route /device-contacts with Premium gate (isPremium ? DeviceContactsScreen : UpgradeScreen)</v>
+      </c>
+      <c r="E104" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F104" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G104" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H104" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B105" t="str">
+        <v>22:00</v>
+      </c>
+      <c r="C105" t="str">
+        <v>src/screens/premium/ImportContactsScreen.tsx</v>
+      </c>
+      <c r="D105" t="str">
+        <v>BL-030: Add "Import from Phone" shortcut card at top of Import screen; navigates to /device-contacts</v>
+      </c>
+      <c r="E105" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F105" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G105" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H105" t="str">
         <v>done</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H97"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H105"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H105"/>
+  <dimension ref="A1:H107"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -2884,9 +2884,61 @@
         <v>done</v>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B106" t="str">
+        <v>23:00</v>
+      </c>
+      <c r="C106" t="str">
+        <v>src/screens/CalendarScreen.tsx</v>
+      </c>
+      <c r="D106" t="str">
+        <v>BUG-043: Fix multi-day holidays only showing dot on first day. Replace isSameDay check with numeric YYYYMMDD range [startNum, endNum] in getHolidaysForDay. Fix monthly list to show holidays overlapping the visible month (not just holidays that start in the month). Remove unused isSameMonth import.</v>
+      </c>
+      <c r="E106" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F106" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G106" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H106" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B107" t="str">
+        <v>23:00</v>
+      </c>
+      <c r="C107" t="str">
+        <v>src/data/holidays.ts</v>
+      </c>
+      <c r="D107" t="str">
+        <v>BUG-044: Add missing sukkot-2026 entry (Sep 25 – Oct 2, 2026 / 15–22 Tishrei 5787). Covers full festival including Hoshana Rabbah and Shemini Atzeret / Simchat Torah. Matches existing sukkot-2025 pattern.</v>
+      </c>
+      <c r="E107" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F107" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G107" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H107" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H105"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H107"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H107"/>
+  <dimension ref="A1:H109"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -2936,9 +2936,61 @@
         <v>done</v>
       </c>
     </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B108" t="str">
+        <v>23:30</v>
+      </c>
+      <c r="C108" t="str">
+        <v>src/screens/ContactDetailScreen.tsx</v>
+      </c>
+      <c r="D108" t="str">
+        <v>BL-045: Replace harsh oscillator with C5/E5/G5 major triad arpeggio (3 sine waves, ~0.75s, pleasant chord). Expand particles from 6 to 10, size text-xl (was text-base), wider spread ±85px h / ±110px v. Animation delay stagger 50ms per particle (was 40ms). State clear timeout 1600ms.</v>
+      </c>
+      <c r="E108" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F108" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G108" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H108" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B109" t="str">
+        <v>23:30</v>
+      </c>
+      <c r="C109" t="str">
+        <v>src/index.css</v>
+      </c>
+      <c r="D109" t="str">
+        <v>BL-045: Update particleBurst keyframe — scale-pop effect: 0.4 → 1.6 → 0 across 0/18%/100% keyframe stops, giving a visible "pop then fly" motion. Animation class duration 1.2s → 1.4s.</v>
+      </c>
+      <c r="E109" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F109" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G109" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H109" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H107"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H109"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H109"/>
+  <dimension ref="A1:H120"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -2988,9 +2988,295 @@
         <v>done</v>
       </c>
     </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B110" t="str">
+        <v>00:00</v>
+      </c>
+      <c r="C110" t="str">
+        <v>src/services/exportService.ts</v>
+      </c>
+      <c r="D110" t="str">
+        <v>BL-025 (Sprint 4): New exportContactsToCSV() using PapaParse. Exports all Contact fields to CSV with UTF-8 BOM for Hebrew Excel compatibility. Downloads as nevermiss-contacts-YYYY-MM-DD.csv.</v>
+      </c>
+      <c r="E110" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F110" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G110" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H110" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B111" t="str">
+        <v>00:00</v>
+      </c>
+      <c r="C111" t="str">
+        <v>src/screens/SettingsScreen.tsx</v>
+      </c>
+      <c r="D111" t="str">
+        <v>BL-025 (Sprint 4): Added Export Contacts to CSV button in Premium Features card. exportDone state shows success feedback for 2.5s.</v>
+      </c>
+      <c r="E111" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F111" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G111" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H111" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B112" t="str">
+        <v>00:00</v>
+      </c>
+      <c r="C112" t="str">
+        <v>src/i18n/index.ts</v>
+      </c>
+      <c r="D112" t="str">
+        <v>BL-025 (Sprint 4): Added i18n keys settings_exportContacts + settings_exportSuccess in EN+HE.</v>
+      </c>
+      <c r="E112" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F112" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G112" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H112" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B113" t="str">
+        <v>00:30</v>
+      </c>
+      <c r="C113" t="str">
+        <v>src/components/Navigation.tsx</v>
+      </c>
+      <c r="D113" t="str">
+        <v>BL-029 (Sprint 4) WCAG 2.5.5: Back button in PageHeader changed to min-w/h-[48px] flex items-center justify-center — 48×48px minimum tap target.</v>
+      </c>
+      <c r="E113" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F113" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G113" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H113" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B114" t="str">
+        <v>00:30</v>
+      </c>
+      <c r="C114" t="str">
+        <v>src/screens/ContactFormScreen.tsx</v>
+      </c>
+      <c r="D114" t="str">
+        <v>BL-029 (Sprint 4) WCAG 2.5.5: Delete icon button in ContactForm PageHeader changed to min-w/h-[48px] tap target.</v>
+      </c>
+      <c r="E114" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F114" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G114" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H114" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B115" t="str">
+        <v>00:30</v>
+      </c>
+      <c r="C115" t="str">
+        <v>src/screens/GroupsScreen.tsx</v>
+      </c>
+      <c r="D115" t="str">
+        <v>BL-029 (Sprint 4) WCAG 2.5.5: Edit and Delete icon buttons on group cards changed to min-w/h-[48px] tap targets.</v>
+      </c>
+      <c r="E115" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F115" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G115" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H115" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B116" t="str">
+        <v>00:30</v>
+      </c>
+      <c r="C116" t="str">
+        <v>src/screens/GreetingEditorScreen.tsx</v>
+      </c>
+      <c r="D116" t="str">
+        <v>BL-029 (Sprint 4) WCAG 2.5.5: Regenerate and Copy icon buttons changed to min-w/h-[48px] tap targets.</v>
+      </c>
+      <c r="E116" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F116" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G116" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H116" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B117" t="str">
+        <v>00:30</v>
+      </c>
+      <c r="C117" t="str">
+        <v>src/components/ui/Modal.tsx</v>
+      </c>
+      <c r="D117" t="str">
+        <v>BL-029 (Sprint 4) WCAG 2.5.5: Close (X) button in Modal header changed to min-w/h-[48px] tap target.</v>
+      </c>
+      <c r="E117" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F117" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G117" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H117" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B118" t="str">
+        <v>00:30</v>
+      </c>
+      <c r="C118" t="str">
+        <v>src/screens/ContactDetailScreen.tsx</v>
+      </c>
+      <c r="D118" t="str">
+        <v>BL-029 (Sprint 4) WCAG 2.5.5: Edit icon button in ContactDetail PageHeader changed to min-w/h-[48px] tap target.</v>
+      </c>
+      <c r="E118" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F118" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G118" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H118" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B119" t="str">
+        <v>00:30</v>
+      </c>
+      <c r="C119" t="str">
+        <v>src/screens/HolidayDetailScreen.tsx</v>
+      </c>
+      <c r="D119" t="str">
+        <v>BL-029 (Sprint 4) WCAG 2.5.5: Copy greeting icon button changed to min-w/h-[48px] tap target.</v>
+      </c>
+      <c r="E119" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F119" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G119" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H119" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B120" t="str">
+        <v>00:30</v>
+      </c>
+      <c r="C120" t="str">
+        <v>src/screens/premium/BirthdayGreetingEditorScreen.tsx</v>
+      </c>
+      <c r="D120" t="str">
+        <v>BL-029 (Sprint 4) WCAG 2.5.5: Regenerate and Copy icon buttons in BirthdayGreetingEditor changed to min-w/h-[48px] tap targets.</v>
+      </c>
+      <c r="E120" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F120" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G120" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H120" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H109"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H120"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H120"/>
+  <dimension ref="A1:H126"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -3274,9 +3274,165 @@
         <v>done</v>
       </c>
     </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B121" t="str">
+        <v>01:00</v>
+      </c>
+      <c r="C121" t="str">
+        <v>src/services/hapticService.ts</v>
+      </c>
+      <c r="D121" t="str">
+        <v>BL-024 (Sprint 4): New hapticService with hapticLight/Medium/Success/Error. Uses Capacitor.isNativePlatform() guard — graceful no-op in browser. ImpactStyle.Light/Medium and NotificationType.Success/Error.</v>
+      </c>
+      <c r="E121" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F121" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G121" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H121" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B122" t="str">
+        <v>01:00</v>
+      </c>
+      <c r="C122" t="str">
+        <v>src/screens/ContactFormScreen.tsx + src/components/ChannelPicker.tsx + src/screens/UpgradeScreen.tsx</v>
+      </c>
+      <c r="D122" t="str">
+        <v>BL-024 (Sprint 4): Haptic wired to 3 key actions — hapticSuccess after contact save, hapticMedium on greeting channel select, hapticSuccess/Error on coupon redemption.</v>
+      </c>
+      <c r="E122" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F122" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G122" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H122" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B123" t="str">
+        <v>01:30</v>
+      </c>
+      <c r="C123" t="str">
+        <v>src/services/storageService.ts</v>
+      </c>
+      <c r="D123" t="str">
+        <v>BL-034 (Sprint 4): exportBackupJSON() exports contacts+groups+drafts+settings as JSON with UTF-8 encoding; importBackupJSON() reads File and restores data after validation. Version and exportedAt metadata included.</v>
+      </c>
+      <c r="E123" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F123" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G123" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H123" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B124" t="str">
+        <v>01:30</v>
+      </c>
+      <c r="C124" t="str">
+        <v>src/screens/SettingsScreen.tsx</v>
+      </c>
+      <c r="D124" t="str">
+        <v>BL-034 (Sprint 4): Added Backup and Restore buttons to Premium Features card. Hidden file input for restore. Success reloads page after 1.2s. Error feedback clears after 3s.</v>
+      </c>
+      <c r="E124" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F124" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G124" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H124" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B125" t="str">
+        <v>01:45</v>
+      </c>
+      <c r="C125" t="str">
+        <v>src/screens/ContactFormScreen.tsx</v>
+      </c>
+      <c r="D125" t="str">
+        <v>BL-035 (Sprint 4): Duplicate contact detection on new contact creation. findDuplicate() checks exact name match or phone (7+ digits stripped). Modal warns with matching name and offers "Save Anyway" or "Cancel". Edit mode excluded.</v>
+      </c>
+      <c r="E125" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F125" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G125" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H125" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B126" t="str">
+        <v>01:45</v>
+      </c>
+      <c r="C126" t="str">
+        <v>src/i18n/index.ts</v>
+      </c>
+      <c r="D126" t="str">
+        <v>BL-024+034+035: Added 13 i18n keys in EN+HE: settings_backupData/Success, settings_restoreData/Success/Error, contactForm_duplicateTitle/Body/SaveAnyway.</v>
+      </c>
+      <c r="E126" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F126" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G126" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H126" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H120"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H126"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H126"/>
+  <dimension ref="A1:H151"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -1864,10 +1864,10 @@
         <v>10:00</v>
       </c>
       <c r="C66" t="str">
-        <v>src/integrations/supabase/client.ts, src/integrations/payment/payme.ts, src/integrations/ai/claudeClient.ts</v>
+        <v>src/integrations/supabase/client.ts</v>
       </c>
       <c r="D66" t="str">
-        <v>BUG-030: Add eslint-disable-next-line no-unused-vars to stub parameters (_userId, _req) in integration files to fix lint errors</v>
+        <v>תוקן BUG-030 — no-unused-vars lint על פרמטר _userId ב-stub; הוסף eslint-disable-next-line</v>
       </c>
       <c r="E66" t="str">
         <v>bugfix</v>
@@ -1887,13 +1887,13 @@
         <v>2026-04-28</v>
       </c>
       <c r="B67" t="str">
-        <v>10:30</v>
+        <v>10:00</v>
       </c>
       <c r="C67" t="str">
-        <v>src/screens/SettingsScreen.tsx</v>
+        <v>src/integrations/payment/payme.ts</v>
       </c>
       <c r="D67" t="str">
-        <v>BUG-031: Language toggle indicator invisible when Hebrew selected. Moved width/borderRadius from Tailwind arbitrary-value class (w-[calc(50%-4px)]) to inline style — Tailwind stripped the spaces in calc() generating invalid CSS</v>
+        <v>תוקן BUG-030 — no-unused-vars lint על פרמטר _req ב-stub; הוסף eslint-disable-next-line</v>
       </c>
       <c r="E67" t="str">
         <v>bugfix</v>
@@ -1902,7 +1902,7 @@
         <v>code_change</v>
       </c>
       <c r="G67" t="str">
-        <v>Agent 1</v>
+        <v>Agent 5</v>
       </c>
       <c r="H67" t="str">
         <v>done</v>
@@ -1913,22 +1913,22 @@
         <v>2026-04-28</v>
       </c>
       <c r="B68" t="str">
-        <v>11:00</v>
+        <v>10:00</v>
       </c>
       <c r="C68" t="str">
-        <v>src/components/WhatsAppButton.tsx</v>
+        <v>src/integrations/ai/claudeClient.ts</v>
       </c>
       <c r="D68" t="str">
-        <v>Add automatic image copy to clipboard on WhatsApp button click; Hebrew popup with paste instructions; close button; stores image as base64 canvas snapshot</v>
+        <v>תוקן BUG-030 — no-unused-vars lint על פרמטר _req ב-stub; הוסף eslint-disable-next-line</v>
       </c>
       <c r="E68" t="str">
-        <v>feature</v>
+        <v>bugfix</v>
       </c>
       <c r="F68" t="str">
         <v>code_change</v>
       </c>
       <c r="G68" t="str">
-        <v>Agent 1</v>
+        <v>Agent 5</v>
       </c>
       <c r="H68" t="str">
         <v>done</v>
@@ -1939,13 +1939,13 @@
         <v>2026-04-28</v>
       </c>
       <c r="B69" t="str">
-        <v>11:00</v>
+        <v>10:30</v>
       </c>
       <c r="C69" t="str">
-        <v>src/services/communicationService.ts</v>
+        <v>src/screens/SettingsScreen.tsx</v>
       </c>
       <c r="D69" t="str">
-        <v>BUG-032/033/034: Fix double 00-prefix in WhatsApp URL builder; add guard for empty phone string; remove deprecated execCommand clipboard fallback</v>
+        <v>תוקן BUG-031 — מחוון שפה בלתי נראה; w-[calc(50%-4px)] ב-Tailwind יצר CSS לא תקין; הועבר ל-inline style</v>
       </c>
       <c r="E69" t="str">
         <v>bugfix</v>
@@ -1965,13 +1965,13 @@
         <v>2026-04-28</v>
       </c>
       <c r="B70" t="str">
-        <v>11:30</v>
+        <v>11:00</v>
       </c>
       <c r="C70" t="str">
-        <v>src/screens/CalendarScreen.tsx</v>
+        <v>src/components/WhatsAppButton.tsx</v>
       </c>
       <c r="D70" t="str">
-        <v>Add @hebcal/core Hebrew date (gematria) to every calendar cell; Rosh Chodesh shows month name; Hebrew month names in pill badge</v>
+        <v>נוסף: העתקת תמונה אוטומטית ל-clipboard בלחיצה על WhatsApp; popup עברי עם הנחיות הדבקה; כפתור סיום</v>
       </c>
       <c r="E70" t="str">
         <v>feature</v>
@@ -1991,22 +1991,22 @@
         <v>2026-04-28</v>
       </c>
       <c r="B71" t="str">
-        <v>11:30</v>
+        <v>11:00</v>
       </c>
       <c r="C71" t="str">
-        <v>src/i18n/index.ts</v>
+        <v>src/services/communicationService.ts</v>
       </c>
       <c r="D71" t="str">
-        <v>Add 3 i18n keys: whatsapp_image_ready_title, whatsapp_image_paste_hint, whatsapp_image_paste_steps (EN + HE)</v>
+        <v>תוקן BUG-032 (00-prefix כפול), BUG-033 (guard טלפון ריק), BUG-034 (הוסר execCommand מיושן)</v>
       </c>
       <c r="E71" t="str">
-        <v>feature</v>
+        <v>bugfix</v>
       </c>
       <c r="F71" t="str">
         <v>code_change</v>
       </c>
       <c r="G71" t="str">
-        <v>Foundation-Agent</v>
+        <v>Agent 1</v>
       </c>
       <c r="H71" t="str">
         <v>done</v>
@@ -2017,16 +2017,16 @@
         <v>2026-04-28</v>
       </c>
       <c r="B72" t="str">
-        <v>12:00</v>
+        <v>11:30</v>
       </c>
       <c r="C72" t="str">
-        <v>AGENTS.md</v>
+        <v>src/screens/CalendarScreen.tsx</v>
       </c>
       <c r="D72" t="str">
-        <v>Create AGENTS.md — documentation of all 8 agent definitions, roles, and iteration action logs</v>
+        <v>נוסף: שילוב @hebcal/core — תאריך עברי (גמטריה) בכל תא; ראש חודש עם שם חודש; שמות חודשים עבריים ב-pill</v>
       </c>
       <c r="E72" t="str">
-        <v>improvement</v>
+        <v>feature</v>
       </c>
       <c r="F72" t="str">
         <v>code_change</v>
@@ -2043,13 +2043,13 @@
         <v>2026-04-28</v>
       </c>
       <c r="B73" t="str">
-        <v>15:00</v>
+        <v>11:30</v>
       </c>
       <c r="C73" t="str">
         <v>src/i18n/index.ts</v>
       </c>
       <c r="D73" t="str">
-        <v>Add 20 i18n keys: urgency_critical/high/medium/low, go_back, action_wish_birthday_today/days, action_wish_holiday_days, action_reconnect_days, action_checkin, action_followup, holiday_major, holiday_moreContacts (EN + HE)</v>
+        <v>נוספו 3 מפתחות i18n: whatsapp_image_ready_title, whatsapp_image_paste_hint, whatsapp_image_paste_steps (EN + HE)</v>
       </c>
       <c r="E73" t="str">
         <v>feature</v>
@@ -2069,16 +2069,16 @@
         <v>2026-04-28</v>
       </c>
       <c r="B74" t="str">
-        <v>15:00</v>
+        <v>12:00</v>
       </c>
       <c r="C74" t="str">
-        <v>src/core/scoringSystem.ts</v>
+        <v>AGENTS.md</v>
       </c>
       <c r="D74" t="str">
-        <v>BUG-020: Fix getBirthdayDaysUntil using date-fns differenceInCalendarDays — prevents wrong result on DST change days</v>
+        <v>נוצר AGENTS.md — תיעוד כל 8 agent הגדרות ופעולות מהפרויקט</v>
       </c>
       <c r="E74" t="str">
-        <v>bugfix</v>
+        <v>feature</v>
       </c>
       <c r="F74" t="str">
         <v>code_change</v>
@@ -2095,22 +2095,22 @@
         <v>2026-04-28</v>
       </c>
       <c r="B75" t="str">
-        <v>15:00</v>
+        <v>13:00</v>
       </c>
       <c r="C75" t="str">
-        <v>src/components/Navigation.tsx, src/screens/ContactDetailScreen.tsx, src/screens/HolidayDetailScreen.tsx, src/screens/DashboardScreen.tsx, src/screens/GroupsScreen.tsx, src/components/ui/Modal.tsx, src/screens/premium/ImportContactsScreen.tsx, src/components/ContactCard.tsx, src/index.css</v>
+        <v>BUG_REPORT.md</v>
       </c>
       <c r="D75" t="str">
-        <v>BUG-036 / FINDINGS 25A/20/23/28A/30B/60/66/67/69: aria-labels localized, urgency/frequency labels translated, group+dashboard cards converted to &lt;button&gt;, .btn:focus-visible ring added, setImporting in finally, decorative icon aria-hidden</v>
+        <v>עודכן בזמן אמת — BUG-022 סומן כ-fixed; נוספו BUG-030 עד BUG-035 עם תיאור מלא</v>
       </c>
       <c r="E75" t="str">
-        <v>bugfix</v>
+        <v>improvement</v>
       </c>
       <c r="F75" t="str">
         <v>code_change</v>
       </c>
       <c r="G75" t="str">
-        <v>Agent 1</v>
+        <v>Agent 4</v>
       </c>
       <c r="H75" t="str">
         <v>done</v>
@@ -2121,22 +2121,22 @@
         <v>2026-04-28</v>
       </c>
       <c r="B76" t="str">
-        <v>15:00</v>
+        <v>13:00</v>
       </c>
       <c r="C76" t="str">
-        <v>src/screens/SettingsScreen.tsx, src/screens/UpgradeScreen.tsx</v>
+        <v>agent_state/iteration_log.md</v>
       </c>
       <c r="D76" t="str">
-        <v>SECURITY: Wrap Danger Zone section and demo premium activation button in import.meta.env.DEV — both are completely tree-shaken from production builds by rolldown</v>
+        <v>נוסף iteration 11 — SettingsScreen/WhatsApp/communicationService/CalendarScreen/i18n/AGENTS.md</v>
       </c>
       <c r="E76" t="str">
-        <v>bugfix</v>
+        <v>improvement</v>
       </c>
       <c r="F76" t="str">
         <v>code_change</v>
       </c>
       <c r="G76" t="str">
-        <v>Agent 1</v>
+        <v>Agent 4</v>
       </c>
       <c r="H76" t="str">
         <v>done</v>
@@ -2147,13 +2147,13 @@
         <v>2026-04-28</v>
       </c>
       <c r="B77" t="str">
-        <v>16:00</v>
+        <v>13:30</v>
       </c>
       <c r="C77" t="str">
-        <v>src/utils/hebrewDateUtils.ts</v>
+        <v>agent_state/qa_status.json</v>
       </c>
       <c r="D77" t="str">
-        <v>Create hebrewDateUtils.ts — getHebrewDateStr(isoDate) converts Gregorian ISO date to Hebrew gematria string (e.g. ד׳ באייר תשפ״ו); uses local-time Date construction to avoid UTC timezone shifts</v>
+        <v>נוצר קובץ סטטוס QA עם 57 בדיקות — מצב נוכחי: 39 ✅ / 13 ❌ / 5 ⚠️</v>
       </c>
       <c r="E77" t="str">
         <v>feature</v>
@@ -2162,7 +2162,7 @@
         <v>code_change</v>
       </c>
       <c r="G77" t="str">
-        <v>Agent 1</v>
+        <v>Agent 4</v>
       </c>
       <c r="H77" t="str">
         <v>done</v>
@@ -2173,22 +2173,22 @@
         <v>2026-04-28</v>
       </c>
       <c r="B78" t="str">
-        <v>16:00</v>
+        <v>13:30</v>
       </c>
       <c r="C78" t="str">
-        <v>src/data/holidays.ts</v>
+        <v>scripts/make-qa-checklist.js</v>
       </c>
       <c r="D78" t="str">
-        <v>BUG-037: Yom HaAtzmaut 2026 was hardcoded as 2026-04-29 (wrong by 8 days); replaced with runtime computation via HebrewCalendar.getHolidaysForYearArray(5786, true) from @hebcal/core; correct date is 2026-04-21 (ד׳ באייר תשפ״ו)</v>
+        <v>נוצר סקריפט ליצירת NeverMiss_QA_Checklist.xlsx — קורא מ-qa_status.json; 57 בדיקות ב-8 קטגוריות</v>
       </c>
       <c r="E78" t="str">
-        <v>bugfix</v>
+        <v>feature</v>
       </c>
       <c r="F78" t="str">
         <v>code_change</v>
       </c>
       <c r="G78" t="str">
-        <v>Agent 1</v>
+        <v>Agent 4</v>
       </c>
       <c r="H78" t="str">
         <v>done</v>
@@ -2199,22 +2199,22 @@
         <v>2026-04-28</v>
       </c>
       <c r="B79" t="str">
-        <v>16:00</v>
+        <v>13:30</v>
       </c>
       <c r="C79" t="str">
-        <v>src/components/HolidayCard.tsx, src/screens/HolidayDetailScreen.tsx</v>
+        <v>package.json</v>
       </c>
       <c r="D79" t="str">
-        <v>Add Hebrew date badge (gematria format) to HolidayCard compact/full views and HolidayDetailScreen hero banner for all dateType === "hebrew" holidays</v>
+        <v>נוספו scripts: "changelog" → node scripts/make-changelog.js; "qa" → node scripts/make-qa-checklist.js</v>
       </c>
       <c r="E79" t="str">
-        <v>feature</v>
+        <v>improvement</v>
       </c>
       <c r="F79" t="str">
         <v>code_change</v>
       </c>
       <c r="G79" t="str">
-        <v>Agent 1</v>
+        <v>Agent 4</v>
       </c>
       <c r="H79" t="str">
         <v>done</v>
@@ -2225,22 +2225,22 @@
         <v>2026-04-28</v>
       </c>
       <c r="B80" t="str">
-        <v>17:00</v>
+        <v>13:30</v>
       </c>
       <c r="C80" t="str">
-        <v>src/screens/TermsScreen.tsx</v>
+        <v>CLAUDE.md</v>
       </c>
       <c r="D80" t="str">
-        <v>BUG-038: Terms of Service page always showed English. Root cause: SECTIONS array was at module scope — t() calls were made once on load, ignoring language changes. Fix: moved SECTIONS inside component; replaced all hardcoded strings with titleKey/bodyKey references + t() calls with as const + TranslationKey cast</v>
+        <v>עודכן Quality Gate — נוספו שלבים 6-9: append changelog_queue, עדכון qa_status.json, הרצת changelog ו-qa</v>
       </c>
       <c r="E80" t="str">
-        <v>bugfix</v>
+        <v>improvement</v>
       </c>
       <c r="F80" t="str">
         <v>code_change</v>
       </c>
       <c r="G80" t="str">
-        <v>Agent 1</v>
+        <v>Agent 4</v>
       </c>
       <c r="H80" t="str">
         <v>done</v>
@@ -2251,13 +2251,13 @@
         <v>2026-04-28</v>
       </c>
       <c r="B81" t="str">
-        <v>17:00</v>
+        <v>13:30</v>
       </c>
       <c r="C81" t="str">
-        <v>src/i18n/index.ts</v>
+        <v>NeverMiss_QA_Checklist.xlsx</v>
       </c>
       <c r="D81" t="str">
-        <v>Add 22 i18n keys for Terms of Service: terms_lastUpdated, terms_intro, terms_s1_title/body through terms_s10_title/body — full Hebrew translations for all 10 sections (EN + HE)</v>
+        <v>נוצר NeverMiss_QA_Checklist.xlsx — 57 בדיקות ב-8 קטגוריות; מעודכן אוטומטית אחרי כל phase</v>
       </c>
       <c r="E81" t="str">
         <v>feature</v>
@@ -2266,7 +2266,7 @@
         <v>code_change</v>
       </c>
       <c r="G81" t="str">
-        <v>Foundation-Agent</v>
+        <v>Agent 4</v>
       </c>
       <c r="H81" t="str">
         <v>done</v>
@@ -2277,22 +2277,22 @@
         <v>2026-04-28</v>
       </c>
       <c r="B82" t="str">
-        <v>18:00</v>
+        <v>15:00</v>
       </c>
       <c r="C82" t="str">
-        <v>src/services/analyticsService.ts</v>
+        <v>src/i18n/index.ts</v>
       </c>
       <c r="D82" t="str">
-        <v>Create local analytics service: getAnonymousUserId() generates/persists UUID in localStorage (nm_user_id); trackEvent(name, metadata?) stores up to 100 events FIFO in nm_events. No backend, no dashboard, zero side effects.</v>
+        <v>נוספו 20 מפתחות i18n: urgency_critical/high/medium/low, go_back, action_wish_birthday_today/days, action_wish_holiday_days, action_reconnect_days, action_checkin, action_followup, holiday_major, holiday_moreContacts — EN + HE</v>
       </c>
       <c r="E82" t="str">
-        <v>feature</v>
+        <v>improvement</v>
       </c>
       <c r="F82" t="str">
         <v>code_change</v>
       </c>
       <c r="G82" t="str">
-        <v>Agent 1</v>
+        <v>Foundation-Agent</v>
       </c>
       <c r="H82" t="str">
         <v>done</v>
@@ -2303,16 +2303,16 @@
         <v>2026-04-28</v>
       </c>
       <c r="B83" t="str">
-        <v>18:00</v>
+        <v>15:00</v>
       </c>
       <c r="C83" t="str">
-        <v>src/App.tsx, src/screens/ContactFormScreen.tsx, src/components/ChannelPicker.tsx, src/screens/premium/ImportContactsScreen.tsx</v>
+        <v>src/core/scoringSystem.ts</v>
       </c>
       <c r="D83" t="str">
-        <v>Add trackEvent calls for 4 events: app_open (AppShell mount), contact_created (new contact only), greeting_sent (with channel metadata), contacts_imported (with count metadata)</v>
+        <v>תוקן BUG-020 — getBirthdayDaysUntil עבר ל-differenceInCalendarDays מ-date-fns; מונע תוצאה שגויה בימי שינוי שעון</v>
       </c>
       <c r="E83" t="str">
-        <v>feature</v>
+        <v>bugfix</v>
       </c>
       <c r="F83" t="str">
         <v>code_change</v>
@@ -2329,13 +2329,13 @@
         <v>2026-04-28</v>
       </c>
       <c r="B84" t="str">
-        <v>19:00</v>
+        <v>15:00</v>
       </c>
       <c r="C84" t="str">
-        <v>src/screens/CalendarScreen.tsx</v>
+        <v>src/components/Navigation.tsx</v>
       </c>
       <c r="D84" t="str">
-        <v>BUG-039: Contact birthdays never appeared in calendar. Added birthdayMap useMemo — builds Map&lt;date-string, Contact[]&gt; for visible month using hebrewBirthday (priority) or birthday. Pink dot (#EC4899) added to cell dots row. Birthday panel section added below calendar showing contact name cards for selected day / full month.</v>
+        <v>תוקן FINDING 25A — PageHeader מוסיף useT(); aria-label="Go back" הוחלף ב-t('go_back') — עברית/אנגלית לפי שפה</v>
       </c>
       <c r="E84" t="str">
         <v>bugfix</v>
@@ -2355,16 +2355,16 @@
         <v>2026-04-28</v>
       </c>
       <c r="B85" t="str">
-        <v>19:00</v>
+        <v>15:00</v>
       </c>
       <c r="C85" t="str">
-        <v>src/types/index.ts</v>
+        <v>src/screens/ContactDetailScreen.tsx</v>
       </c>
       <c r="D85" t="str">
-        <v>FEATURE: Add optional hebrewBirthday?: string field to Contact interface — stored as "DD-MM" (Hebrew day-month, year-agnostic). Additive only; does not affect existing birthday field.</v>
+        <v>תוקן FINDING 20/23 — urgencyLevel מוצג עם t(); interactionFrequency עם t(); translatedActionLabel IIFE לפי action.type</v>
       </c>
       <c r="E85" t="str">
-        <v>feature</v>
+        <v>bugfix</v>
       </c>
       <c r="F85" t="str">
         <v>code_change</v>
@@ -2381,16 +2381,16 @@
         <v>2026-04-28</v>
       </c>
       <c r="B86" t="str">
-        <v>19:00</v>
+        <v>15:00</v>
       </c>
       <c r="C86" t="str">
-        <v>src/utils/hebrewDateUtils.ts</v>
+        <v>src/screens/HolidayDetailScreen.tsx</v>
       </c>
       <c r="D86" t="str">
-        <v>FEATURE: Add hebrewBirthdayToGregorianInCalendarYear(hebrewBirthday, gregorianYear) — converts "DD-MM" Hebrew date to Gregorian Date for a given year; tries approxHYear and approxHYear+1 to handle year boundary; returns null for invalid combos (e.g. Adar II in non-leap year)</v>
+        <v>תוקן FINDING 28A — ★ Major הוחלף ב-t('holiday_major'); +N more contacts הוחלף ב-t('holiday_moreContacts', { n })</v>
       </c>
       <c r="E86" t="str">
-        <v>feature</v>
+        <v>bugfix</v>
       </c>
       <c r="F86" t="str">
         <v>code_change</v>
@@ -2407,16 +2407,16 @@
         <v>2026-04-28</v>
       </c>
       <c r="B87" t="str">
-        <v>19:00</v>
+        <v>15:00</v>
       </c>
       <c r="C87" t="str">
-        <v>src/screens/ContactFormScreen.tsx</v>
+        <v>src/screens/DashboardScreen.tsx</v>
       </c>
       <c r="D87" t="str">
-        <v>FEATURE: Add Hebrew Birthday UI in premium section — shown for Judaism contacts or when hebrewBirthday already set. Two dropdowns (day 1–30, Hebrew month 1–12 with names). Derives day/month from form.hebrewBirthday via useMemo. Clear button removes the field. Saved as "DD-MM" string.</v>
+        <v>תוקן FINDING 67 — Today highlight cards (holiday + birthday) הומרו מ-div ל-&lt;button type=button&gt; עם w-full text-left</v>
       </c>
       <c r="E87" t="str">
-        <v>feature</v>
+        <v>bugfix</v>
       </c>
       <c r="F87" t="str">
         <v>code_change</v>
@@ -2433,22 +2433,22 @@
         <v>2026-04-28</v>
       </c>
       <c r="B88" t="str">
-        <v>19:00</v>
+        <v>15:00</v>
       </c>
       <c r="C88" t="str">
-        <v>src/i18n/index.ts</v>
+        <v>src/screens/GroupsScreen.tsx</v>
       </c>
       <c r="D88" t="str">
-        <v>Add 7 i18n keys (EN + HE): calendar_birthdays, calendar_birthdayLabel, calendar_birthdaysOn, contactForm_hebrewBirthday, contactForm_hebrewBirthdayDay, contactForm_hebrewBirthdayMonth, contactForm_hebrewBirthdayClear</v>
+        <v>תוקן FINDING 67 — Group card הומר מ-div ל-&lt;button type=button&gt; עם w-full text-left</v>
       </c>
       <c r="E88" t="str">
-        <v>feature</v>
+        <v>bugfix</v>
       </c>
       <c r="F88" t="str">
         <v>code_change</v>
       </c>
       <c r="G88" t="str">
-        <v>Foundation-Agent</v>
+        <v>Agent 1</v>
       </c>
       <c r="H88" t="str">
         <v>done</v>
@@ -2459,16 +2459,16 @@
         <v>2026-04-28</v>
       </c>
       <c r="B89" t="str">
-        <v>20:00</v>
+        <v>15:00</v>
       </c>
       <c r="C89" t="str">
-        <v>src/screens/GreetingEditorScreen.tsx</v>
+        <v>src/index.css</v>
       </c>
       <c r="D89" t="str">
-        <v>BL-015: Replace hardcoded tier desc strings with i18n keys (greeting_tier_*_desc). Signature placeholder via t('greeting_signature_placeholder'). BL-017: aria-label on Regenerate and Copy icon buttons. BL-018: aria-expanded on Advanced tone + Signature toggle buttons. aria-hidden on decorative icons.</v>
+        <v>תוקן FINDING 69 — נוסף .btn:focus-visible { outline: 2px solid var(--color-primary) }; נוסף @media (min-width: 768px) שמסיר max-width:480px על דסקטופ</v>
       </c>
       <c r="E89" t="str">
-        <v>improvement</v>
+        <v>bugfix</v>
       </c>
       <c r="F89" t="str">
         <v>code_change</v>
@@ -2485,22 +2485,22 @@
         <v>2026-04-28</v>
       </c>
       <c r="B90" t="str">
-        <v>20:00</v>
+        <v>15:00</v>
       </c>
       <c r="C90" t="str">
-        <v>src/i18n/index.ts</v>
+        <v>src/components/ui/Modal.tsx</v>
       </c>
       <c r="D90" t="str">
-        <v>BL-015: Add 4 i18n keys (EN + HE): greeting_tier_casual_desc, greeting_tier_professional_desc, greeting_tier_vip_desc, greeting_signature_placeholder</v>
+        <v>תוקן FINDING 30B — Modal מייבא useT(); aria-label='Close' הוחלף ב-t('close') — עברית/אנגלית לפי שפה</v>
       </c>
       <c r="E90" t="str">
-        <v>improvement</v>
+        <v>bugfix</v>
       </c>
       <c r="F90" t="str">
         <v>code_change</v>
       </c>
       <c r="G90" t="str">
-        <v>Foundation-Agent</v>
+        <v>Agent 1</v>
       </c>
       <c r="H90" t="str">
         <v>done</v>
@@ -2511,16 +2511,16 @@
         <v>2026-04-28</v>
       </c>
       <c r="B91" t="str">
-        <v>20:00</v>
+        <v>15:00</v>
       </c>
       <c r="C91" t="str">
-        <v>src/components/ContactCard.tsx</v>
+        <v>src/screens/premium/ImportContactsScreen.tsx</v>
       </c>
       <c r="D91" t="str">
-        <v>BL-016: Add ACTION_KEY Record&lt;SuggestedActionType, TranslationKey&gt; map. Use useT() + t(ACTION_KEY[...]) to display action label in current language instead of raw English label string.</v>
+        <v>תוקן FINDING 60 — setImporting(false) הועבר ל-finally block; מניעת Import button תקוע במצב loading</v>
       </c>
       <c r="E91" t="str">
-        <v>improvement</v>
+        <v>bugfix</v>
       </c>
       <c r="F91" t="str">
         <v>code_change</v>
@@ -2537,16 +2537,16 @@
         <v>2026-04-28</v>
       </c>
       <c r="B92" t="str">
-        <v>20:00</v>
+        <v>15:00</v>
       </c>
       <c r="C92" t="str">
-        <v>src/screens/ContactDetailScreen.tsx</v>
+        <v>src/components/ContactCard.tsx</v>
       </c>
       <c r="D92" t="str">
-        <v>BL-017: aria-label on Edit icon button via t('contactForm_edit'). BL-041: Add celebration feedback on Mark as Contacted — 6 emoji particle burst (.animate-particle with --tx/--ty CSS vars), Web Audio oscillator ping (880→1200Hz ramp, 0.4s), haptic navigator.vibrate(40). Respects prefers-reduced-motion. useState celebrating moved before early return to comply with hooks rules.</v>
+        <v>תוקן FINDING 66 — aria-hidden="true" נוסף ל-Crown ו-Building2 icons; אלמנטים דקורטיביים מוסתרים מקורא מסך</v>
       </c>
       <c r="E92" t="str">
-        <v>improvement</v>
+        <v>bugfix</v>
       </c>
       <c r="F92" t="str">
         <v>code_change</v>
@@ -2563,13 +2563,13 @@
         <v>2026-04-28</v>
       </c>
       <c r="B93" t="str">
-        <v>20:00</v>
+        <v>15:00</v>
       </c>
       <c r="C93" t="str">
-        <v>src/index.css</v>
+        <v>agent_state/qa_status.json</v>
       </c>
       <c r="D93" t="str">
-        <v>BL-041: Add @keyframes particleBurst (translate + scale to 0 + opacity fade driven by --tx/--ty CSS custom properties) and .animate-particle utility class (1.2s ease-out forwards).</v>
+        <v>עודכן — T05/T07/T08/T09/T10/T39/T40/T41/T42/T45/T46/T48 סומנו כ-✅; 8 בדיקות תוקנו ב-iteration 12</v>
       </c>
       <c r="E93" t="str">
         <v>improvement</v>
@@ -2578,7 +2578,7 @@
         <v>code_change</v>
       </c>
       <c r="G93" t="str">
-        <v>Agent 1</v>
+        <v>Agent 4</v>
       </c>
       <c r="H93" t="str">
         <v>done</v>
@@ -2589,22 +2589,22 @@
         <v>2026-04-28</v>
       </c>
       <c r="B94" t="str">
-        <v>20:30</v>
+        <v>16:00</v>
       </c>
       <c r="C94" t="str">
-        <v>agent_state/iteration_log.md</v>
+        <v>src/utils/hebrewDateUtils.ts</v>
       </c>
       <c r="D94" t="str">
-        <v>BUG-040 fix: reconstructed iterations 13–17 from changelog_queue.json. All 5 entries appended: iter 13 (Hebrew date display + BUG-037), iter 14 (BUG-038 Terms fix), iter 15 (analytics foundation), iter 16 (BUG-039 birthday calendar + Hebrew birthday feature), iter 17 (BL-015/016/017/018/041 i18n + accessibility + celebration). Agent 2/3 columns marked TBD where source files have no entries. Log is now continuous 0–17.</v>
+        <v>נוצר util חדש — getHebrewDateStr() מחזיר תאריך עברי בגימטריה: ד׳ באייר תשפ״ו; משתמש ב-HDate + gematriya מ-@hebcal/core</v>
       </c>
       <c r="E94" t="str">
-        <v>bugfix</v>
+        <v>feature</v>
       </c>
       <c r="F94" t="str">
         <v>code_change</v>
       </c>
       <c r="G94" t="str">
-        <v>Agent 4</v>
+        <v>Agent 1</v>
       </c>
       <c r="H94" t="str">
         <v>done</v>
@@ -2615,13 +2615,13 @@
         <v>2026-04-28</v>
       </c>
       <c r="B95" t="str">
-        <v>20:30</v>
+        <v>16:00</v>
       </c>
       <c r="C95" t="str">
-        <v>BUG_REPORT.md</v>
+        <v>src/data/holidays.ts</v>
       </c>
       <c r="D95" t="str">
-        <v>Added BUG-040 entry: iteration_log.md missing iterations 13–17. Marked fixed.</v>
+        <v>תוקן BUG-037 — יום העצמאות 2026 היה מקודד כ-2026-04-29 (שגוי); כעת מחושב בזמן ריצה ע"י HebrewCalendar.getHolidaysForYearArray(5786) מ-@hebcal/core; התוצאה: 2026-04-21 (ד׳ באייר תשפ"ו)</v>
       </c>
       <c r="E95" t="str">
         <v>bugfix</v>
@@ -2630,7 +2630,7 @@
         <v>code_change</v>
       </c>
       <c r="G95" t="str">
-        <v>Agent 4</v>
+        <v>Agent 1</v>
       </c>
       <c r="H95" t="str">
         <v>done</v>
@@ -2641,13 +2641,13 @@
         <v>2026-04-28</v>
       </c>
       <c r="B96" t="str">
-        <v>21:00</v>
+        <v>16:00</v>
       </c>
       <c r="C96" t="str">
-        <v>src/App.tsx</v>
+        <v>src/components/HolidayCard.tsx</v>
       </c>
       <c r="D96" t="str">
-        <v>BL-019: Convert 13 screens to React.lazy (CalendarScreen, HolidayDetailScreen, ContactsScreen, ContactDetailScreen, ContactFormScreen, GreetingEditorScreen, GroupsScreen, SettingsScreen, UpgradeScreen, AboutScreen, PrivacyScreen, TermsScreen, WhatsNewScreen). Move Suspense fallback into WithNav so BottomNav stays visible during load. Remove now-redundant inner Suspense from 3 premium routes. Main bundle: 435 kB → 285 kB raw (-150 kB), 130 kB → 93 kB gzip (-37 kB).</v>
+        <v>נוסף תצוגת תאריך עברי לחגים יהודיים (dateType === 'hebrew') — כרטיס קומפקטי ומלא; פורמט: ד׳ באייר תשפ״ו</v>
       </c>
       <c r="E96" t="str">
         <v>improvement</v>
@@ -2667,13 +2667,25 @@
         <v>2026-04-28</v>
       </c>
       <c r="B97" t="str">
-        <v>21:00</v>
+        <v>16:00</v>
       </c>
       <c r="C97" t="str">
-        <v>src/core/scoringSystem.ts</v>
+        <v>src/screens/HolidayDetailScreen.tsx</v>
       </c>
       <c r="D97" t="str">
-        <v>BL-020: Add module-level scoreCache Map&lt;string, RelationshipScore&gt; keyed by `contact.id|contact.updatedAt`. calculateRelationshipScore checks cache on entry and sets result before return. Eliminates redundant scoring for unchanged contacts on every render. Stale results impossible since updatedAt is always stamped on mutation.</v>
+        <v>נוסף badge תאריך עברי בבאנר הראשי של מסך פרטי החג; מוצג רק לחגים עם dateType === 'hebrew'</v>
+      </c>
+      <c r="E97" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F97" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G97" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H97" t="str">
+        <v>done</v>
       </c>
     </row>
     <row r="98">
@@ -2681,22 +2693,22 @@
         <v>2026-04-28</v>
       </c>
       <c r="B98" t="str">
-        <v>22:00</v>
+        <v>17:00</v>
       </c>
       <c r="C98" t="str">
-        <v>src/types/index.ts</v>
+        <v>src/screens/TermsScreen.tsx</v>
       </c>
       <c r="D98" t="str">
-        <v>BL-026: Add CelebrationType union type (Jewish|Christian|Muslim|Druze|Secular); add optional celebrationType field to Contact interface</v>
+        <v>תוקן BUG-038 — מסך תנאי שירות הציג תמיד אנגלית; SECTIONS הועבר לתוך הקומפוננטה עם t(); כל 10 כותרות + גופי סעיפים + כותרת הגיבור + תאריך עדכון + טקסט מבוא כעת דינמיים</v>
       </c>
       <c r="E98" t="str">
-        <v>feature</v>
+        <v>bugfix</v>
       </c>
       <c r="F98" t="str">
         <v>code_change</v>
       </c>
       <c r="G98" t="str">
-        <v>Foundation Agent</v>
+        <v>Agent 1</v>
       </c>
       <c r="H98" t="str">
         <v>done</v>
@@ -2707,22 +2719,22 @@
         <v>2026-04-28</v>
       </c>
       <c r="B99" t="str">
-        <v>22:00</v>
+        <v>17:00</v>
       </c>
       <c r="C99" t="str">
         <v>src/i18n/index.ts</v>
       </c>
       <c r="D99" t="str">
-        <v>BL-026+BL-023+BL-030: Add 34 i18n keys — celebrationType_* (5 values EN+HE), contactForm_celebrationType, notif_overdue/notif_overdue_body, 14 deviceContacts_* keys, premium_feat_device_contacts — all in EN and HE</v>
+        <v>נוספו 22 מפתחות i18n לתנאי שירות: terms_lastUpdated, terms_intro, terms_s1_title/body עד terms_s10_title/body — בעברית ובאנגלית</v>
       </c>
       <c r="E99" t="str">
-        <v>improvement</v>
+        <v>feature</v>
       </c>
       <c r="F99" t="str">
         <v>code_change</v>
       </c>
       <c r="G99" t="str">
-        <v>Foundation Agent</v>
+        <v>Foundation-Agent</v>
       </c>
       <c r="H99" t="str">
         <v>done</v>
@@ -2733,13 +2745,13 @@
         <v>2026-04-28</v>
       </c>
       <c r="B100" t="str">
-        <v>22:00</v>
+        <v>18:00</v>
       </c>
       <c r="C100" t="str">
-        <v>src/core/scoringSystem.ts</v>
+        <v>src/services/analyticsService.ts</v>
       </c>
       <c r="D100" t="str">
-        <v>BL-026: Add CELEBRATION_TO_RELIGION map; update getUpcomingHolidaysForContact to prefer celebrationType over religion when set, falling back to religion for existing contacts</v>
+        <v>נוסף שירות analytics מקומי: getAnonymousUserId() (localStorage nm_user_id), trackEvent(name, metadata?) — שומר עד 100 אירועים ב-FIFO ב-nm_events; ללא backend</v>
       </c>
       <c r="E100" t="str">
         <v>feature</v>
@@ -2759,16 +2771,16 @@
         <v>2026-04-28</v>
       </c>
       <c r="B101" t="str">
-        <v>22:00</v>
+        <v>18:00</v>
       </c>
       <c r="C101" t="str">
-        <v>src/screens/ContactFormScreen.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="D101" t="str">
-        <v>BL-026: Add celebrationType Select dropdown to Cultural &amp; Language section; wire into form state and handleSave; import CelebrationType type</v>
+        <v>נוסף מעקב app_open ב-AppShell useEffect — מופעל פעם אחת בטעינת האפליקציה</v>
       </c>
       <c r="E101" t="str">
-        <v>feature</v>
+        <v>improvement</v>
       </c>
       <c r="F101" t="str">
         <v>code_change</v>
@@ -2785,16 +2797,16 @@
         <v>2026-04-28</v>
       </c>
       <c r="B102" t="str">
-        <v>22:00</v>
+        <v>18:00</v>
       </c>
       <c r="C102" t="str">
-        <v>src/services/notificationService.ts</v>
+        <v>src/screens/ContactFormScreen.tsx</v>
       </c>
       <c r="D102" t="str">
-        <v>BL-023: Add overdue-contact reminder — fires when daysSince &gt;= 45 days with no upcoming birthday within 7 days; dedup via existing nm_notif_sent localStorage mechanism</v>
+        <v>נוסף מעקב contact_created לאחר addContact() ביצירת איש קשר חדש בלבד (לא בעדכון)</v>
       </c>
       <c r="E102" t="str">
-        <v>feature</v>
+        <v>improvement</v>
       </c>
       <c r="F102" t="str">
         <v>code_change</v>
@@ -2811,16 +2823,16 @@
         <v>2026-04-28</v>
       </c>
       <c r="B103" t="str">
-        <v>22:00</v>
+        <v>18:00</v>
       </c>
       <c r="C103" t="str">
-        <v>src/screens/DeviceContactsScreen.tsx</v>
+        <v>src/components/ChannelPicker.tsx</v>
       </c>
       <c r="D103" t="str">
-        <v>BL-030: New screen — consent → permission request → device contact list with checkboxes → import with phone dedup. Capacitor.isNativePlatform() guard shows graceful web-only message. Imports @capacitor-community/contacts. Premium-gated via App.tsx route.</v>
+        <v>נוסף מעקב greeting_sent עם metadata { channel } בכל שליחת ברכה דרך כל ערוץ</v>
       </c>
       <c r="E103" t="str">
-        <v>feature</v>
+        <v>improvement</v>
       </c>
       <c r="F103" t="str">
         <v>code_change</v>
@@ -2837,16 +2849,16 @@
         <v>2026-04-28</v>
       </c>
       <c r="B104" t="str">
-        <v>22:00</v>
+        <v>18:00</v>
       </c>
       <c r="C104" t="str">
-        <v>src/App.tsx</v>
+        <v>src/screens/premium/ImportContactsScreen.tsx</v>
       </c>
       <c r="D104" t="str">
-        <v>BL-030: Add DeviceContactsScreen lazy import; add route /device-contacts with Premium gate (isPremium ? DeviceContactsScreen : UpgradeScreen)</v>
+        <v>נוסף מעקב contacts_imported עם metadata { count } לאחר ייבוא אנשי קשר מוצלח</v>
       </c>
       <c r="E104" t="str">
-        <v>feature</v>
+        <v>improvement</v>
       </c>
       <c r="F104" t="str">
         <v>code_change</v>
@@ -2863,16 +2875,16 @@
         <v>2026-04-28</v>
       </c>
       <c r="B105" t="str">
-        <v>22:00</v>
+        <v>19:00</v>
       </c>
       <c r="C105" t="str">
-        <v>src/screens/premium/ImportContactsScreen.tsx</v>
+        <v>src/screens/CalendarScreen.tsx</v>
       </c>
       <c r="D105" t="str">
-        <v>BL-030: Add "Import from Phone" shortcut card at top of Import screen; navigates to /device-contacts</v>
+        <v>תוקן BUG-039 — ימי הולדת לא הוצגו בלוח השנה; נוסף birthdayMap useMemo; נוספת נקודה ורודה (#EC4899) על תאים עם ימי הולדת; נוסף פאנל 'ימי הולדת' עם שמות אנשי קשר</v>
       </c>
       <c r="E105" t="str">
-        <v>improvement</v>
+        <v>bugfix</v>
       </c>
       <c r="F105" t="str">
         <v>code_change</v>
@@ -2889,16 +2901,16 @@
         <v>2026-04-28</v>
       </c>
       <c r="B106" t="str">
-        <v>23:00</v>
+        <v>19:00</v>
       </c>
       <c r="C106" t="str">
-        <v>src/screens/CalendarScreen.tsx</v>
+        <v>src/types/index.ts</v>
       </c>
       <c r="D106" t="str">
-        <v>BUG-043: Fix multi-day holidays only showing dot on first day. Replace isSameDay check with numeric YYYYMMDD range [startNum, endNum] in getHolidaysForDay. Fix monthly list to show holidays overlapping the visible month (not just holidays that start in the month). Remove unused isSameMonth import.</v>
+        <v>נוסף שדה hebrewBirthday?: string לממשק Contact — פורמט 'DD-MM' (יום-חודש עברי ללא שנה)</v>
       </c>
       <c r="E106" t="str">
-        <v>bugfix</v>
+        <v>improvement</v>
       </c>
       <c r="F106" t="str">
         <v>code_change</v>
@@ -2915,16 +2927,16 @@
         <v>2026-04-28</v>
       </c>
       <c r="B107" t="str">
-        <v>23:00</v>
+        <v>19:00</v>
       </c>
       <c r="C107" t="str">
-        <v>src/data/holidays.ts</v>
+        <v>src/utils/hebrewDateUtils.ts</v>
       </c>
       <c r="D107" t="str">
-        <v>BUG-044: Add missing sukkot-2026 entry (Sep 25 – Oct 2, 2026 / 15–22 Tishrei 5787). Covers full festival including Hoshana Rabbah and Shemini Atzeret / Simchat Torah. Matches existing sukkot-2025 pattern.</v>
+        <v>נוספה פונקציה hebrewBirthdayToGregorianInCalendarYear() — ממירה 'DD-MM' עברי לתאריך גרגוריאני בשנה נתונה; בודקת שתי שנות היברו סמוכות</v>
       </c>
       <c r="E107" t="str">
-        <v>bugfix</v>
+        <v>improvement</v>
       </c>
       <c r="F107" t="str">
         <v>code_change</v>
@@ -2941,13 +2953,13 @@
         <v>2026-04-28</v>
       </c>
       <c r="B108" t="str">
-        <v>23:30</v>
+        <v>19:00</v>
       </c>
       <c r="C108" t="str">
-        <v>src/screens/ContactDetailScreen.tsx</v>
+        <v>src/screens/ContactFormScreen.tsx</v>
       </c>
       <c r="D108" t="str">
-        <v>BL-045: Replace harsh oscillator with C5/E5/G5 major triad arpeggio (3 sine waves, ~0.75s, pleasant chord). Expand particles from 6 to 10, size text-xl (was text-base), wider spread ±85px h / ±110px v. Animation delay stagger 50ms per particle (was 40ms). State clear timeout 1600ms.</v>
+        <v>נוסף UI לתאריך לידה עברי בסעיף פרמיום — מוצג לאנשי קשר יהודים או כשהשדה כבר מוגדר; שני dropdowns (יום + חודש עברי) + כפתור ניקוי</v>
       </c>
       <c r="E108" t="str">
         <v>improvement</v>
@@ -2967,13 +2979,13 @@
         <v>2026-04-28</v>
       </c>
       <c r="B109" t="str">
-        <v>23:30</v>
+        <v>19:00</v>
       </c>
       <c r="C109" t="str">
-        <v>src/index.css</v>
+        <v>src/i18n/index.ts</v>
       </c>
       <c r="D109" t="str">
-        <v>BL-045: Update particleBurst keyframe — scale-pop effect: 0.4 → 1.6 → 0 across 0/18%/100% keyframe stops, giving a visible "pop then fly" motion. Animation class duration 1.2s → 1.4s.</v>
+        <v>נוספו 7 מפתחות i18n: calendar_birthdays, calendar_birthdayLabel, calendar_birthdaysOn, contactForm_hebrewBirthday, contactForm_hebrewBirthdayDay, contactForm_hebrewBirthdayMonth, contactForm_hebrewBirthdayClear — EN + HE</v>
       </c>
       <c r="E109" t="str">
         <v>improvement</v>
@@ -2982,7 +2994,7 @@
         <v>code_change</v>
       </c>
       <c r="G109" t="str">
-        <v>Agent 1</v>
+        <v>Foundation-Agent</v>
       </c>
       <c r="H109" t="str">
         <v>done</v>
@@ -2990,19 +3002,19 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-28</v>
       </c>
       <c r="B110" t="str">
-        <v>00:00</v>
+        <v>20:00</v>
       </c>
       <c r="C110" t="str">
-        <v>src/services/exportService.ts</v>
+        <v>src/screens/GreetingEditorScreen.tsx</v>
       </c>
       <c r="D110" t="str">
-        <v>BL-025 (Sprint 4): New exportContactsToCSV() using PapaParse. Exports all Contact fields to CSV with UTF-8 BOM for Hebrew Excel compatibility. Downloads as nevermiss-contacts-YYYY-MM-DD.csv.</v>
+        <v>BL-015: החלפת תיאורי tier קשיחים ב-i18n (greeting_tier_*_desc); placeholder חתימה דרך t('greeting_signature_placeholder'); aria-label על כפתורי Regenerate ו-Copy; aria-expanded על toggles</v>
       </c>
       <c r="E110" t="str">
-        <v>feature</v>
+        <v>improvement</v>
       </c>
       <c r="F110" t="str">
         <v>code_change</v>
@@ -3016,19 +3028,19 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-28</v>
       </c>
       <c r="B111" t="str">
-        <v>00:00</v>
+        <v>20:00</v>
       </c>
       <c r="C111" t="str">
-        <v>src/screens/SettingsScreen.tsx</v>
+        <v>src/components/ContactCard.tsx</v>
       </c>
       <c r="D111" t="str">
-        <v>BL-025 (Sprint 4): Added Export Contacts to CSV button in Premium Features card. exportDone state shows success feedback for 2.5s.</v>
+        <v>BL-016: תרגום תיאור פעולה מוצעת — ACTION_KEY map מ-SuggestedActionType ל-TranslationKey; שימוש ב-t() במקום label גולמי</v>
       </c>
       <c r="E111" t="str">
-        <v>feature</v>
+        <v>improvement</v>
       </c>
       <c r="F111" t="str">
         <v>code_change</v>
@@ -3042,19 +3054,19 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-28</v>
       </c>
       <c r="B112" t="str">
-        <v>00:00</v>
+        <v>20:00</v>
       </c>
       <c r="C112" t="str">
-        <v>src/i18n/index.ts</v>
+        <v>src/screens/ContactDetailScreen.tsx</v>
       </c>
       <c r="D112" t="str">
-        <v>BL-025 (Sprint 4): Added i18n keys settings_exportContacts + settings_exportSuccess in EN+HE.</v>
+        <v>BL-017/018: aria-label על כפתור עריכה; BL-041: אנימציית פרטיקלים (6 אמוג'ים), צליל Web Audio (880→1200Hz), haptic navigator.vibrate(40) בלחיצה על 'סימון כיצרנו קשר'; תומך prefers-reduced-motion</v>
       </c>
       <c r="E112" t="str">
-        <v>feature</v>
+        <v>improvement</v>
       </c>
       <c r="F112" t="str">
         <v>code_change</v>
@@ -3068,16 +3080,16 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-28</v>
       </c>
       <c r="B113" t="str">
-        <v>00:30</v>
+        <v>20:00</v>
       </c>
       <c r="C113" t="str">
-        <v>src/components/Navigation.tsx</v>
+        <v>src/i18n/index.ts</v>
       </c>
       <c r="D113" t="str">
-        <v>BL-029 (Sprint 4) WCAG 2.5.5: Back button in PageHeader changed to min-w/h-[48px] flex items-center justify-center — 48×48px minimum tap target.</v>
+        <v>BL-015: נוספו מפתחות greeting_tier_casual_desc, greeting_tier_professional_desc, greeting_tier_vip_desc, greeting_signature_placeholder — EN + HE</v>
       </c>
       <c r="E113" t="str">
         <v>improvement</v>
@@ -3086,7 +3098,7 @@
         <v>code_change</v>
       </c>
       <c r="G113" t="str">
-        <v>Agent 1</v>
+        <v>Foundation-Agent</v>
       </c>
       <c r="H113" t="str">
         <v>done</v>
@@ -3094,16 +3106,16 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-28</v>
       </c>
       <c r="B114" t="str">
-        <v>00:30</v>
+        <v>20:00</v>
       </c>
       <c r="C114" t="str">
-        <v>src/screens/ContactFormScreen.tsx</v>
+        <v>src/index.css</v>
       </c>
       <c r="D114" t="str">
-        <v>BL-029 (Sprint 4) WCAG 2.5.5: Delete icon button in ContactForm PageHeader changed to min-w/h-[48px] tap target.</v>
+        <v>BL-041: נוספה keyframe particleBurst ו-class .animate-particle לאנימציית פרטיקלים בחגיגה</v>
       </c>
       <c r="E114" t="str">
         <v>improvement</v>
@@ -3120,25 +3132,25 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-28</v>
       </c>
       <c r="B115" t="str">
-        <v>00:30</v>
+        <v>20:30</v>
       </c>
       <c r="C115" t="str">
-        <v>src/screens/GroupsScreen.tsx</v>
+        <v>agent_state/iteration_log.md</v>
       </c>
       <c r="D115" t="str">
-        <v>BL-029 (Sprint 4) WCAG 2.5.5: Edit and Delete icon buttons on group cards changed to min-w/h-[48px] tap targets.</v>
+        <v>תוקן BUG-040 — iteration_log.md חסר iterations 13–17; שוחזרו מ-changelog_queue.json; עמודות Agent 2/3 סומנו TBD היכן שאין רשומות; הלוג רציף 0–17</v>
       </c>
       <c r="E115" t="str">
-        <v>improvement</v>
+        <v>bugfix</v>
       </c>
       <c r="F115" t="str">
         <v>code_change</v>
       </c>
       <c r="G115" t="str">
-        <v>Agent 1</v>
+        <v>Agent 4</v>
       </c>
       <c r="H115" t="str">
         <v>done</v>
@@ -3146,16 +3158,16 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-28</v>
       </c>
       <c r="B116" t="str">
-        <v>00:30</v>
+        <v>20:30</v>
       </c>
       <c r="C116" t="str">
-        <v>src/screens/GreetingEditorScreen.tsx</v>
+        <v>BUG_REPORT.md</v>
       </c>
       <c r="D116" t="str">
-        <v>BL-029 (Sprint 4) WCAG 2.5.5: Regenerate and Copy icon buttons changed to min-w/h-[48px] tap targets.</v>
+        <v>נוסף BUG-040 — iteration_log.md חסר iterations 13–17; סומן כ-fixed</v>
       </c>
       <c r="E116" t="str">
         <v>improvement</v>
@@ -3164,7 +3176,7 @@
         <v>code_change</v>
       </c>
       <c r="G116" t="str">
-        <v>Agent 1</v>
+        <v>Agent 4</v>
       </c>
       <c r="H116" t="str">
         <v>done</v>
@@ -3172,16 +3184,16 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-28</v>
       </c>
       <c r="B117" t="str">
-        <v>00:30</v>
+        <v>21:00</v>
       </c>
       <c r="C117" t="str">
-        <v>src/components/ui/Modal.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="D117" t="str">
-        <v>BL-029 (Sprint 4) WCAG 2.5.5: Close (X) button in Modal header changed to min-w/h-[48px] tap target.</v>
+        <v>BL-019: 13 מסכים הומרו ל-React.lazy; Suspense נוסף בתוך WithNav; inner Suspense הוסר מנתיבי premium; bundle ראשי ירד מ-435kB ל-285kB</v>
       </c>
       <c r="E117" t="str">
         <v>improvement</v>
@@ -3198,16 +3210,16 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-28</v>
       </c>
       <c r="B118" t="str">
-        <v>00:30</v>
+        <v>21:00</v>
       </c>
       <c r="C118" t="str">
-        <v>src/screens/ContactDetailScreen.tsx</v>
+        <v>src/core/scoringSystem.ts</v>
       </c>
       <c r="D118" t="str">
-        <v>BL-029 (Sprint 4) WCAG 2.5.5: Edit icon button in ContactDetail PageHeader changed to min-w/h-[48px] tap target.</v>
+        <v>BL-020: נוסף Map cache (scoreCache) ברמת המודול; מפתח: id|updatedAt; תוצאה נשמרת ומוחזרת מהמטמון לאנשי קשר שלא השתנו</v>
       </c>
       <c r="E118" t="str">
         <v>improvement</v>
@@ -3224,16 +3236,16 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-28</v>
       </c>
       <c r="B119" t="str">
-        <v>00:30</v>
+        <v>22:00</v>
       </c>
       <c r="C119" t="str">
-        <v>src/screens/HolidayDetailScreen.tsx</v>
+        <v>src/types/index.ts</v>
       </c>
       <c r="D119" t="str">
-        <v>BL-029 (Sprint 4) WCAG 2.5.5: Copy greeting icon button changed to min-w/h-[48px] tap target.</v>
+        <v>BL-026: נוסף סוג CelebrationType (Jewish/Christian/Muslim/Druze/Secular) + שדה celebrationType? על Contact interface</v>
       </c>
       <c r="E119" t="str">
         <v>improvement</v>
@@ -3242,7 +3254,7 @@
         <v>code_change</v>
       </c>
       <c r="G119" t="str">
-        <v>Agent 1</v>
+        <v>FoundationAgent</v>
       </c>
       <c r="H119" t="str">
         <v>done</v>
@@ -3250,16 +3262,16 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-28</v>
       </c>
       <c r="B120" t="str">
-        <v>00:30</v>
+        <v>22:00</v>
       </c>
       <c r="C120" t="str">
-        <v>src/screens/premium/BirthdayGreetingEditorScreen.tsx</v>
+        <v>src/i18n/index.ts</v>
       </c>
       <c r="D120" t="str">
-        <v>BL-029 (Sprint 4) WCAG 2.5.5: Regenerate and Copy icon buttons in BirthdayGreetingEditor changed to min-w/h-[48px] tap targets.</v>
+        <v>BL-026+BL-023+BL-030: נוספו 34 מפתחות i18n — celebrationType_*, contactForm_celebrationType, notif_overdue/body, deviceContacts_*, premium_feat_device_contacts — EN+HE</v>
       </c>
       <c r="E120" t="str">
         <v>improvement</v>
@@ -3268,7 +3280,7 @@
         <v>code_change</v>
       </c>
       <c r="G120" t="str">
-        <v>Agent 1</v>
+        <v>FoundationAgent</v>
       </c>
       <c r="H120" t="str">
         <v>done</v>
@@ -3276,19 +3288,19 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-28</v>
       </c>
       <c r="B121" t="str">
-        <v>01:00</v>
+        <v>22:00</v>
       </c>
       <c r="C121" t="str">
-        <v>src/services/hapticService.ts</v>
+        <v>src/core/scoringSystem.ts</v>
       </c>
       <c r="D121" t="str">
-        <v>BL-024 (Sprint 4): New hapticService with hapticLight/Medium/Success/Error. Uses Capacitor.isNativePlatform() guard — graceful no-op in browser. ImpactStyle.Light/Medium and NotificationType.Success/Error.</v>
+        <v>BL-026: נוסף CELEBRATION_TO_RELIGION map; getUpcomingHolidaysForContact עכשיו מסנן לפי celebrationType כאשר מוגדר, נופל בחזרה ל-religion</v>
       </c>
       <c r="E121" t="str">
-        <v>feature</v>
+        <v>improvement</v>
       </c>
       <c r="F121" t="str">
         <v>code_change</v>
@@ -3302,19 +3314,19 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-28</v>
       </c>
       <c r="B122" t="str">
-        <v>01:00</v>
+        <v>22:00</v>
       </c>
       <c r="C122" t="str">
-        <v>src/screens/ContactFormScreen.tsx + src/components/ChannelPicker.tsx + src/screens/UpgradeScreen.tsx</v>
+        <v>src/screens/ContactFormScreen.tsx</v>
       </c>
       <c r="D122" t="str">
-        <v>BL-024 (Sprint 4): Haptic wired to 3 key actions — hapticSuccess after contact save, hapticMedium on greeting channel select, hapticSuccess/Error on coupon redemption.</v>
+        <v>BL-026: נוסף select לסוג חגיגה בקטע תרבות (Cultural); celebrationType עובר ל-handleSave</v>
       </c>
       <c r="E122" t="str">
-        <v>feature</v>
+        <v>improvement</v>
       </c>
       <c r="F122" t="str">
         <v>code_change</v>
@@ -3328,19 +3340,19 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-28</v>
       </c>
       <c r="B123" t="str">
-        <v>01:30</v>
+        <v>22:00</v>
       </c>
       <c r="C123" t="str">
-        <v>src/services/storageService.ts</v>
+        <v>src/services/notificationService.ts</v>
       </c>
       <c r="D123" t="str">
-        <v>BL-034 (Sprint 4): exportBackupJSON() exports contacts+groups+drafts+settings as JSON with UTF-8 encoding; importBackupJSON() reads File and restores data after validation. Version and exportedAt metadata included.</v>
+        <v>BL-023: נוספה התראת overdue — נשלחת כאשר daysSince &gt;= 45 ואין יום הולדת בקרוב (בעוד 7 ימים); dedup קיים דרך nm_notif_sent</v>
       </c>
       <c r="E123" t="str">
-        <v>feature</v>
+        <v>improvement</v>
       </c>
       <c r="F123" t="str">
         <v>code_change</v>
@@ -3354,16 +3366,16 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-28</v>
       </c>
       <c r="B124" t="str">
-        <v>01:30</v>
+        <v>22:00</v>
       </c>
       <c r="C124" t="str">
-        <v>src/screens/SettingsScreen.tsx</v>
+        <v>src/screens/DeviceContactsScreen.tsx</v>
       </c>
       <c r="D124" t="str">
-        <v>BL-034 (Sprint 4): Added Backup and Restore buttons to Premium Features card. Hidden file input for restore. Success reloads page after 1.2s. Error feedback clears after 3s.</v>
+        <v>BL-030: מסך ייבוא מהטלפון — תהליך consent/permission/list/import; dedup טלפון; fallback ל-web; @capacitor-community/contacts</v>
       </c>
       <c r="E124" t="str">
         <v>feature</v>
@@ -3380,19 +3392,19 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-28</v>
       </c>
       <c r="B125" t="str">
-        <v>01:45</v>
+        <v>22:00</v>
       </c>
       <c r="C125" t="str">
-        <v>src/screens/ContactFormScreen.tsx</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="D125" t="str">
-        <v>BL-035 (Sprint 4): Duplicate contact detection on new contact creation. findDuplicate() checks exact name match or phone (7+ digits stripped). Modal warns with matching name and offers "Save Anyway" or "Cancel". Edit mode excluded.</v>
+        <v>BL-030: נוסף lazy import ל-DeviceContactsScreen; נוסף route /device-contacts עם Premium gate</v>
       </c>
       <c r="E125" t="str">
-        <v>feature</v>
+        <v>improvement</v>
       </c>
       <c r="F125" t="str">
         <v>code_change</v>
@@ -3406,33 +3418,683 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B126" t="str">
+        <v>22:00</v>
+      </c>
+      <c r="C126" t="str">
+        <v>src/screens/premium/ImportContactsScreen.tsx</v>
+      </c>
+      <c r="D126" t="str">
+        <v>BL-030: נוסף כרטיס קיצור דרך «ייבוא מהטלפון» בראש מסך Import — מנווט ל-/device-contacts</v>
+      </c>
+      <c r="E126" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F126" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G126" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H126" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B127" t="str">
+        <v>22:00</v>
+      </c>
+      <c r="C127" t="str">
+        <v>BACKLOG.md</v>
+      </c>
+      <c r="D127" t="str">
+        <v>Sprint 3 מסומן כ-✅ COMPLETE; BL-024/025/027/028/029 הועברו ל-Sprint 4</v>
+      </c>
+      <c r="E127" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F127" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G127" t="str">
+        <v>Agent 4</v>
+      </c>
+      <c r="H127" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B128" t="str">
+        <v>23:00</v>
+      </c>
+      <c r="C128" t="str">
+        <v>src/screens/CalendarScreen.tsx</v>
+      </c>
+      <c r="D128" t="str">
+        <v>BUG-043: תוקן — חגים רב-יומיים הציגו נקודה רק ביום הראשון; getHolidaysForDay עודכן לבדיקת טווח [date, endDate]; רשימת חודש מסוננת לפי חפיפה עם החודש הנוכחי; isSameMonth הוסר מה-imports</v>
+      </c>
+      <c r="E128" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F128" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G128" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H128" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B129" t="str">
+        <v>23:00</v>
+      </c>
+      <c r="C129" t="str">
+        <v>src/data/holidays.ts</v>
+      </c>
+      <c r="D129" t="str">
+        <v>BUG-044: נוסף sukkot-2026 (15-22 תשרי תשפ״ז, 25 ספטמבר–2 אוקטובר 2026) — ה-entry של 2025 קיים אך 2026 חסר</v>
+      </c>
+      <c r="E129" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F129" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G129" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H129" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B130" t="str">
+        <v>23:30</v>
+      </c>
+      <c r="C130" t="str">
+        <v>src/screens/ContactDetailScreen.tsx</v>
+      </c>
+      <c r="D130" t="str">
+        <v>BL-045: שיפור celebration feedback — צליל: C5/E5/G5 אקורד גדול arpeggio במקום oscillator; אנימציה: 10 חלקיקים (במקום 6), גדולים יותר (text-xl), פיזור רחב יותר (±85px/±110px), 1.6s</v>
+      </c>
+      <c r="E130" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F130" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G130" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H130" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B131" t="str">
+        <v>23:30</v>
+      </c>
+      <c r="C131" t="str">
+        <v>src/index.css</v>
+      </c>
+      <c r="D131" t="str">
+        <v>BL-045: keyframe particleBurst עודכן — scale-pop (0.4→1.6→0) + מסלול רחב יותר; אנימציה עודכנה ל-1.4s</v>
+      </c>
+      <c r="E131" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F131" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G131" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H131" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
         <v>2026-04-29</v>
       </c>
-      <c r="B126" t="str">
-        <v>01:45</v>
-      </c>
-      <c r="C126" t="str">
+      <c r="B132" t="str">
+        <v>00:00</v>
+      </c>
+      <c r="C132" t="str">
+        <v>src/services/exportService.ts</v>
+      </c>
+      <c r="D132" t="str">
+        <v>BL-025: exportContactsToCSV — ייצוא כל שדות קשר ל-CSV עם BOM לתמיכה ב-Excel Hebrew; PapaParse</v>
+      </c>
+      <c r="E132" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F132" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G132" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H132" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B133" t="str">
+        <v>00:00</v>
+      </c>
+      <c r="C133" t="str">
+        <v>src/screens/SettingsScreen.tsx</v>
+      </c>
+      <c r="D133" t="str">
+        <v>BL-025: נוסף כפתור ייצוא CSV בכרטיס Premium Features; exportDone state עם הצלחה feedback 2.5s</v>
+      </c>
+      <c r="E133" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F133" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G133" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H133" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B134" t="str">
+        <v>00:00</v>
+      </c>
+      <c r="C134" t="str">
         <v>src/i18n/index.ts</v>
       </c>
-      <c r="D126" t="str">
-        <v>BL-024+034+035: Added 13 i18n keys in EN+HE: settings_backupData/Success, settings_restoreData/Success/Error, contactForm_duplicateTitle/Body/SaveAnyway.</v>
-      </c>
-      <c r="E126" t="str">
+      <c r="D134" t="str">
+        <v>BL-025: נוספו מפתחות settings_exportContacts + settings_exportSuccess ב-EN+HE</v>
+      </c>
+      <c r="E134" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F134" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G134" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H134" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B135" t="str">
+        <v>00:30</v>
+      </c>
+      <c r="C135" t="str">
+        <v>src/components/Navigation.tsx</v>
+      </c>
+      <c r="D135" t="str">
+        <v>BL-029 WCAG 2.5.5: כפתור חזרה ב-PageHeader עודכן ל-min-w/h-[48px] flex items-center justify-center</v>
+      </c>
+      <c r="E135" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F135" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G135" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H135" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B136" t="str">
+        <v>00:30</v>
+      </c>
+      <c r="C136" t="str">
+        <v>src/screens/ContactFormScreen.tsx</v>
+      </c>
+      <c r="D136" t="str">
+        <v>BL-029 WCAG 2.5.5: כפתור מחיקה ב-PageHeader עודכן ל-min-w/h-[48px] flex items-center justify-center</v>
+      </c>
+      <c r="E136" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F136" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G136" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H136" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B137" t="str">
+        <v>00:30</v>
+      </c>
+      <c r="C137" t="str">
+        <v>src/screens/GroupsScreen.tsx</v>
+      </c>
+      <c r="D137" t="str">
+        <v>BL-029 WCAG 2.5.5: כפתורי Edit/Delete בכרטיסי קבוצה עודכנו ל-min-w/h-[48px] flex items-center justify-center</v>
+      </c>
+      <c r="E137" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F137" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G137" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H137" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B138" t="str">
+        <v>00:30</v>
+      </c>
+      <c r="C138" t="str">
+        <v>src/screens/GreetingEditorScreen.tsx</v>
+      </c>
+      <c r="D138" t="str">
+        <v>BL-029 WCAG 2.5.5: כפתורי Regenerate/Copy עודכנו ל-min-w/h-[48px] flex items-center justify-center</v>
+      </c>
+      <c r="E138" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F138" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G138" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H138" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B139" t="str">
+        <v>00:30</v>
+      </c>
+      <c r="C139" t="str">
+        <v>src/components/ui/Modal.tsx</v>
+      </c>
+      <c r="D139" t="str">
+        <v>BL-029 WCAG 2.5.5: כפתור סגירה ב-Modal עודכן ל-min-w/h-[48px] flex items-center justify-center</v>
+      </c>
+      <c r="E139" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F139" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G139" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H139" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B140" t="str">
+        <v>00:30</v>
+      </c>
+      <c r="C140" t="str">
+        <v>src/screens/ContactDetailScreen.tsx</v>
+      </c>
+      <c r="D140" t="str">
+        <v>BL-029 WCAG 2.5.5: כפתור עריכה ב-PageHeader עודכן ל-min-w/h-[48px] flex items-center justify-center</v>
+      </c>
+      <c r="E140" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F140" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G140" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H140" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B141" t="str">
+        <v>00:30</v>
+      </c>
+      <c r="C141" t="str">
+        <v>src/screens/HolidayDetailScreen.tsx</v>
+      </c>
+      <c r="D141" t="str">
+        <v>BL-029 WCAG 2.5.5: כפתור העתקת ברכה עודכן ל-min-w/h-[48px] flex items-center justify-center</v>
+      </c>
+      <c r="E141" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F141" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G141" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H141" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B142" t="str">
+        <v>00:30</v>
+      </c>
+      <c r="C142" t="str">
+        <v>src/screens/premium/BirthdayGreetingEditorScreen.tsx</v>
+      </c>
+      <c r="D142" t="str">
+        <v>BL-029 WCAG 2.5.5: כפתורי Regenerate/Copy עודכנו ל-min-w/h-[48px] flex items-center justify-center</v>
+      </c>
+      <c r="E142" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F142" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G142" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H142" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B143" t="str">
+        <v>01:00</v>
+      </c>
+      <c r="C143" t="str">
+        <v>src/services/hapticService.ts</v>
+      </c>
+      <c r="D143" t="str">
+        <v>BL-024 (Sprint 4): שירות haptic feedback — hapticLight/Medium/Success/Error; Capacitor.isNativePlatform() guard; graceful no-op בדפדפן</v>
+      </c>
+      <c r="E143" t="str">
         <v>feature</v>
       </c>
-      <c r="F126" t="str">
-        <v>code_change</v>
-      </c>
-      <c r="G126" t="str">
-        <v>Agent 1</v>
-      </c>
-      <c r="H126" t="str">
+      <c r="F143" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G143" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H143" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B144" t="str">
+        <v>01:00</v>
+      </c>
+      <c r="C144" t="str">
+        <v>src/screens/ContactFormScreen.tsx</v>
+      </c>
+      <c r="D144" t="str">
+        <v>BL-024: hapticSuccess() מופעל לאחר שמירת איש קשר; BL-035: findDuplicate() + Modal אזהרה לשם/טלפון כפול + doSave() refactor</v>
+      </c>
+      <c r="E144" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F144" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G144" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H144" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B145" t="str">
+        <v>01:00</v>
+      </c>
+      <c r="C145" t="str">
+        <v>src/components/ChannelPicker.tsx</v>
+      </c>
+      <c r="D145" t="str">
+        <v>BL-024: hapticMedium() מופעל עם שליחת ברכה בכל ערוץ</v>
+      </c>
+      <c r="E145" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F145" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G145" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H145" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B146" t="str">
+        <v>01:00</v>
+      </c>
+      <c r="C146" t="str">
+        <v>src/screens/UpgradeScreen.tsx</v>
+      </c>
+      <c r="D146" t="str">
+        <v>BL-024: hapticSuccess() בהפעלת קופון; hapticError() בכישלון</v>
+      </c>
+      <c r="E146" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F146" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G146" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H146" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B147" t="str">
+        <v>01:30</v>
+      </c>
+      <c r="C147" t="str">
+        <v>src/services/storageService.ts</v>
+      </c>
+      <c r="D147" t="str">
+        <v>BL-034 (Sprint 4): exportBackupJSON() ו-importBackupJSON() — מייצאים/מייבאים contacts+groups+drafts+settings כ-JSON עם version+timestamp</v>
+      </c>
+      <c r="E147" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F147" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G147" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H147" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B148" t="str">
+        <v>01:30</v>
+      </c>
+      <c r="C148" t="str">
+        <v>src/screens/SettingsScreen.tsx</v>
+      </c>
+      <c r="D148" t="str">
+        <v>BL-034: כפתורי Backup/Restore בכרטיס Premium Features; hidden file input; feedback states</v>
+      </c>
+      <c r="E148" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F148" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G148" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H148" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B149" t="str">
+        <v>01:30</v>
+      </c>
+      <c r="C149" t="str">
+        <v>src/i18n/index.ts</v>
+      </c>
+      <c r="D149" t="str">
+        <v>BL-024+034+035: מפתחות backup/restore/duplicate ב-EN+HE; 13 מפתחות חדשים סה"כ</v>
+      </c>
+      <c r="E149" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F149" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G149" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H149" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B150" t="str">
+        <v>02:00</v>
+      </c>
+      <c r="C150" t="str">
+        <v>BACKLOG.md</v>
+      </c>
+      <c r="D150" t="str">
+        <v>Sprint 4 BL-024/025/027/028/029/034/035 מסומנים ✅ Done; BL-031/032/033/036/037/038 הועברו ל-Sprint 5; נוספו BL-046 עד BL-052 (7 משימות חדשות מהמשתמש: Import entry point, CSV label, device contacts visibility, BottomNav active tab, group assignment, Excel template, smart holiday suggestions by group purpose)</v>
+      </c>
+      <c r="E150" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F150" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G150" t="str">
+        <v>Agent 4</v>
+      </c>
+      <c r="H150" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B151" t="str">
+        <v>03:00</v>
+      </c>
+      <c r="C151" t="str">
+        <v>scripts/make-changelog.js</v>
+      </c>
+      <c r="D151" t="str">
+        <v>שיפור מעקב changelog: הסקריפט מחדש קורא ישירות מ-changelog_queue.json במקום מערך hardcoded; 64 שורות legacy נשמרות כ-LEGACY_ROWS; כל השינויים העתידיים נרשמים אוטומטית; 24 רשומות שהיו חסרות שוחזרו — סה"כ 149 רשומות (היה 125)</v>
+      </c>
+      <c r="E151" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F151" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G151" t="str">
+        <v>Agent 4</v>
+      </c>
+      <c r="H151" t="str">
         <v>done</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H126"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H151"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H151"/>
+  <dimension ref="A1:H157"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -4092,9 +4092,165 @@
         <v>done</v>
       </c>
     </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B152" t="str">
+        <v>04:00</v>
+      </c>
+      <c r="C152" t="str">
+        <v>src/screens/ContactsScreen.tsx</v>
+      </c>
+      <c r="D152" t="str">
+        <v>BL-046 Sprint 5: נוסף כפתור Import (FileUp) בכותרת לפרמיום; קיצור דרך ייבוא בEmpty State לפרמיום</v>
+      </c>
+      <c r="E152" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F152" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G152" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H152" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B153" t="str">
+        <v>04:00</v>
+      </c>
+      <c r="C153" t="str">
+        <v>src/screens/premium/ImportContactsScreen.tsx</v>
+      </c>
+      <c r="D153" t="str">
+        <v>BL-047: accept='.csv,.xlsx' → accept='.csv'; תווית CSV-only בולטת עם badge. BL-048: כפתור device contacts עוצב כ-CTA כחול בולט עם gradient+shadow; מפריד 'או העלה קובץ CSV'</v>
+      </c>
+      <c r="E153" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F153" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G153" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H153" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B154" t="str">
+        <v>04:00</v>
+      </c>
+      <c r="C154" t="str">
+        <v>src/components/Navigation.tsx</v>
+      </c>
+      <c r="D154" t="str">
+        <v>BL-049: שיפור Active tab — icon גדול יותר (22px), label בצבע primary עם fontWeight 800, נקודת אינדיקטור קטנה מתחת ל-label</v>
+      </c>
+      <c r="E154" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F154" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G154" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H154" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B155" t="str">
+        <v>04:30</v>
+      </c>
+      <c r="C155" t="str">
+        <v>src/types/index.ts</v>
+      </c>
+      <c r="D155" t="str">
+        <v>BL-052: GroupPurpose union type (family/friends/work/clients/hr/community/custom) + purpose?: GroupPurpose שדה ב-Group interface</v>
+      </c>
+      <c r="E155" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F155" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G155" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H155" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B156" t="str">
+        <v>04:30</v>
+      </c>
+      <c r="C156" t="str">
+        <v>src/screens/GroupsScreen.tsx</v>
+      </c>
+      <c r="D156" t="str">
+        <v>BL-052: SUGGESTED_BASES lookup לפי purpose; applyPurpose() מוסיף הצעות ל-selectedHolidayIds ללא דריסה; purpose selector pills במודל; ✦ badge על חגים מוצעים ברשימה; form+save+openForm מעודכנים עם purpose</v>
+      </c>
+      <c r="E156" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F156" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G156" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H156" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B157" t="str">
+        <v>04:30</v>
+      </c>
+      <c r="C157" t="str">
+        <v>src/i18n/index.ts</v>
+      </c>
+      <c r="D157" t="str">
+        <v>BL-046/047/048/049/052: נוספו 20 מפתחות ב-EN+HE: import_csvOnly/fromPhoneDesc/orCSV; group_purpose/hint + 7 purpose labels; group_holidays_selected</v>
+      </c>
+      <c r="E157" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F157" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G157" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H157" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H151"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H157"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H157"/>
+  <dimension ref="A1:H160"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -4248,9 +4248,87 @@
         <v>done</v>
       </c>
     </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B158" t="str">
+        <v>12:00</v>
+      </c>
+      <c r="C158" t="str">
+        <v>src/screens/premium/ImportContactsScreen.tsx</v>
+      </c>
+      <c r="D158" t="str">
+        <v>BL-050: group assignment UI בשלב done — select + כפתור assign; מיזוג contactIds עם Set למניעת כפילויות; groupAssigned feedback</v>
+      </c>
+      <c r="E158" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F158" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G158" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H158" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B159" t="str">
+        <v>12:01</v>
+      </c>
+      <c r="C159" t="str">
+        <v>src/screens/premium/ImportContactsScreen.tsx</v>
+      </c>
+      <c r="D159" t="str">
+        <v>BL-051: downloadCSVTemplate() — Blob CSV עם BOM + כותרות עבריות + שורת דוגמה; כפתור הורדה בשלב upload</v>
+      </c>
+      <c r="E159" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F159" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G159" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H159" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B160" t="str">
+        <v>12:02</v>
+      </c>
+      <c r="C160" t="str">
+        <v>src/i18n/index.ts</v>
+      </c>
+      <c r="D160" t="str">
+        <v>BL-050/051: נוספו 10 מפתחות EN+HE: import_addToGroup/Hint/selectGroup/assignGroup/groupAssigned/noGroups/downloadTemplate/templateHint</v>
+      </c>
+      <c r="E160" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F160" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G160" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H160" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H157"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H160"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H160"/>
+  <dimension ref="A1:H167"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -4326,9 +4326,191 @@
         <v>done</v>
       </c>
     </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B161" t="str">
+        <v>12:00</v>
+      </c>
+      <c r="C161" t="str">
+        <v>src/data/groupSuggestions.ts</v>
+      </c>
+      <c r="D161" t="str">
+        <v>FINDING 86: חולץ SUGGESTED_BASES לקובץ נתונים עצמאי src/data/groupSuggestions.ts; GroupsScreen.tsx מייבא ממנו</v>
+      </c>
+      <c r="E161" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F161" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G161" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H161" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B162" t="str">
+        <v>12:00</v>
+      </c>
+      <c r="C162" t="str">
+        <v>src/screens/GroupsScreen.tsx</v>
+      </c>
+      <c r="D162" t="str">
+        <v>FINDING 75/87: applyPurpose() מסיר עכשיו את ה-holidays המוצעים על-ידי הקטגוריה הישנה לפני הוספת החדשים; FINDING 86: SUGGESTED_BASES מיובא מ-groupSuggestions.ts</v>
+      </c>
+      <c r="E162" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F162" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G162" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H162" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B163" t="str">
+        <v>12:00</v>
+      </c>
+      <c r="C163" t="str">
+        <v>src/components/MediaAttachmentPicker.tsx</v>
+      </c>
+      <c r="D163" t="str">
+        <v>FINDING 31: הוסרו המילים " 1:00" המיותרות שצורפו לאחר media_record_limit; המפתח כבר מכיל "מקסימום 60 שניות"</v>
+      </c>
+      <c r="E163" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F163" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G163" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H163" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B164" t="str">
+        <v>12:00</v>
+      </c>
+      <c r="C164" t="str">
+        <v>src/screens/DashboardScreen.tsx</v>
+      </c>
+      <c r="D164" t="str">
+        <v>FINDING 49: כפתור "שלח לקבוצה" מנווט עכשיו ל-/greeting?contactId=&amp;holidayId= (איש הקשר הראשון בקבוצה + חג); במקום ל-/contacts גנרי</v>
+      </c>
+      <c r="E164" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F164" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G164" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H164" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B165" t="str">
+        <v>12:00</v>
+      </c>
+      <c r="C165" t="str">
+        <v>src/screens/ContactFormScreen.tsx</v>
+      </c>
+      <c r="D165" t="str">
+        <v>FINDING 76/81: findDuplicate() בודקת גם עת עריכת קשר קיים (לא רק חדש); מוסיפה self-exclusion לפי contact ID; handleSave מפעיל בדיקה גם בעריכה</v>
+      </c>
+      <c r="E165" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F165" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G165" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H165" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B166" t="str">
+        <v>12:00</v>
+      </c>
+      <c r="C166" t="str">
+        <v>src/screens/premium/ImportContactsScreen.tsx</v>
+      </c>
+      <c r="D166" t="str">
+        <v>FINDING 84: כפתור שיוך לקבוצה עטוף ב-try/catch + הודעת שגיאה בעברית; FINDING 85: כרטיס שיוך קבוצה מוסתר כאשר importedIds.length === 0</v>
+      </c>
+      <c r="E166" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F166" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G166" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H166" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B167" t="str">
+        <v>12:00</v>
+      </c>
+      <c r="C167" t="str">
+        <v>src/i18n/index.ts</v>
+      </c>
+      <c r="D167" t="str">
+        <v>נוסף מפתח import_groupAssignError בעברית ובאנגלית — הודעת שגיאה לשיוך קבוצה שנכשל</v>
+      </c>
+      <c r="E167" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F167" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G167" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H167" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H160"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H167"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H167"/>
+  <dimension ref="A1:H180"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -4508,9 +4508,347 @@
         <v>done</v>
       </c>
     </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B168" t="str">
+        <v>14:00</v>
+      </c>
+      <c r="C168" t="str">
+        <v>src/data/demoData.ts</v>
+      </c>
+      <c r="D168" t="str">
+        <v>BL-036 Sprint 7: נוצר קובץ נתוני הדגמה — 6 אנשי קשר דוגמה (Sarah Cohen, Ahmed Al-Rashid, David Levi, Maria García, Yosef Mizrahi, Nadia Khalil) + 2 קבוצות (Jewish Holidays, VIP Clients)</v>
+      </c>
+      <c r="E168" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F168" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G168" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H168" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B169" t="str">
+        <v>14:00</v>
+      </c>
+      <c r="C169" t="str">
+        <v>src/services/storageService.ts</v>
+      </c>
+      <c r="D169" t="str">
+        <v>BL-036 Sprint 7: נוספו פונקציות מצב הדגמה — isDemoMode(), enableDemoMode(), clearDemoMode(); getContacts/saveContacts/getGroups/saveGroups מנותבים לכתובות nm_demo_* כשמצב הדגמה פעיל; נתוני משתמש אמיתיים לא נפגעים</v>
+      </c>
+      <c r="E169" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F169" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G169" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H169" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B170" t="str">
+        <v>14:00</v>
+      </c>
+      <c r="C170" t="str">
+        <v>src/context/AppContext.tsx</v>
+      </c>
+      <c r="D170" t="str">
+        <v>BL-036 Sprint 7: נוספו isDemoMode, enableDemo, clearDemo לממשק וה-context value; enableDemo() מפעיל מצב הדגמה ומרענן; clearDemo() מוחק נתוני הדגמה ומרענן</v>
+      </c>
+      <c r="E170" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F170" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G170" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H170" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B171" t="str">
+        <v>14:00</v>
+      </c>
+      <c r="C171" t="str">
+        <v>src/screens/OnboardingScreen.tsx</v>
+      </c>
+      <c r="D171" t="str">
+        <v>BL-036 Sprint 7: נוסף כפתור 'נסה הדגמה' בשקף האחרון של ה-Onboarding; לחיצה מפעילה enableDemo() ומנווטת לדשבורד עם נתוני דוגמה</v>
+      </c>
+      <c r="E171" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F171" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G171" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H171" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B172" t="str">
+        <v>14:00</v>
+      </c>
+      <c r="C172" t="str">
+        <v>src/App.tsx</v>
+      </c>
+      <c r="D172" t="str">
+        <v>BL-036 Sprint 7: נוסף DemoBanner קבוע בראש המסך כשמצב הדגמה פעיל — באנר סגול עם כפתור יציאה; WithNav מוסיף padding-top כדי לפנות מקום לבאנר</v>
+      </c>
+      <c r="E172" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F172" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G172" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H172" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B173" t="str">
+        <v>14:00</v>
+      </c>
+      <c r="C173" t="str">
+        <v>src/screens/SettingsScreen.tsx</v>
+      </c>
+      <c r="D173" t="str">
+        <v>BL-036 Sprint 7: נוסף כרטיס 'צא ממצב הדגמה' בהגדרות כשמצב הדגמה פעיל; כפתור מפעיל clearDemo()</v>
+      </c>
+      <c r="E173" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F173" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G173" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H173" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B174" t="str">
+        <v>14:10</v>
+      </c>
+      <c r="C174" t="str">
+        <v>src/i18n/index.ts</v>
+      </c>
+      <c r="D174" t="str">
+        <v>Sprint 7 i18n: נוספו 20 מפתחות EN+HE — 7 ל-BirthdayCenterScreen (birthday_heroSubtitle, contactCount, noneTracked, todayBadge, itsTheirBirthday, day, days), 4 מפתחות נגישות (contacts_addContact, calendar_prevMonth, calendar_nextMonth, groups_searchHolidays), 2 לדשבורד (dashboard_isTomorrow, dashboard_prepareGreetings), 5 למצב הדגמה (demo_banner, demo_loadData, demo_clear, demo_clearConfirm, demo_cleared)</v>
+      </c>
+      <c r="E174" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F174" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G174" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H174" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B175" t="str">
+        <v>14:10</v>
+      </c>
+      <c r="C175" t="str">
+        <v>src/screens/premium/BirthdayCenterScreen.tsx</v>
+      </c>
+      <c r="D175" t="str">
+        <v>Sprint 7 i18n: 7 מחרוזות אנגלית קשיחות הוחלפו ב-t() — birthday_title בהרו, birthday_heroSubtitle, birthday_contactCount, birthday_noneTracked, birthday_todayBadge, birthday_itsTheirBirthday, birthday_day/days במחשבון ספירת ימים</v>
+      </c>
+      <c r="E175" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F175" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G175" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H175" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B176" t="str">
+        <v>14:10</v>
+      </c>
+      <c r="C176" t="str">
+        <v>src/screens/DashboardScreen.tsx</v>
+      </c>
+      <c r="D176" t="str">
+        <v>Sprint 7 i18n: 3 מחרוזות תורגמו — label כפתור Add Contact, טקסט '{name} is Tomorrow!', טקסט 'Prepare your greetings now', aria-label כפתור FAB</v>
+      </c>
+      <c r="E176" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F176" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G176" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H176" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B177" t="str">
+        <v>14:10</v>
+      </c>
+      <c r="C177" t="str">
+        <v>src/screens/ContactsScreen.tsx</v>
+      </c>
+      <c r="D177" t="str">
+        <v>Sprint 7 i18n: aria-label 'Add contact' הוחלף ב-t('contacts_addContact')</v>
+      </c>
+      <c r="E177" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F177" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G177" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H177" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B178" t="str">
+        <v>14:10</v>
+      </c>
+      <c r="C178" t="str">
+        <v>src/screens/CalendarScreen.tsx</v>
+      </c>
+      <c r="D178" t="str">
+        <v>Sprint 7 i18n: aria-label 'Previous month' ו-'Next month' הוחלפו ב-t('calendar_prevMonth') ו-t('calendar_nextMonth')</v>
+      </c>
+      <c r="E178" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F178" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G178" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H178" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B179" t="str">
+        <v>14:10</v>
+      </c>
+      <c r="C179" t="str">
+        <v>src/screens/GroupsScreen.tsx</v>
+      </c>
+      <c r="D179" t="str">
+        <v>Sprint 7 i18n: placeholder 'Search holidays...' הוחלף ב-t('groups_searchHolidays')</v>
+      </c>
+      <c r="E179" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F179" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G179" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H179" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B180" t="str">
+        <v>14:10</v>
+      </c>
+      <c r="C180" t="str">
+        <v>src/screens/HolidayDetailScreen.tsx</v>
+      </c>
+      <c r="D180" t="str">
+        <v>Sprint 7 i18n: aria-label 'Copy' הוחלף ב-t('greeting_copy'); נוסף useT() ל-GreetingRow sub-component</v>
+      </c>
+      <c r="E180" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F180" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G180" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H180" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H167"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H180"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H180"/>
+  <dimension ref="A1:H185"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -4846,9 +4846,139 @@
         <v>done</v>
       </c>
     </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B181" t="str">
+        <v>15:00</v>
+      </c>
+      <c r="C181" t="str">
+        <v>src/i18n/index.ts</v>
+      </c>
+      <c r="D181" t="str">
+        <v>Sprint 8 FINDING 28D: נוספה פונקציית dir(langCode) — מחזירה 'rtl'|'ltr' לפי קוד שפה (RTL_LANG_CODES: he/ar/fa/ur/yi/dv)</v>
+      </c>
+      <c r="E181" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F181" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G181" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H181" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B182" t="str">
+        <v>15:01</v>
+      </c>
+      <c r="C182" t="str">
+        <v>src/i18n/index.ts</v>
+      </c>
+      <c r="D182" t="str">
+        <v>Sprint 8 FINDING 29A+29B: נוספו מפתחות contactForm_avatarColor (EN: Avatar Color / HE: צבע אווטאר) ו-contactForm_autoGradient (EN: Auto gradient / HE: גרדיאנט אוטומטי)</v>
+      </c>
+      <c r="E182" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F182" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G182" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H182" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B183" t="str">
+        <v>15:02</v>
+      </c>
+      <c r="C183" t="str">
+        <v>src/screens/HolidayDetailScreen.tsx</v>
+      </c>
+      <c r="D183" t="str">
+        <v>FINDING 28D תוקן: GreetingRow הוסף prop langCode; dir attribute מחושב עם dir(langCode) במקום השוואת מחרוזת מוקשת; 4 call sites עודכנו עם he/ar/en</v>
+      </c>
+      <c r="E183" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F183" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G183" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H183" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B184" t="str">
+        <v>15:03</v>
+      </c>
+      <c r="C184" t="str">
+        <v>src/screens/ContactFormScreen.tsx</v>
+      </c>
+      <c r="D184" t="str">
+        <v>FINDING 29A תוקן: תווית 'Avatar Color' הוחלפה ב-t('contactForm_avatarColor') — עברית: צבע אווטאר</v>
+      </c>
+      <c r="E184" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F184" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G184" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H184" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B185" t="str">
+        <v>15:04</v>
+      </c>
+      <c r="C185" t="str">
+        <v>src/screens/ContactFormScreen.tsx</v>
+      </c>
+      <c r="D185" t="str">
+        <v>FINDING 29B תוקן: title='Auto gradient' הוחלף ב-aria-label={t('contactForm_autoGradient')} — מתקן הפרת WCAG 4.1.2 על כפתור icon-only</v>
+      </c>
+      <c r="E185" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F185" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G185" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H185" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H180"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H185"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H185"/>
+  <dimension ref="A1:H188"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -4976,9 +4976,87 @@
         <v>done</v>
       </c>
     </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B186" t="str">
+        <v>15:30</v>
+      </c>
+      <c r="C186" t="str">
+        <v>BACKLOG.md</v>
+      </c>
+      <c r="D186" t="str">
+        <v>BL-059 נוסף: Premium holiday reminder notifications — Sprint 9; Push/SMS/Email/WhatsApp; dedup; Premium gate</v>
+      </c>
+      <c r="E186" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F186" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G186" t="str">
+        <v>Agent 4</v>
+      </c>
+      <c r="H186" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B187" t="str">
+        <v>15:30</v>
+      </c>
+      <c r="C187" t="str">
+        <v>BACKLOG.csv</v>
+      </c>
+      <c r="D187" t="str">
+        <v>BL-059 שורה חדשה ב-BACKLOG.csv — Premium holiday reminder notifications</v>
+      </c>
+      <c r="E187" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F187" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G187" t="str">
+        <v>Agent 4</v>
+      </c>
+      <c r="H187" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B188" t="str">
+        <v>15:30</v>
+      </c>
+      <c r="C188" t="str">
+        <v>FEATURES.md</v>
+      </c>
+      <c r="D188" t="str">
+        <v>BL-059 תועד ב-FEATURES.md: תיאור Feature, Sprint 9 Planned section, טבלת Free vs Premium עודכנה עם Holiday reminders + Notification channels</v>
+      </c>
+      <c r="E188" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F188" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G188" t="str">
+        <v>Agent 4</v>
+      </c>
+      <c r="H188" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H185"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H188"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H188"/>
+  <dimension ref="A1:H195"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -5054,9 +5054,191 @@
         <v>done</v>
       </c>
     </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B189" t="str">
+        <v>16:00</v>
+      </c>
+      <c r="C189" t="str">
+        <v>src/i18n/index.ts</v>
+      </c>
+      <c r="D189" t="str">
+        <v>Sprint 9: נוספו 21 מפתחות reminders_* (EN+HE) ו-24 מפתחות payme_* (EN+HE) עבור BL-059 ו-BL-032</v>
+      </c>
+      <c r="E189" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F189" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G189" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H189" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B190" t="str">
+        <v>16:01</v>
+      </c>
+      <c r="C190" t="str">
+        <v>src/services/reminderService.ts</v>
+      </c>
+      <c r="D190" t="str">
+        <v>BL-059: שירות תזכורות חגים — HolidayReminderSettings, getReminderSettings/saveReminderSettings, hasBeenReminded/markReminded; localStorage key nm_holiday_reminder_settings + nm_holiday_reminder_sent</v>
+      </c>
+      <c r="E190" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F190" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G190" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H190" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B191" t="str">
+        <v>16:02</v>
+      </c>
+      <c r="C191" t="str">
+        <v>src/screens/HolidayRemindersScreen.tsx</v>
+      </c>
+      <c r="D191" t="str">
+        <v>BL-059: מסך תזכורות חגים — Premium gate, toggle הפעל/כבה, בחירת ימים מראש (1/3/7), 4 ערוצים (Push/SMS/Email/WhatsApp) עם הערת provider לערוצים עתידיים, רשימת אנשי קשר+חגים קרובים, שמירה ב-localStorage</v>
+      </c>
+      <c r="E191" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F191" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G191" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H191" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B192" t="str">
+        <v>16:03</v>
+      </c>
+      <c r="C192" t="str">
+        <v>src/screens/PaymeScreen.tsx</v>
+      </c>
+      <c r="D192" t="str">
+        <v>BL-032: מסך תשלום PayMe — בחירת תוכנית חודשי/שנתי, טופס שם+אימייל, כפתור שלם עם PayMe (קורא ל-createPaymentLink stub), error handling בעברית, disclaimer הדגמה, מצב premium active</v>
+      </c>
+      <c r="E192" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F192" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G192" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H192" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B193" t="str">
+        <v>16:04</v>
+      </c>
+      <c r="C193" t="str">
+        <v>src/App.tsx</v>
+      </c>
+      <c r="D193" t="str">
+        <v>Sprint 9: נוספו routes /reminders (HolidayRemindersScreen) ו-/payment (PaymeScreen), שניהם lazy loaded</v>
+      </c>
+      <c r="E193" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F193" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G193" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H193" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B194" t="str">
+        <v>16:05</v>
+      </c>
+      <c r="C194" t="str">
+        <v>src/screens/SettingsScreen.tsx</v>
+      </c>
+      <c r="D194" t="str">
+        <v>BL-059: נוסף כפתור 'תזכורות חגים' לסעיף Premium Features בהגדרות (מוביל ל-/reminders)</v>
+      </c>
+      <c r="E194" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F194" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G194" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H194" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B195" t="str">
+        <v>16:06</v>
+      </c>
+      <c r="C195" t="str">
+        <v>src/screens/UpgradeScreen.tsx</v>
+      </c>
+      <c r="D195" t="str">
+        <v>BL-032: נוסף כפתור 'שלם עם PayMe' (gradient amber) מעל קטע הקופון — מנווט ל-/payment; import CreditCard מ-lucide-react</v>
+      </c>
+      <c r="E195" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F195" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G195" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H195" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H188"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H195"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H195"/>
+  <dimension ref="A1:H198"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -5236,9 +5236,87 @@
         <v>done</v>
       </c>
     </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B196" t="str">
+        <v>16:10</v>
+      </c>
+      <c r="C196" t="str">
+        <v>src/i18n/index.ts</v>
+      </c>
+      <c r="D196" t="str">
+        <v>BUG-045/BL-062: נוסף מפתח upgrade_cta גנרי (EN: 'Upgrade Now' / HE: 'שדרג עכשיו') — ללא שם ספק; תוקן upgrade_unlockEverything בעברית מ-'פתח הכל' ל-'שדרג לפרמיום' (BUG-046)</v>
+      </c>
+      <c r="E196" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F196" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G196" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H196" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B197" t="str">
+        <v>16:10</v>
+      </c>
+      <c r="C197" t="str">
+        <v>src/screens/UpgradeScreen.tsx</v>
+      </c>
+      <c r="D197" t="str">
+        <v>BUG-045/BL-062: הוחלף t('payme_goPayMe') ב-t('upgrade_cta') בכפתור ה-CTA הראשי — הטקסט עכשיו גנרי ללא שם ספק</v>
+      </c>
+      <c r="E197" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F197" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G197" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H197" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B198" t="str">
+        <v>16:11</v>
+      </c>
+      <c r="C198" t="str">
+        <v>BUG_REPORT.md</v>
+      </c>
+      <c r="D198" t="str">
+        <v>BUG-045 ו-BUG-046: תועדו שני באגים בדף השדרוג — טקסט CTA ספציפי לספק ו-כותרת גיבור לא ברורה; שניהם סומנו כתוקנו</v>
+      </c>
+      <c r="E198" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F198" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G198" t="str">
+        <v>Agent 4</v>
+      </c>
+      <c r="H198" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H195"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H198"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H198"/>
+  <dimension ref="A1:H200"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -5314,9 +5314,61 @@
         <v>done</v>
       </c>
     </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B199" t="str">
+        <v>16:22</v>
+      </c>
+      <c r="C199" t="str">
+        <v>BACKLOG.md</v>
+      </c>
+      <c r="D199" t="str">
+        <v>BL-063: נוסף תיאור מלא לבאג — סוג ברכה לא מיושם (אין רגנרציה אוטומטית) + דקדוק עברי שגוי בתבניות; מתוכנן לספרינט 11</v>
+      </c>
+      <c r="E199" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F199" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G199" t="str">
+        <v>Agent 4</v>
+      </c>
+      <c r="H199" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B200" t="str">
+        <v>16:22</v>
+      </c>
+      <c r="C200" t="str">
+        <v>BUG_REPORT.md</v>
+      </c>
+      <c r="D200" t="str">
+        <v>BUG-047 (סוג ברכה לא מיושם) ו-BUG-048 (דקדוק עברי שגוי): תועדו שני באגים חדשים; שניהם פתוחים ומתוכננים לספרינט 11</v>
+      </c>
+      <c r="E200" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F200" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G200" t="str">
+        <v>Agent 4</v>
+      </c>
+      <c r="H200" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H198"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H200"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H200"/>
+  <dimension ref="A1:H204"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -5366,9 +5366,113 @@
         <v>done</v>
       </c>
     </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B201" t="str">
+        <v>17:00</v>
+      </c>
+      <c r="C201" t="str">
+        <v>src/services/aiSuggestionsService.ts</v>
+      </c>
+      <c r="D201" t="str">
+        <v>BL-033: שירות הצעות AI חדש — getAISuggestions מחזיר 3 הודעות מוכנות שונות לפי tone (casual/professional/vip) × hasHoliday × language (EN/HE/AR); ללא API חיצוני</v>
+      </c>
+      <c r="E201" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F201" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G201" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H201" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B202" t="str">
+        <v>17:01</v>
+      </c>
+      <c r="C202" t="str">
+        <v>src/i18n/index.ts</v>
+      </c>
+      <c r="D202" t="str">
+        <v>BL-033: נוספו 7 מפתחות i18n לממשק הצעות AI (ai_suggestions_btn/title/subtitle/generating/use/option/premium_desc) בעברית ובאנגלית</v>
+      </c>
+      <c r="E202" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F202" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G202" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H202" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B203" t="str">
+        <v>17:02</v>
+      </c>
+      <c r="C203" t="str">
+        <v>src/screens/GreetingEditorScreen.tsx</v>
+      </c>
+      <c r="D203" t="str">
+        <v>BL-033: נוסף כפתור AI Suggestions — premium gate (PRO badge + ניווט /upgrade); premium: לחיצה → 400ms delay → 3 options panel; בחירת option → ממלא message field; Sparkles+Crown icons</v>
+      </c>
+      <c r="E203" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F203" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G203" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H203" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B204" t="str">
+        <v>17:03</v>
+      </c>
+      <c r="C204" t="str">
+        <v>src/data/holidays.ts</v>
+      </c>
+      <c r="D204" t="str">
+        <v>BL-060: נוספו 5 תאריכים חילוניים/לאומיים: יום השואה הבינלאומי (27 ינואר), יום השואה (27 ניסן), יום הזיכרון (4 אייר), יום הזיכרון האמריקאי (25 מאי), יום העצמאות האמריקאי (4 יולי) — כולם religion: Secular עם ברכות EN+HE</v>
+      </c>
+      <c r="E204" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F204" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G204" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H204" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H200"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H204"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H204"/>
+  <dimension ref="A1:H210"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -5470,9 +5470,165 @@
         <v>done</v>
       </c>
     </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B205" t="str">
+        <v>18:00</v>
+      </c>
+      <c r="C205" t="str">
+        <v>src/screens/UpgradeScreen.tsx</v>
+      </c>
+      <c r="D205" t="str">
+        <v>BL-062 / BUG-045: הוחלף t('payme_goPayMe') ב-t('upgrade_cta') — CTA כפתור כעת גנרי ולא תלוי ספק</v>
+      </c>
+      <c r="E205" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F205" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G205" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H205" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B206" t="str">
+        <v>18:01</v>
+      </c>
+      <c r="C206" t="str">
+        <v>src/i18n/index.ts</v>
+      </c>
+      <c r="D206" t="str">
+        <v>BL-062 / BUG-045+046: נוסף מפתח upgrade_cta (EN: 'Upgrade Now', HE: 'שדרג עכשיו'); upgrade_unlockEverything HE שונה מ-'פתח הכל' ל-'שדרג לפרמיום'</v>
+      </c>
+      <c r="E206" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F206" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G206" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H206" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B207" t="str">
+        <v>18:02</v>
+      </c>
+      <c r="C207" t="str">
+        <v>src/services/greetingService.ts</v>
+      </c>
+      <c r="D207" t="str">
+        <v>BL-063 / BUG-048: תוקנו תבניות עברית friendly generic — 'לברר' → 'לדעת', 'שכל טוב' → 'שיהיה הכל טוב'; business 'שלחתי ידו/ת' → 'פניתי'</v>
+      </c>
+      <c r="E207" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F207" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G207" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H207" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B208" t="str">
+        <v>18:03</v>
+      </c>
+      <c r="C208" t="str">
+        <v>src/screens/GreetingEditorScreen.tsx</v>
+      </c>
+      <c r="D208" t="str">
+        <v>BL-063 / BUG-047: נוסף useEffect([tone]) — כל שינוי ב-tone מחולל generate() מחדש; טיפ שמנוע אוטומטי עובד רק כשיש קשר ומסר</v>
+      </c>
+      <c r="E208" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F208" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G208" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H208" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B209" t="str">
+        <v>18:04</v>
+      </c>
+      <c r="C209" t="str">
+        <v>src/i18n/index.ts</v>
+      </c>
+      <c r="D209" t="str">
+        <v>BL-064: נוספו 8 מפתחות dashboard_quick_send_* ב-EN+HE — dashboard_quick_send/title/subtitle/wa/copy/copied/open_editor</v>
+      </c>
+      <c r="E209" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F209" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G209" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H209" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B210" t="str">
+        <v>18:05</v>
+      </c>
+      <c r="C210" t="str">
+        <v>src/screens/DashboardScreen.tsx</v>
+      </c>
+      <c r="D210" t="str">
+        <v>BL-064: Quick Send panel — כפתור 'שלח ברכה' על כרטיסי ימי הולדת וכרטיסי קבוצה; פאנל overlay תחתי עם 3 אפשרויות AI per contact; כפתורי WhatsApp/Copy/Open Editor לכל option; premium gate</v>
+      </c>
+      <c r="E210" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F210" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G210" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H210" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H204"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H210"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H210"/>
+  <dimension ref="A1:H218"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -5626,9 +5626,217 @@
         <v>done</v>
       </c>
     </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B211" t="str">
+        <v>19:00</v>
+      </c>
+      <c r="C211" t="str">
+        <v>src/services/userProfileService.ts</v>
+      </c>
+      <c r="D211" t="str">
+        <v>BL-067: שירות חדש — getUserName/saveUserName/isProfileSetup; מאחסן שם המשתמש ב-localStorage תחת nm_user_name</v>
+      </c>
+      <c r="E211" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F211" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G211" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H211" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B212" t="str">
+        <v>19:01</v>
+      </c>
+      <c r="C212" t="str">
+        <v>src/screens/UserSetupScreen.tsx</v>
+      </c>
+      <c r="D212" t="str">
+        <v>BL-067: מסך הגדרת פרופיל ראשוני — שאלת שם, שמירה ב-localStorage, CTA 'יאללה נתחיל', קישור דלג; מנווט ל-/dashboard</v>
+      </c>
+      <c r="E212" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F212" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G212" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H212" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B213" t="str">
+        <v>19:02</v>
+      </c>
+      <c r="C213" t="str">
+        <v>src/App.tsx</v>
+      </c>
+      <c r="D213" t="str">
+        <v>BL-067: נוסף route /setup + UserSetupScreen; redirect שורש עודכן: onboarding→setup→dashboard לפי isOnboardingDone + isProfileSetup</v>
+      </c>
+      <c r="E213" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F213" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G213" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H213" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B214" t="str">
+        <v>19:03</v>
+      </c>
+      <c r="C214" t="str">
+        <v>src/i18n/index.ts</v>
+      </c>
+      <c r="D214" t="str">
+        <v>BL-067: נוספו 10 מפתחות EN+HE — setup_title/subtitle/placeholder/cta; dashboard_hello/send_now/pending_greetings/pending_singular/pending_plural/first_greeting</v>
+      </c>
+      <c r="E214" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F214" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G214" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H214" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B215" t="str">
+        <v>19:04</v>
+      </c>
+      <c r="C215" t="str">
+        <v>src/screens/DashboardScreen.tsx</v>
+      </c>
+      <c r="D215" t="str">
+        <v>BL-067: hero banner — 'היי {name}' כשיש שם; pending greetings count בכותרת; כפתור 'שלח ברכה עכשיו'; פאנל 'ברכות ממתינות' עם items קליקביליים → Quick Send (BL-064); pendingItems useMemo</v>
+      </c>
+      <c r="E215" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F215" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G215" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H215" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B216" t="str">
+        <v>19:05</v>
+      </c>
+      <c r="C216" t="str">
+        <v>src/services/aiSuggestionsService.ts</v>
+      </c>
+      <c r="D216" t="str">
+        <v>BL-065 MVP: נוסף relationshipType ל-AISuggestionsContext; PROFESSIONAL_RELATIONSHIPS set (client/business_partner/manager/employee/mentor); resolveTone מחזיר professional מינימום לסוגי קשר מקצועיים; import RelationshipType מ-types</v>
+      </c>
+      <c r="E216" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F216" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G216" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H216" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B217" t="str">
+        <v>19:06</v>
+      </c>
+      <c r="C217" t="str">
+        <v>src/screens/GreetingEditorScreen.tsx</v>
+      </c>
+      <c r="D217" t="str">
+        <v>BL-065: נוסף relationshipType: selectedContact.relationshipType ל-getAISuggestions call</v>
+      </c>
+      <c r="E217" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F217" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G217" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H217" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B218" t="str">
+        <v>19:07</v>
+      </c>
+      <c r="C218" t="str">
+        <v>src/screens/DashboardScreen.tsx</v>
+      </c>
+      <c r="D218" t="str">
+        <v>BL-065: נוסף relationshipType: contact.relationshipType ל-getAISuggestions call ב-openQuickSend</v>
+      </c>
+      <c r="E218" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F218" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G218" t="str">
+        <v>Agent 1</v>
+      </c>
+      <c r="H218" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H210"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H218"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H218"/>
+  <dimension ref="A1:H232"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -5834,9 +5834,373 @@
         <v>done</v>
       </c>
     </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B219" t="str">
+        <v>10:00</v>
+      </c>
+      <c r="C219" t="str">
+        <v>src/screens/CalendarScreen.tsx</v>
+      </c>
+      <c r="D219" t="str">
+        <v>תוקן RTL: חצי ניווט חודש (הקודם/הבא) מחליפים אייקון ב-RTL — ChevronLeft/Right מתחלפים לפי lang==='he'; dir='ltr' על div הניווט למניעת היפוך flex; ייבוא useLang</v>
+      </c>
+      <c r="E219" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F219" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G219" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H219" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B220" t="str">
+        <v>10:00</v>
+      </c>
+      <c r="C220" t="str">
+        <v>src/screens/CalendarScreen.tsx</v>
+      </c>
+      <c r="D220" t="str">
+        <v>תוקן לוגיקת birthdayMap — Hebrew ו-Gregorian birthday מטופלים כעת כשני אירועים עצמאיים; איש קשר עם שניהם יופיע פעמיים בלוח השנה; שינוי type ל-BirthdayEntry[]</v>
+      </c>
+      <c r="E220" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F220" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G220" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H220" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B221" t="str">
+        <v>10:00</v>
+      </c>
+      <c r="C221" t="str">
+        <v>src/utils/hebrewDateUtils.ts</v>
+      </c>
+      <c r="D221" t="str">
+        <v>נוספה formatHebrewBirthdayDisplay() — ממירה 'DD-MM' לפורמט תצוגה 'כ״א בטבת' (גמטריה + שם חודש עברי)</v>
+      </c>
+      <c r="E221" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F221" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G221" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H221" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B222" t="str">
+        <v>10:00</v>
+      </c>
+      <c r="C222" t="str">
+        <v>src/screens/ContactFormScreen.tsx</v>
+      </c>
+      <c r="D222" t="str">
+        <v>תוקן dropdown יום בלידה עברית — מציג גמטריה (א, ב... ל) במקום מספרים; ייבוא gematriya מ-@hebcal/core</v>
+      </c>
+      <c r="E222" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F222" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G222" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H222" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B223" t="str">
+        <v>10:00</v>
+      </c>
+      <c r="C223" t="str">
+        <v>src/screens/ContactDetailScreen.tsx</v>
+      </c>
+      <c r="D223" t="str">
+        <v>נוסף שורת 'יום הולדת עברי' בפרטי איש קשר (Premium) — מציג פורמט כ״א בטבת; ייבוא formatHebrewBirthdayDisplay</v>
+      </c>
+      <c r="E223" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F223" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G223" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H223" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B224" t="str">
+        <v>10:00</v>
+      </c>
+      <c r="C224" t="str">
+        <v>src/i18n/index.ts</v>
+      </c>
+      <c r="D224" t="str">
+        <v>נוסף מפתח contactDetail_hebrewBirthday — EN: 'Hebrew Birthday', HE: 'יום הולדת עברי'</v>
+      </c>
+      <c r="E224" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F224" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G224" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H224" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B225" t="str">
+        <v>10:01</v>
+      </c>
+      <c r="C225" t="str">
+        <v>agent_state/qa_status.json</v>
+      </c>
+      <c r="D225" t="str">
+        <v>נוספו T121 (RTL calendar arrows) ו-T122 (Hebrew birthday display) — שניהם ✅</v>
+      </c>
+      <c r="E225" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F225" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G225" t="str">
+        <v>Documentation</v>
+      </c>
+      <c r="H225" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B226" t="str">
+        <v>10:30</v>
+      </c>
+      <c r="C226" t="str">
+        <v>src/screens/PaymeScreen.tsx</v>
+      </c>
+      <c r="D226" t="str">
+        <v>תוקן BUG-049 — PaymeScreen שוכתב כמסך הדגמה: הוסרו form/plan picker/createPaymentLink; נוסף באנר הדגמה עם payme_demoNotice ו-כפתור 'הפעל פרימיום (הדגמה)' שמפעיל activatePremium() ומנווט ל-/dashboard</v>
+      </c>
+      <c r="E226" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F226" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G226" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H226" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B227" t="str">
+        <v>10:30</v>
+      </c>
+      <c r="C227" t="str">
+        <v>src/i18n/index.ts</v>
+      </c>
+      <c r="D227" t="str">
+        <v>נוספו 2 מפתחות i18n: payme_demoNotice (EN: 'This is a demo version — no real payment is required' / HE: 'זוהי גרסת הדגמה — לא נדרש תשלום אמיתי') ו-payme_activateDemo (EN/HE: 'Activate Premium (Demo)' / 'הפעל פרימיום (הדגמה)')</v>
+      </c>
+      <c r="E227" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F227" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G227" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H227" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B228" t="str">
+        <v>10:31</v>
+      </c>
+      <c r="C228" t="str">
+        <v>BUG_REPORT.md</v>
+      </c>
+      <c r="D228" t="str">
+        <v>נוסף BUG-049 — PaymeScreen זורק שגיאת תשלום; משתמשים לא יכולים לגשת לפרמיום ללא קוד קופון; סומן כ-fixed</v>
+      </c>
+      <c r="E228" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F228" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G228" t="str">
+        <v>Documentation</v>
+      </c>
+      <c r="H228" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B229" t="str">
+        <v>10:32</v>
+      </c>
+      <c r="C229" t="str">
+        <v>agent_state/qa_status.json</v>
+      </c>
+      <c r="D229" t="str">
+        <v>נוסף T123 (Premium upgrade path — demo activation flow) — ✅</v>
+      </c>
+      <c r="E229" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F229" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G229" t="str">
+        <v>Documentation</v>
+      </c>
+      <c r="H229" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B230" t="str">
+        <v>11:00</v>
+      </c>
+      <c r="C230" t="str">
+        <v>src/screens/UpgradeScreen.tsx</v>
+      </c>
+      <c r="D230" t="str">
+        <v>תוקן BUG-050 — נוסף כפתור 'שדרג עכשיו' (upgrade_now) גדול ורחב מלא מעל חלק הקופון ב-UpgradeScreen; כפתור gradient amber→orange, מנווט ל-/payment</v>
+      </c>
+      <c r="E230" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F230" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G230" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H230" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B231" t="str">
+        <v>11:00</v>
+      </c>
+      <c r="C231" t="str">
+        <v>src/i18n/index.ts</v>
+      </c>
+      <c r="D231" t="str">
+        <v>נוסף מפתח i18n upgrade_now — EN: 'Upgrade Now' / HE: 'שדרג עכשיו' — בשני הלוקאלים</v>
+      </c>
+      <c r="E231" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F231" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G231" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H231" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B232" t="str">
+        <v>11:01</v>
+      </c>
+      <c r="C232" t="str">
+        <v>BUG_REPORT.md</v>
+      </c>
+      <c r="D232" t="str">
+        <v>נוסף BUG-050 — כפתור 'שדרג עכשיו' לא גלוי מעל חלק הקופון ב-UpgradeScreen; סומן כ-fixed</v>
+      </c>
+      <c r="E232" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F232" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G232" t="str">
+        <v>Documentation</v>
+      </c>
+      <c r="H232" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H218"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H232"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H232"/>
+  <dimension ref="A1:H235"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -6198,9 +6198,87 @@
         <v>done</v>
       </c>
     </row>
+    <row r="233">
+      <c r="A233" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B233" t="str">
+        <v>11:30</v>
+      </c>
+      <c r="C233" t="str">
+        <v>src/screens/UpgradeScreen.tsx</v>
+      </c>
+      <c r="D233" t="str">
+        <v>תוקן BUG-051 — הוסר כפתור upgrade_cta/CreditCard הכפול; נשמר רק כפתור upgrade_now/Crown מעל חלק הקופון; הוסר import של CreditCard שלא בשימוש</v>
+      </c>
+      <c r="E233" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F233" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G233" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H233" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B234" t="str">
+        <v>11:30</v>
+      </c>
+      <c r="C234" t="str">
+        <v>src/screens/PaymeScreen.tsx</v>
+      </c>
+      <c r="D234" t="str">
+        <v>תוקן BUG-052 — שינויי מצב הדגמה של PaymeScreen לא הועלו ל-git; הועלה הגרסה הנכונה: מסך הדגמה עם payme_demoNotice ו-payme_activateDemo ללא form/createPaymentLink</v>
+      </c>
+      <c r="E234" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F234" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G234" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H234" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B235" t="str">
+        <v>11:31</v>
+      </c>
+      <c r="C235" t="str">
+        <v>BUG_REPORT.md</v>
+      </c>
+      <c r="D235" t="str">
+        <v>נוספו BUG-051 ו-BUG-052 — כפתור CTA כפול ב-UpgradeScreen וגרסת PaymeScreen שלא הועלתה; שניהם סומנו כ-fixed</v>
+      </c>
+      <c r="E235" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F235" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G235" t="str">
+        <v>Documentation</v>
+      </c>
+      <c r="H235" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H232"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H235"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H235"/>
+  <dimension ref="A1:H241"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -6276,9 +6276,165 @@
         <v>done</v>
       </c>
     </row>
+    <row r="236">
+      <c r="A236" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B236" t="str">
+        <v>12:00</v>
+      </c>
+      <c r="C236" t="str">
+        <v>src/screens/ContactFormScreen.tsx</v>
+      </c>
+      <c r="D236" t="str">
+        <v>תוקן BUG-053 — נוסף dir='ltr' לשני שדות תאריך (lastContactDate ו-birthday) כדי שלוח שנה ייפתח בלחיצה במצב RTL</v>
+      </c>
+      <c r="E236" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F236" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G236" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H236" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B237" t="str">
+        <v>12:00</v>
+      </c>
+      <c r="C237" t="str">
+        <v>src/screens/ContactFormScreen.tsx</v>
+      </c>
+      <c r="D237" t="str">
+        <v>תוקן BUG-054 — הועלו שינויי Bug Fix 1 שלא הועלו: gematriya(d) כתווית ביום עברי, import של gematriya</v>
+      </c>
+      <c r="E237" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F237" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G237" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H237" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B238" t="str">
+        <v>12:00</v>
+      </c>
+      <c r="C238" t="str">
+        <v>src/utils/hebrewDateUtils.ts</v>
+      </c>
+      <c r="D238" t="str">
+        <v>הועלה פונקציית formatHebrewBirthdayDisplay — ממיר DD-MM לפורמט 'כ״א בטבת'</v>
+      </c>
+      <c r="E238" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F238" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G238" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H238" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B239" t="str">
+        <v>12:00</v>
+      </c>
+      <c r="C239" t="str">
+        <v>src/screens/ContactDetailScreen.tsx</v>
+      </c>
+      <c r="D239" t="str">
+        <v>הועלה שורת תצוגת יום הולדת עברי ב-ContactDetailScreen עם formatHebrewBirthdayDisplay</v>
+      </c>
+      <c r="E239" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F239" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G239" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H239" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B240" t="str">
+        <v>12:00</v>
+      </c>
+      <c r="C240" t="str">
+        <v>src/screens/CalendarScreen.tsx</v>
+      </c>
+      <c r="D240" t="str">
+        <v>הועלו תיקוני Bug Fix 1: חצי ניווט RTL תקינים, סוג BirthdayEntry לאירועי יום הולדת עברי/גרגוריאני עצמאיים</v>
+      </c>
+      <c r="E240" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F240" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G240" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H240" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B241" t="str">
+        <v>12:01</v>
+      </c>
+      <c r="C241" t="str">
+        <v>BUG_REPORT.md</v>
+      </c>
+      <c r="D241" t="str">
+        <v>נוספו BUG-053 ו-BUG-054 — שדות תאריך לא פותחים לוח שנה ב-RTL; יום עברי לא בגמטריה (שינויים לא הועלו); שניהם סומנו כ-fixed</v>
+      </c>
+      <c r="E241" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F241" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G241" t="str">
+        <v>Documentation</v>
+      </c>
+      <c r="H241" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H235"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H241"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H241"/>
+  <dimension ref="A1:H244"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -6432,9 +6432,87 @@
         <v>done</v>
       </c>
     </row>
+    <row r="242">
+      <c r="A242" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B242" t="str">
+        <v>13:00</v>
+      </c>
+      <c r="C242" t="str">
+        <v>src/index.css</v>
+      </c>
+      <c r="D242" t="str">
+        <v>תוקן BUG-055 — נוספו עיצוב CSS ל-::-webkit-calendar-picker-indicator: גודל 20×20px, opacity 0.65, hover עם רקע var(--color-surface-2), filter: invert(var(--calendar-picker-invert)) לנראות בתמה כהה</v>
+      </c>
+      <c r="E242" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F242" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G242" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H242" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B243" t="str">
+        <v>13:00</v>
+      </c>
+      <c r="C243" t="str">
+        <v>src/data/themes.ts</v>
+      </c>
+      <c r="D243" t="str">
+        <v>נוספה משתנה CSS --calendar-picker-invert ב-applyTheme: '1' לתמות כהות (isDark), '0' לתמות בהירות</v>
+      </c>
+      <c r="E243" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F243" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G243" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H243" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B244" t="str">
+        <v>13:01</v>
+      </c>
+      <c r="C244" t="str">
+        <v>BUG_REPORT.md</v>
+      </c>
+      <c r="D244" t="str">
+        <v>נוסף BUG-055 — אייקון לוח שנה לא גלוי בתמה כהה; סומן כ-fixed</v>
+      </c>
+      <c r="E244" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F244" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G244" t="str">
+        <v>Documentation</v>
+      </c>
+      <c r="H244" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H241"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H244"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H244"/>
+  <dimension ref="A1:H247"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -6510,9 +6510,87 @@
         <v>done</v>
       </c>
     </row>
+    <row r="245">
+      <c r="A245" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B245" t="str">
+        <v>14:00</v>
+      </c>
+      <c r="C245" t="str">
+        <v>src/screens/ContactFormScreen.tsx</v>
+      </c>
+      <c r="D245" t="str">
+        <v>תוקן BUG-056 — נוספו refs (lastContactRef, birthdayRef) ופונקציית openDatePicker עם showPicker()/click() לשדות תאריך; onClick על כל שדה פותח לוח שנה בלחיצה בכל מקום</v>
+      </c>
+      <c r="E245" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F245" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G245" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H245" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B246" t="str">
+        <v>14:00</v>
+      </c>
+      <c r="C246" t="str">
+        <v>src/index.css</v>
+      </c>
+      <c r="D246" t="str">
+        <v>נוסף cursor: pointer ל-input[type='date'].form-input בהתאם לסגנון select.form-input הקיים</v>
+      </c>
+      <c r="E246" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F246" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G246" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H246" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B247" t="str">
+        <v>14:01</v>
+      </c>
+      <c r="C247" t="str">
+        <v>BUG_REPORT.md</v>
+      </c>
+      <c r="D247" t="str">
+        <v>נוסף BUG-056 — שדות תאריך לא פותחים לוח שנה בלחיצה על כל השדה; סומן כ-fixed</v>
+      </c>
+      <c r="E247" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F247" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G247" t="str">
+        <v>Documentation</v>
+      </c>
+      <c r="H247" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H244"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H247"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H247"/>
+  <dimension ref="A1:H249"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -6588,9 +6588,61 @@
         <v>done</v>
       </c>
     </row>
+    <row r="248">
+      <c r="A248" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B248" t="str">
+        <v>15:00</v>
+      </c>
+      <c r="C248" t="str">
+        <v>src/screens/ContactFormScreen.tsx</v>
+      </c>
+      <c r="D248" t="str">
+        <v>תוקן BUG-057 — דרופדאון יום הולדת עברי מאפסים לאחר בחירה: הוחלף useMemo של hbParts ב-useState של hbDay/hbMonth; ערך מקומי נשמר גם כשרק חלק אחד נבחר; כפתור ניקוי מאפס גם state מקומי</v>
+      </c>
+      <c r="E248" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F248" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G248" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H248" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B249" t="str">
+        <v>15:01</v>
+      </c>
+      <c r="C249" t="str">
+        <v>BUG_REPORT.md</v>
+      </c>
+      <c r="D249" t="str">
+        <v>נוסף BUG-057 — דרופדאון יום הולדת עברי מתאפסים לאחר בחירה חלקית; סומן כ-fixed</v>
+      </c>
+      <c r="E249" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F249" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G249" t="str">
+        <v>Documentation</v>
+      </c>
+      <c r="H249" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H247"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H249"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H249"/>
+  <dimension ref="A1:H251"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -6640,9 +6640,61 @@
         <v>done</v>
       </c>
     </row>
+    <row r="250">
+      <c r="A250" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B250" t="str">
+        <v>16:00</v>
+      </c>
+      <c r="C250" t="str">
+        <v>src/components/ui/Modal.tsx</v>
+      </c>
+      <c r="D250" t="str">
+        <v>תוקן BUG-058 — שדה תיאור בטופס קבוצה מאבד פוקוס אחרי כל תו: הוסר onClose מ-dependency array של useEffect הראשי; הוחלף ב-onCloseRef שמתעדכן ב-useEffect נפרד. הפוקוס-טרפ מופעל רק בפתיחה/סגירה של המודאל</v>
+      </c>
+      <c r="E250" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F250" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G250" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H250" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B251" t="str">
+        <v>16:01</v>
+      </c>
+      <c r="C251" t="str">
+        <v>BUG_REPORT.md</v>
+      </c>
+      <c r="D251" t="str">
+        <v>נוסף BUG-058 — שדה תיאור בטופס קבוצה מאבד פוקוס; סומן כ-fixed</v>
+      </c>
+      <c r="E251" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F251" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G251" t="str">
+        <v>Documentation</v>
+      </c>
+      <c r="H251" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H249"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H251"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H251"/>
+  <dimension ref="A1:H256"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -6692,9 +6692,139 @@
         <v>done</v>
       </c>
     </row>
+    <row r="252">
+      <c r="A252" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B252" t="str">
+        <v>00:00</v>
+      </c>
+      <c r="C252" t="str">
+        <v>index.html</v>
+      </c>
+      <c r="D252" t="str">
+        <v>תוקן BUG-059 — הוסף translate="no" ו-notranslate class למניעת תרגום Google Translate של תוכן האפליקציה</v>
+      </c>
+      <c r="E252" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F252" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G252" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H252" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B253" t="str">
+        <v>00:00</v>
+      </c>
+      <c r="C253" t="str">
+        <v>src/types/index.ts</v>
+      </c>
+      <c r="D253" t="str">
+        <v>הוסף שדה heDescription אופציונלי לממשק Holiday לתמיכה בתיאורי חגים בעברית</v>
+      </c>
+      <c r="E253" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F253" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G253" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H253" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B254" t="str">
+        <v>00:00</v>
+      </c>
+      <c r="C254" t="str">
+        <v>src/data/holidays.ts</v>
+      </c>
+      <c r="D254" t="str">
+        <v>תוקן BUG-060 — הוסף heDescription לכל 46 ערכי חגים לתצוגת תיאורים בעברית</v>
+      </c>
+      <c r="E254" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F254" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G254" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H254" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B255" t="str">
+        <v>00:00</v>
+      </c>
+      <c r="C255" t="str">
+        <v>src/screens/HolidayDetailScreen.tsx</v>
+      </c>
+      <c r="D255" t="str">
+        <v>עודכן מסך פרטי חג להציג heDescription כשהשפה עברית ויש תיאור עברי</v>
+      </c>
+      <c r="E255" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F255" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G255" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H255" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B256" t="str">
+        <v>00:00</v>
+      </c>
+      <c r="C256" t="str">
+        <v>src/screens/GroupsScreen.tsx</v>
+      </c>
+      <c r="D256" t="str">
+        <v>תוקן BUG-061 — ביטול כפילויות ברשימת חגים; תרגום שמות חגים ותוויות דת לפי שפה פעילה</v>
+      </c>
+      <c r="E256" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F256" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G256" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H256" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H251"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H256"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H256"/>
+  <dimension ref="A1:H257"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -6822,9 +6822,35 @@
         <v>done</v>
       </c>
     </row>
+    <row r="257">
+      <c r="A257" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B257" t="str">
+        <v>10:00</v>
+      </c>
+      <c r="C257" t="str">
+        <v>CLAUDE.md</v>
+      </c>
+      <c r="D257" t="str">
+        <v>נוסף כלל אימות פרומפטים — validation נדרש לפיצ'רים/באגים/שיפורים ותכנון בלבד; דילוג על steering פשוט, UI קטן, הבהרות; פורמט דוח עם Prompt Type/Clarity/Risk/Issues/Recommendation</v>
+      </c>
+      <c r="E257" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F257" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G257" t="str">
+        <v>Documentation</v>
+      </c>
+      <c r="H257" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H256"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H257"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H257"/>
+  <dimension ref="A1:H259"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -6848,9 +6848,61 @@
         <v>done</v>
       </c>
     </row>
+    <row r="258">
+      <c r="A258" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B258" t="str">
+        <v>10:30</v>
+      </c>
+      <c r="C258" t="str">
+        <v>src/context/AppContext.tsx</v>
+      </c>
+      <c r="D258" t="str">
+        <v>TEMP BL-070: נוסף TEMP_PREMIUM_UNLOCK = true — כל שערי Premium מושבתים זמנית לצורך בדיקות MVP; שורה אחת להחזרה ל-false לפני פרודקשן</v>
+      </c>
+      <c r="E258" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F258" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G258" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H258" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B259" t="str">
+        <v>10:30</v>
+      </c>
+      <c r="C259" t="str">
+        <v>BACKLOG.md</v>
+      </c>
+      <c r="D259" t="str">
+        <v>נוסף BL-070 — משימת תזכורת pre-launch: השבת TEMP_PREMIUM_UNLOCK לפני פרודקשן</v>
+      </c>
+      <c r="E259" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F259" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G259" t="str">
+        <v>Documentation</v>
+      </c>
+      <c r="H259" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H257"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H259"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H259"/>
+  <dimension ref="A1:H263"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -6900,9 +6900,113 @@
         <v>done</v>
       </c>
     </row>
+    <row r="260">
+      <c r="A260" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B260" t="str">
+        <v>11:00</v>
+      </c>
+      <c r="C260" t="str">
+        <v>src/screens/SettingsScreen.tsx</v>
+      </c>
+      <c r="D260" t="str">
+        <v>תוקן BUG-062 — כפתור שדרוג בהגדרות הציג mo/₪29 ב-RTL; הוחלף /mo ב-t('upgrade_month') ועטוף ב-span dir=ltr</v>
+      </c>
+      <c r="E260" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F260" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G260" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H260" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B261" t="str">
+        <v>11:10</v>
+      </c>
+      <c r="C261" t="str">
+        <v>src/screens/WhatsNewScreen.tsx</v>
+      </c>
+      <c r="D261" t="str">
+        <v>תוקן BUG-063 — ציר זמן ב-WhatsNew היה בצד שמאל גם ב-RTL; נוסף isRTL flag; ציר, נקודה ו-padding מחליפים צד לפי כיוון שפה</v>
+      </c>
+      <c r="E261" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F261" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G261" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H261" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B262" t="str">
+        <v>11:15</v>
+      </c>
+      <c r="C262" t="str">
+        <v>BUG_REPORT.md</v>
+      </c>
+      <c r="D262" t="str">
+        <v>עודכן סטטוס BUG-047 ו-BUG-048 מ-open ל-fixed (תוקנו ב-Sprint 11 — תיעוד היה מאחור); נוספו BUG-062 ו-BUG-063</v>
+      </c>
+      <c r="E262" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F262" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G262" t="str">
+        <v>Documentation</v>
+      </c>
+      <c r="H262" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B263" t="str">
+        <v>11:15</v>
+      </c>
+      <c r="C263" t="str">
+        <v>BACKLOG.md</v>
+      </c>
+      <c r="D263" t="str">
+        <v>BL-063 סומן ✅ Done (היה 📋 Backlog בטעות — תוקן ב-Sprint 11)</v>
+      </c>
+      <c r="E263" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F263" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G263" t="str">
+        <v>Documentation</v>
+      </c>
+      <c r="H263" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H259"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H263"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H263"/>
+  <dimension ref="A1:H265"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -7004,9 +7004,61 @@
         <v>done</v>
       </c>
     </row>
+    <row r="264">
+      <c r="A264" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B264" t="str">
+        <v>11:30</v>
+      </c>
+      <c r="C264" t="str">
+        <v>src/screens/SettingsScreen.tsx</v>
+      </c>
+      <c r="D264" t="str">
+        <v>תוקן BUG-064 — נקודת toggle התחילה תמיד בשמאל גם ב-RTL; עדכון ל-right-0.5 + translateX(-20px) בעברית</v>
+      </c>
+      <c r="E264" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F264" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G264" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H264" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B265" t="str">
+        <v>11:30</v>
+      </c>
+      <c r="C265" t="str">
+        <v>src/screens/HolidayRemindersScreen.tsx</v>
+      </c>
+      <c r="D265" t="str">
+        <v>תוקן BUG-064 — 2 toggles (enabled + channels) תוקנו ל-RTL; נוסף ייבוא useLang</v>
+      </c>
+      <c r="E265" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F265" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G265" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H265" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H263"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H265"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H265"/>
+  <dimension ref="A1:H270"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -7056,9 +7056,139 @@
         <v>done</v>
       </c>
     </row>
+    <row r="266">
+      <c r="A266" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B266" t="str">
+        <v>12:00</v>
+      </c>
+      <c r="C266" t="str">
+        <v>src/screens/UpgradeScreen.tsx</v>
+      </c>
+      <c r="D266" t="str">
+        <v>תוקן BUG-065 — ml-1 הוחלף ב-ms-1 (margin-inline-start) כדי שהרווח יהיה בצד הנכון ב-RTL</v>
+      </c>
+      <c r="E266" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F266" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G266" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H266" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B267" t="str">
+        <v>12:00</v>
+      </c>
+      <c r="C267" t="str">
+        <v>src/screens/CalendarScreen.tsx</v>
+      </c>
+      <c r="D267" t="str">
+        <v>תוקן BUG-065 — שני ml-2 בכותרות קטגוריות הוחלפו ב-ms-2 כדי שספירת הפריטים תופיע בצד הנכון ב-RTL</v>
+      </c>
+      <c r="E267" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F267" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G267" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H267" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B268" t="str">
+        <v>12:00</v>
+      </c>
+      <c r="C268" t="str">
+        <v>src/screens/GreetingEditorScreen.tsx</v>
+      </c>
+      <c r="D268" t="str">
+        <v>תוקן BUG-065 — ml-1 בסרגל הצעות AI הוחלף ב-ms-1</v>
+      </c>
+      <c r="E268" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F268" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G268" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H268" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B269" t="str">
+        <v>12:00</v>
+      </c>
+      <c r="C269" t="str">
+        <v>src/screens/UpgradeScreen.tsx</v>
+      </c>
+      <c r="D269" t="str">
+        <v>תוקן BUG-066 — המלצות המשתמשים (testimonials) היו hardcoded באנגלית; הועברו למפתחות i18n עם תרגום לעברית</v>
+      </c>
+      <c r="E269" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F269" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G269" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H269" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B270" t="str">
+        <v>12:00</v>
+      </c>
+      <c r="C270" t="str">
+        <v>src/i18n/index.ts</v>
+      </c>
+      <c r="D270" t="str">
+        <v>נוספו 6 מפתחות i18n לעדויות משתמשים ב-UpgradeScreen (upgrade_testimonial_1/2_name/role/quote) — EN + HE</v>
+      </c>
+      <c r="E270" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F270" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G270" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H270" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H265"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H270"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H270"/>
+  <dimension ref="A1:H276"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -7186,9 +7186,165 @@
         <v>done</v>
       </c>
     </row>
+    <row r="271">
+      <c r="A271" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B271" t="str">
+        <v>12:30</v>
+      </c>
+      <c r="C271" t="str">
+        <v>src/screens/CalendarScreen.tsx</v>
+      </c>
+      <c r="D271" t="str">
+        <v>תוקן BUG-067 — borderLeft של כרטיסי ימי הולדת עבר לצד הנכון ב-RTL באמצעות computed property key</v>
+      </c>
+      <c r="E271" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F271" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G271" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H271" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B272" t="str">
+        <v>12:30</v>
+      </c>
+      <c r="C272" t="str">
+        <v>src/screens/DashboardScreen.tsx</v>
+      </c>
+      <c r="D272" t="str">
+        <v>תוקן BUG-067 — borderLeft של כרטיסי התראות חגים עבר ל-RTL; נוסף ייבוא useLang</v>
+      </c>
+      <c r="E272" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F272" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G272" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H272" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B273" t="str">
+        <v>12:30</v>
+      </c>
+      <c r="C273" t="str">
+        <v>src/screens/GreetingEditorScreen.tsx</v>
+      </c>
+      <c r="D273" t="str">
+        <v>תוקן BUG-067 — borderLeft של בלוק ציטוט חג עבר ל-RTL; נוסף ייבוא useLang</v>
+      </c>
+      <c r="E273" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F273" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G273" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H273" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B274" t="str">
+        <v>12:30</v>
+      </c>
+      <c r="C274" t="str">
+        <v>src/screens/ContactFormScreen.tsx</v>
+      </c>
+      <c r="D274" t="str">
+        <v>תוקן BUG-067 — borderLeft של קטע שדות Premium עבר ל-RTL; נוסף ייבוא useLang</v>
+      </c>
+      <c r="E274" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F274" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G274" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H274" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B275" t="str">
+        <v>12:30</v>
+      </c>
+      <c r="C275" t="str">
+        <v>src/screens/HolidayDetailScreen.tsx</v>
+      </c>
+      <c r="D275" t="str">
+        <v>תוקן BUG-067 — borderLeft של הערות רגישות עבר ל-RTL</v>
+      </c>
+      <c r="E275" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F275" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G275" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H275" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B276" t="str">
+        <v>12:30</v>
+      </c>
+      <c r="C276" t="str">
+        <v>src/screens/GroupsScreen.tsx</v>
+      </c>
+      <c r="D276" t="str">
+        <v>תוקן BUG-067 — borderLeft של כרטיסי קבוצות עבר ל-RTL</v>
+      </c>
+      <c r="E276" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F276" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G276" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H276" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H270"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H276"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H276"/>
+  <dimension ref="A1:H280"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -7342,9 +7342,113 @@
         <v>done</v>
       </c>
     </row>
+    <row r="277">
+      <c r="A277" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B277" t="str">
+        <v>13:00</v>
+      </c>
+      <c r="C277" t="str">
+        <v>src/screens/GroupsScreen.tsx</v>
+      </c>
+      <c r="D277" t="str">
+        <v>תוקן BUG-068 — text-left הוחלף ב-text-start (3 מופעים) כדי שהיישור יעקוב אחרי כיוון הטקסט</v>
+      </c>
+      <c r="E277" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F277" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G277" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H277" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B278" t="str">
+        <v>13:00</v>
+      </c>
+      <c r="C278" t="str">
+        <v>src/screens/DashboardScreen.tsx</v>
+      </c>
+      <c r="D278" t="str">
+        <v>תוקן BUG-068 — text-left הוחלף ב-text-start (3 מופעים)</v>
+      </c>
+      <c r="E278" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F278" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G278" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H278" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B279" t="str">
+        <v>13:00</v>
+      </c>
+      <c r="C279" t="str">
+        <v>src/screens/SettingsScreen.tsx</v>
+      </c>
+      <c r="D279" t="str">
+        <v>תוקן BUG-068 — text-left הוחלף ב-text-start (5 מופעים); border-l-2 הוחלף ב-border-s-2 בהדגשת אזור הסכנה</v>
+      </c>
+      <c r="E279" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F279" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G279" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H279" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B280" t="str">
+        <v>13:00</v>
+      </c>
+      <c r="C280" t="str">
+        <v>src/screens/premium/ImportContactsScreen.tsx</v>
+      </c>
+      <c r="D280" t="str">
+        <v>תוקן BUG-068 — text-left בכותרות טבלת CSV הוחלף ב-text-start</v>
+      </c>
+      <c r="E280" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F280" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G280" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H280" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H276"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H280"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H280"/>
+  <dimension ref="A1:H282"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -7446,9 +7446,61 @@
         <v>done</v>
       </c>
     </row>
+    <row r="281">
+      <c r="A281" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B281" t="str">
+        <v>13:30</v>
+      </c>
+      <c r="C281" t="str">
+        <v>src/screens/SettingsScreen.tsx</v>
+      </c>
+      <c r="D281" t="str">
+        <v>תוקן BUG-069 — 5 סמלי ChevronRight בפריטי רשימה עטופו בתנאי RTL (ChevronLeft בעברית); נוסף ייבוא ChevronLeft</v>
+      </c>
+      <c r="E281" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F281" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G281" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H281" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B282" t="str">
+        <v>13:30</v>
+      </c>
+      <c r="C282" t="str">
+        <v>src/screens/OnboardingScreen.tsx</v>
+      </c>
+      <c r="D282" t="str">
+        <v>תוקן BUG-069 — ChevronRight בכפתור המשך עבר ל-ChevronLeft בעברית; נוסף ייבוא useLang</v>
+      </c>
+      <c r="E282" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F282" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G282" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H282" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H280"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H282"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H282"/>
+  <dimension ref="A1:H286"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -7498,9 +7498,113 @@
         <v>done</v>
       </c>
     </row>
+    <row r="283">
+      <c r="A283" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B283" t="str">
+        <v>14:00</v>
+      </c>
+      <c r="C283" t="str">
+        <v>src/components/ContactCard.tsx</v>
+      </c>
+      <c r="D283" t="str">
+        <v>תוקן BUG-070 — text-left → text-start; borderLeft של פס דחיפות עבר ל-RTL; נוסף ייבוא useLang</v>
+      </c>
+      <c r="E283" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F283" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G283" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H283" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B284" t="str">
+        <v>14:00</v>
+      </c>
+      <c r="C284" t="str">
+        <v>src/components/HolidayCard.tsx</v>
+      </c>
+      <c r="D284" t="str">
+        <v>תוקן BUG-070 — borderLeft של כרטיס חג מהיר עבר ל-RTL; נוסף ייבוא useLang</v>
+      </c>
+      <c r="E284" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F284" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G284" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H284" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B285" t="str">
+        <v>14:00</v>
+      </c>
+      <c r="C285" t="str">
+        <v>src/components/ui/Card.tsx</v>
+      </c>
+      <c r="D285" t="str">
+        <v>תוקן BUG-070 — prop accent: borderLeft עבר ל-RTL; נוסף ייבוא useLang</v>
+      </c>
+      <c r="E285" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F285" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G285" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H285" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B286" t="str">
+        <v>14:00</v>
+      </c>
+      <c r="C286" t="str">
+        <v>src/components/ChannelPicker.tsx</v>
+      </c>
+      <c r="D286" t="str">
+        <v>תוקן BUG-070 — text-left → text-start על ספן תוויות הערוצים</v>
+      </c>
+      <c r="E286" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F286" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G286" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H286" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H282"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H286"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H286"/>
+  <dimension ref="A1:H289"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -7602,9 +7602,87 @@
         <v>done</v>
       </c>
     </row>
+    <row r="287">
+      <c r="A287" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B287" t="str">
+        <v>14:30</v>
+      </c>
+      <c r="C287" t="str">
+        <v>src/screens/premium/BirthdayGreetingEditorScreen.tsx</v>
+      </c>
+      <c r="D287" t="str">
+        <v>תוקן BUG-071 — כל המחרוזות האנגליות hardcoded הועברו למפתחות i18n (כותרת, סגנונות, תצוגה מקדימה, ספירת תווים)</v>
+      </c>
+      <c r="E287" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F287" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G287" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H287" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B288" t="str">
+        <v>14:30</v>
+      </c>
+      <c r="C288" t="str">
+        <v>src/i18n/index.ts</v>
+      </c>
+      <c r="D288" t="str">
+        <v>נוספו 14 מפתחות i18n לעורך ברכות יום הולדת (birthday_greeting_* + birthday_tier_*) — EN + HE</v>
+      </c>
+      <c r="E288" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F288" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G288" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H288" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B289" t="str">
+        <v>14:30</v>
+      </c>
+      <c r="C289" t="str">
+        <v>src/screens/CalendarScreen.tsx</v>
+      </c>
+      <c r="D289" t="str">
+        <v>תוקן BUG-071 — aria-label של כפתור הסינון הוחלף ב-t('calendar_filterByReligion') במקום מחרוזת hardcoded</v>
+      </c>
+      <c r="E289" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F289" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G289" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H289" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H286"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H289"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H289"/>
+  <dimension ref="A1:H291"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -7680,9 +7680,61 @@
         <v>done</v>
       </c>
     </row>
+    <row r="290">
+      <c r="A290" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B290" t="str">
+        <v>15:00</v>
+      </c>
+      <c r="C290" t="str">
+        <v>src/screens/premium/ImportContactsScreen.tsx</v>
+      </c>
+      <c r="D290" t="str">
+        <v>תוקן BUG-072 — CONTACT_FIELDS הועבר לתוך הקומפוננטה עם t(); StepIndicator קיבל useT(); תוויות סטטיסטיקה הוחלפו ב-t()</v>
+      </c>
+      <c r="E290" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F290" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G290" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H290" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B291" t="str">
+        <v>15:00</v>
+      </c>
+      <c r="C291" t="str">
+        <v>src/i18n/index.ts</v>
+      </c>
+      <c r="D291" t="str">
+        <v>נוספו 13 מפתחות i18n לייבוא אנשי קשר (import_field_* + import_stat_*) — EN + HE</v>
+      </c>
+      <c r="E291" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F291" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G291" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H291" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H289"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H291"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H291"/>
+  <dimension ref="A1:H292"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -7732,9 +7732,35 @@
         <v>done</v>
       </c>
     </row>
+    <row r="292">
+      <c r="A292" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B292" t="str">
+        <v>15:15</v>
+      </c>
+      <c r="C292" t="str">
+        <v>src/screens/GroupsScreen.tsx</v>
+      </c>
+      <c r="D292" t="str">
+        <v>תוקן BUG-073 — כפתורי עריכה ומחיקה של קבוצות קיבלו aria-label לנגישות</v>
+      </c>
+      <c r="E292" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F292" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G292" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H292" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H291"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H292"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H292"/>
+  <dimension ref="A1:H293"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -7758,9 +7758,35 @@
         <v>done</v>
       </c>
     </row>
+    <row r="293">
+      <c r="A293" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B293" t="str">
+        <v>15:30</v>
+      </c>
+      <c r="C293" t="str">
+        <v>src/components/ui/Input.tsx</v>
+      </c>
+      <c r="D293" t="str">
+        <v>תיקון BUG-074: ממשק Input לא היה מודע ל-RTL — האייקונים הופיעו בצד הלא נכון בעברית. הוספת useLang ו-isRTL לניהול מיקום האייקון והריפוד בהתאם לכיוון הטקסט.</v>
+      </c>
+      <c r="E293" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F293" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G293" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H293" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H292"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H293"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H293"/>
+  <dimension ref="A1:H295"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -7784,9 +7784,61 @@
         <v>done</v>
       </c>
     </row>
+    <row r="294">
+      <c r="A294" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B294" t="str">
+        <v>15:45</v>
+      </c>
+      <c r="C294" t="str">
+        <v>src/screens/PrivacyScreen.tsx</v>
+      </c>
+      <c r="D294" t="str">
+        <v>תיקון BUG-075: כל תוכן מסך הפרטיות היה קשיח באנגלית. הועבר מערך SECTIONS לתוך הקומפוננטה עם שימוש ב-t() לכל הכותרות ותוכן הסעיפים.</v>
+      </c>
+      <c r="E294" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F294" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G294" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H294" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B295" t="str">
+        <v>15:45</v>
+      </c>
+      <c r="C295" t="str">
+        <v>src/i18n/index.ts</v>
+      </c>
+      <c r="D295" t="str">
+        <v>תיקון BUG-075: הוספת 25 מפתחות i18n חדשים (EN+HE) עבור מסך הפרטיות: privacy_hero_title, privacy_last_updated, privacy_badge, privacy_intro, privacy_footer, privacy_s1 עד privacy_s10 (כותרות וגוף טקסט).</v>
+      </c>
+      <c r="E295" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F295" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G295" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H295" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H293"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H295"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H295"/>
+  <dimension ref="A1:H301"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -7836,9 +7836,165 @@
         <v>done</v>
       </c>
     </row>
+    <row r="296">
+      <c r="A296" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B296" t="str">
+        <v>16:00</v>
+      </c>
+      <c r="C296" t="str">
+        <v>src/screens/premium/BirthdayGreetingEditorScreen.tsx</v>
+      </c>
+      <c r="D296" t="str">
+        <v>תיקון BUG-076: החלפת מחלקות CSS פיזיות (ml-*, mr-*, text-right) בתכונות לוגיות (ms-*, me-*, text-end) לתמיכה נכונה ב-RTL.</v>
+      </c>
+      <c r="E296" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F296" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G296" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H296" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B297" t="str">
+        <v>16:00</v>
+      </c>
+      <c r="C297" t="str">
+        <v>src/App.tsx</v>
+      </c>
+      <c r="D297" t="str">
+        <v>תיקון BUG-076: החלפת מחלקות CSS פיזיות (ml-*, mr-*, text-right) בתכונות לוגיות (ms-*, me-*, text-end) לתמיכה נכונה ב-RTL.</v>
+      </c>
+      <c r="E297" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F297" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G297" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H297" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B298" t="str">
+        <v>16:00</v>
+      </c>
+      <c r="C298" t="str">
+        <v>src/screens/DashboardScreen.tsx</v>
+      </c>
+      <c r="D298" t="str">
+        <v>תיקון BUG-076: החלפת מחלקות CSS פיזיות (ml-*, mr-*, text-right) בתכונות לוגיות (ms-*, me-*, text-end) לתמיכה נכונה ב-RTL.</v>
+      </c>
+      <c r="E298" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F298" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G298" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H298" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B299" t="str">
+        <v>16:00</v>
+      </c>
+      <c r="C299" t="str">
+        <v>src/components/MediaAttachmentPicker.tsx</v>
+      </c>
+      <c r="D299" t="str">
+        <v>תיקון BUG-076: החלפת מחלקות CSS פיזיות (ml-*, mr-*, text-right) בתכונות לוגיות (ms-*, me-*, text-end) לתמיכה נכונה ב-RTL.</v>
+      </c>
+      <c r="E299" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F299" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G299" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H299" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B300" t="str">
+        <v>16:00</v>
+      </c>
+      <c r="C300" t="str">
+        <v>src/screens/GreetingEditorScreen.tsx</v>
+      </c>
+      <c r="D300" t="str">
+        <v>תיקון BUG-076: החלפת מחלקות CSS פיזיות (ml-*, mr-*, text-right) בתכונות לוגיות (ms-*, me-*, text-end) לתמיכה נכונה ב-RTL.</v>
+      </c>
+      <c r="E300" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F300" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G300" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H300" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B301" t="str">
+        <v>16:00</v>
+      </c>
+      <c r="C301" t="str">
+        <v>src/screens/WhatsNewScreen.tsx</v>
+      </c>
+      <c r="D301" t="str">
+        <v>תיקון BUG-076: החלפת מחלקות CSS פיזיות (ml-*, mr-*, text-right) בתכונות לוגיות (ms-*, me-*, text-end) לתמיכה נכונה ב-RTL.</v>
+      </c>
+      <c r="E301" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F301" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G301" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H301" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H295"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H301"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H301"/>
+  <dimension ref="A1:H302"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -7992,9 +7992,35 @@
         <v>done</v>
       </c>
     </row>
+    <row r="302">
+      <c r="A302" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B302" t="str">
+        <v>16:10</v>
+      </c>
+      <c r="C302" t="str">
+        <v>src/screens/CalendarScreen.tsx</v>
+      </c>
+      <c r="D302" t="str">
+        <v>תיקון: החלפת mr-1 ml-1 (מרווחים פיזיים סימטריים) ב-mx-1 (מרווח אופקי לוגי) על span תאריך לידה עברי.</v>
+      </c>
+      <c r="E302" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F302" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G302" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H302" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H301"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H302"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H302"/>
+  <dimension ref="A1:H304"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -8018,9 +8018,61 @@
         <v>done</v>
       </c>
     </row>
+    <row r="303">
+      <c r="A303" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B303" t="str">
+        <v>16:15</v>
+      </c>
+      <c r="C303" t="str">
+        <v>agent_state/qa_status.json</v>
+      </c>
+      <c r="D303" t="str">
+        <v>עדכון qa_status.json — הוספת רשומות BUG-074/075/076 (status: fixed + fixedAt) ורשומות T127/T128/T129 לרשימת ה-QA.</v>
+      </c>
+      <c r="E303" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F303" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G303" t="str">
+        <v>Documentation</v>
+      </c>
+      <c r="H303" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B304" t="str">
+        <v>16:15</v>
+      </c>
+      <c r="C304" t="str">
+        <v>scripts/make-qa-checklist.js</v>
+      </c>
+      <c r="D304" t="str">
+        <v>הוספת T127/T128/T129 למערך TESTS — בדיקות QA עבור BUG-074/075/076.</v>
+      </c>
+      <c r="E304" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F304" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G304" t="str">
+        <v>Documentation</v>
+      </c>
+      <c r="H304" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H302"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H304"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H304"/>
+  <dimension ref="A1:H308"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -8070,9 +8070,113 @@
         <v>done</v>
       </c>
     </row>
+    <row r="305">
+      <c r="A305" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B305" t="str">
+        <v>16:30</v>
+      </c>
+      <c r="C305" t="str">
+        <v>src/services/communicationService.ts</v>
+      </c>
+      <c r="D305" t="str">
+        <v>BUG-077 verified — encodeURIComponent in buildWhatsAppUrl confirmed; all WhatsApp paths funnel through it; no code change needed.</v>
+      </c>
+      <c r="E305" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F305" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G305" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H305" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B306" t="str">
+        <v>16:35</v>
+      </c>
+      <c r="C306" t="str">
+        <v>src/components/ChannelPicker.tsx</v>
+      </c>
+      <c r="D306" t="str">
+        <v>BUG-078: added voice hint Modal shown after WhatsApp opens when media.type===audio; stays until dismissed; RTL-ready.</v>
+      </c>
+      <c r="E306" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F306" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G306" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H306" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B307" t="str">
+        <v>16:35</v>
+      </c>
+      <c r="C307" t="str">
+        <v>src/components/WhatsAppButton.tsx</v>
+      </c>
+      <c r="D307" t="str">
+        <v>BUG-078: added showVoiceHint Modal; fires on handleSend when media.type===audio; same pattern as image clipboard hint.</v>
+      </c>
+      <c r="E307" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F307" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G307" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H307" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B308" t="str">
+        <v>16:35</v>
+      </c>
+      <c r="C308" t="str">
+        <v>src/i18n/index.ts</v>
+      </c>
+      <c r="D308" t="str">
+        <v>BUG-078: added 2 i18n keys EN+HE: whatsapp_voice_hint_title, whatsapp_voice_hint_body.</v>
+      </c>
+      <c r="E308" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F308" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G308" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H308" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H304"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H308"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H308"/>
+  <dimension ref="A1:H310"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -8174,9 +8174,61 @@
         <v>done</v>
       </c>
     </row>
+    <row r="309">
+      <c r="A309" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B309" t="str">
+        <v>17:00</v>
+      </c>
+      <c r="C309" t="str">
+        <v>src/data/holidays.ts</v>
+      </c>
+      <c r="D309" t="str">
+        <v>BUG-079 (BL-074): 14 רשומות חגים יהודיים חסרים נוספו - לג בעומר, שמחת תורה, תשעה באב, 17 בתמוז, 10 בטבת, תענית אסתר, צום גדליה (2025+2026 לכל אחד); hebcalDate() לתאריכים; type fast/minor/major; EN+HE</v>
+      </c>
+      <c r="E309" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F309" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G309" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H309" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B310" t="str">
+        <v>17:15</v>
+      </c>
+      <c r="C310" t="str">
+        <v>src/screens/GreetingEditorScreen.tsx</v>
+      </c>
+      <c r="D310" t="str">
+        <v>BUG-080 (BL-073): כפילות חגים בתפריט Event Type תוקנה - useMemo dedup by name (upcoming-first); יבוא useMemo נוסף</v>
+      </c>
+      <c r="E310" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F310" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G310" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H310" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H308"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H310"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H310"/>
+  <dimension ref="A1:H312"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -8226,9 +8226,61 @@
         <v>done</v>
       </c>
     </row>
+    <row r="311">
+      <c r="A311" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B311" t="str">
+        <v>18:00</v>
+      </c>
+      <c r="C311" t="str">
+        <v>src/screens/DashboardScreen.tsx</v>
+      </c>
+      <c r="D311" t="str">
+        <v>BL-064: ChannelPicker שולב ב-Quick Send Panel (מחליף כפתור WhatsApp ישיר); כפתור שלח ברכה נוסף לכרטיסי חג היום ומחר; ייבוא ChannelPicker וstate channelPickerData; הוסר openWhatsApp שאינו בשימוש</v>
+      </c>
+      <c r="E311" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F311" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G311" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H311" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B312" t="str">
+        <v>18:01</v>
+      </c>
+      <c r="C312" t="str">
+        <v>src/i18n/index.ts</v>
+      </c>
+      <c r="D312" t="str">
+        <v>BL-064: 2 מפתחות i18n חדשים (EN+HE): dashboard_quick_send_channel, dashboard_send_greeting</v>
+      </c>
+      <c r="E312" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F312" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G312" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H312" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H310"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H312"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H312"/>
+  <dimension ref="A1:H313"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -8278,9 +8278,35 @@
         <v>done</v>
       </c>
     </row>
+    <row r="313">
+      <c r="A313" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B313" t="str">
+        <v>20:00</v>
+      </c>
+      <c r="C313" t="str">
+        <v>src/data/holidays.ts</v>
+      </c>
+      <c r="D313" t="str">
+        <v>BL-077: הוחלפה שיטת הגדרת חגים יהודיים — מ-hardcoded תאריכים שנתיים לגנרציה דינמית ב-runtime ע״י @hebcal/core (Israel mode); 17 תבניות Hebrew (HebrewTemplate) + YEAR_RANGE=[שנה-1..שנה+2]; תאריכים גרגוריאניים (חג המולד, רמדאן וכו׳) נשארים סטטיים; כל IDs, exports וממשקי Holiday נשמרו ללא שינוי</v>
+      </c>
+      <c r="E313" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F313" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G313" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H313" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H312"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H313"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H313"/>
+  <dimension ref="A1:H314"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -8304,9 +8304,35 @@
         <v>done</v>
       </c>
     </row>
+    <row r="314">
+      <c r="A314" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B314" t="str">
+        <v>21:00</v>
+      </c>
+      <c r="C314" t="str">
+        <v>src/data/holidays.ts</v>
+      </c>
+      <c r="D314" t="str">
+        <v>BL-077 תיקון: (1) 3 hebcalMatch שגויים תוקנו — simchat-torah: Shmini Atzeret, shiva-asar-btammuz: Tzom Tammuz, israel-independence-day: Yom HaAtzma'ut; (2) הוחלפה לוגיקת startsWith בטבלת mapping מבוקרת (exact match בלבד); (3) נוסף erevAdjust לשחזור תאריכי ערב (Rosh Hashana/Yom Kippur/Sukkot/Passover/Shavuot/Simchat Torah); (4) אומת: 21 השוואות BEFORE vs AFTER — אפס הבדלים</v>
+      </c>
+      <c r="E314" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F314" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G314" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H314" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H313"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H314"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H314"/>
+  <dimension ref="A1:H317"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -8330,9 +8330,87 @@
         <v>done</v>
       </c>
     </row>
+    <row r="315">
+      <c r="A315" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B315" t="str">
+        <v>22:00</v>
+      </c>
+      <c r="C315" t="str">
+        <v>src/screens/ContactsScreen.tsx</v>
+      </c>
+      <c r="D315" t="str">
+        <v>BL-046 — הוסרה הגבלת isPremium מכפתורי הייבוא בכרטיסיית אנשי קשר; כפתור הייבוא בכותרת ובמצב ריק מוצגים לכל המשתמשים; שמירת גייט ה-Premium בנתיב /import ברמת הנתיב</v>
+      </c>
+      <c r="E315" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F315" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G315" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H315" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B316" t="str">
+        <v>22:01</v>
+      </c>
+      <c r="C316" t="str">
+        <v>src/screens/premium/ImportContactsScreen.tsx</v>
+      </c>
+      <c r="D316" t="str">
+        <v>BL-047 — אומת: מפתח import_csvOnly (כרגע ניתן לייבא קובץ CSV בלבד) מוצג בתוך אזור ההעלאה; תרגום עברי קיים ב-i18n; אין שינוי קוד נדרש</v>
+      </c>
+      <c r="E316" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F316" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G316" t="str">
+        <v>Reviewer</v>
+      </c>
+      <c r="H316" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B317" t="str">
+        <v>22:02</v>
+      </c>
+      <c r="C317" t="str">
+        <v>src/screens/premium/ImportContactsScreen.tsx</v>
+      </c>
+      <c r="D317" t="str">
+        <v>BL-048 — אומת: כרטיסיית ייבוא מאנשי קשר במכשיר (גרדיאנט כחול, אייקון סמארטפון) מוצגת בראש המסך; נגישות ויזואלית מלאה; אין שינוי קוד נדרש</v>
+      </c>
+      <c r="E317" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F317" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G317" t="str">
+        <v>Reviewer</v>
+      </c>
+      <c r="H317" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H314"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H317"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H317"/>
+  <dimension ref="A1:H318"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -8408,9 +8408,35 @@
         <v>done</v>
       </c>
     </row>
+    <row r="318">
+      <c r="A318" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B318" t="str">
+        <v>22:30</v>
+      </c>
+      <c r="C318" t="str">
+        <v>BACKLOG.md / BACKLOG.csv</v>
+      </c>
+      <c r="D318" t="str">
+        <v>BL-078 נוסף לבקלוג — UX: תיקון הודעת "מצריכה מובייל" המטעה במדפדפן מובייל לייבוא אנשי קשר ממכשיר; עדיפות 🟢 נמוכה; לא יושם בספרינט הנוכחי</v>
+      </c>
+      <c r="E318" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F318" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G318" t="str">
+        <v>Documentation</v>
+      </c>
+      <c r="H318" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H317"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H318"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H318"/>
+  <dimension ref="A1:H319"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -8434,9 +8434,35 @@
         <v>done</v>
       </c>
     </row>
+    <row r="319">
+      <c r="A319" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B319" t="str">
+        <v>23:00</v>
+      </c>
+      <c r="C319" t="str">
+        <v>BACKLOG.md / BACKLOG.csv</v>
+      </c>
+      <c r="D319" t="str">
+        <v>BL-079 נוסף לבקלוג — שיפור: הוספת תפריט בחירה של שפה ודת לתבנית ייבוא Excel/CSV; עדיפות 🟡 בינונית; לא יושם בספרינט הנוכחי</v>
+      </c>
+      <c r="E319" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F319" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G319" t="str">
+        <v>Documentation</v>
+      </c>
+      <c r="H319" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H318"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H319"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H319"/>
+  <dimension ref="A1:H320"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -8460,9 +8460,35 @@
         <v>done</v>
       </c>
     </row>
+    <row r="320">
+      <c r="A320" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B320" t="str">
+        <v>23:30</v>
+      </c>
+      <c r="C320" t="str">
+        <v>src/screens/UserSetupScreen.tsx / src/screens/DashboardScreen.tsx / src/services/userProfileService.ts</v>
+      </c>
+      <c r="D320" t="str">
+        <v>BL-067 אומת — DoD מלא: מסך הגדרת שם (first-launch), שמירה ב-nm_user_name, ברכה אישית ב-Dashboard, פאנל ברכות ממתינות עם קליקביליות, מצבי ריק תקינים, EN+HE i18n מלא, build+lint ✅</v>
+      </c>
+      <c r="E320" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F320" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G320" t="str">
+        <v>Reviewer</v>
+      </c>
+      <c r="H320" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H319"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H320"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H320"/>
+  <dimension ref="A1:H323"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -8486,9 +8486,87 @@
         <v>done</v>
       </c>
     </row>
+    <row r="321">
+      <c r="A321" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B321" t="str">
+        <v>23:45</v>
+      </c>
+      <c r="C321" t="str">
+        <v>src/context/AppContext.tsx</v>
+      </c>
+      <c r="D321" t="str">
+        <v>BUG-081 — נוסף showPremiumUI = !TEMP_PREMIUM_UNLOCK לקונטקסט; מסתיר תיוג Premium כשהגייט הזמני פתוח; לא משפיע על גישה לתכונות</v>
+      </c>
+      <c r="E321" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F321" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G321" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H321" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B322" t="str">
+        <v>23:45</v>
+      </c>
+      <c r="C322" t="str">
+        <v>src/screens/ContactFormScreen.tsx</v>
+      </c>
+      <c r="D322" t="str">
+        <v>BUG-081 — כותרת "פרטי פרמיום" + Crown + גבול ענבר מוסתרים כששוPremiumUI=false; שדות הטופס נשארים גלויים</v>
+      </c>
+      <c r="E322" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F322" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G322" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H322" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B323" t="str">
+        <v>23:45</v>
+      </c>
+      <c r="C323" t="str">
+        <v>src/screens/SettingsScreen.tsx</v>
+      </c>
+      <c r="D323" t="str">
+        <v>BUG-081 — סעיף Premium (Crown + באנר זהב + "Premium Active") מוסתר כשshowPremiumUI=false; כותרת "Premium Features" מוסתרת; אייקון Crown של Birthday Center הוחלף ב-Sparkles במצב MVP</v>
+      </c>
+      <c r="E323" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F323" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G323" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H323" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H320"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H323"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H323"/>
+  <dimension ref="A1:H324"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -8564,9 +8564,35 @@
         <v>done</v>
       </c>
     </row>
+    <row r="324">
+      <c r="A324" t="str">
+        <v>2026-05-02</v>
+      </c>
+      <c r="B324" t="str">
+        <v>00:00</v>
+      </c>
+      <c r="C324" t="str">
+        <v>BACKLOG.md / BACKLOG.csv</v>
+      </c>
+      <c r="D324" t="str">
+        <v>BL-080 נוסף לבקלוג — BUG: תזמון שגוי של התראות לחגים ישראליים (יום הזיכרון / יום העצמאות); עדיפות 🔴 גבוהה; לא יושם — ממתין לספרינט מאושר</v>
+      </c>
+      <c r="E324" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F324" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G324" t="str">
+        <v>Documentation</v>
+      </c>
+      <c r="H324" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H323"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H324"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H324"/>
+  <dimension ref="A1:H325"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -8590,9 +8590,35 @@
         <v>done</v>
       </c>
     </row>
+    <row r="325">
+      <c r="A325" t="str">
+        <v>2026-05-02</v>
+      </c>
+      <c r="B325" t="str">
+        <v>00:30</v>
+      </c>
+      <c r="C325" t="str">
+        <v>src/services/notificationService.ts</v>
+      </c>
+      <c r="D325" t="str">
+        <v>BL-080 / BUG-082 תוקן — new Date("YYYY-MM-DD") הוחלף ב-parseDateLocal() שמפרש תאריכים כחצות שעון מקומי; מונע הסטה של יום בגלל UTC+3 (Asia/Jerusalem); נוספו בטיחות: דילוג על holiday.date ריק/לא תקין; Hebcal Israel mode כבר היה נכון</v>
+      </c>
+      <c r="E325" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F325" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G325" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H325" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H324"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H325"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H325"/>
+  <dimension ref="A1:H335"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -8616,9 +8616,269 @@
         <v>done</v>
       </c>
     </row>
+    <row r="326">
+      <c r="A326" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B326" t="str">
+        <v>12:00</v>
+      </c>
+      <c r="C326" t="str">
+        <v>BACKLOG.md</v>
+      </c>
+      <c r="D326" t="str">
+        <v>BL-081 נוסף לבאקלוג — באג: אייקוני כיוון (ArrowRight) ב-ImportContactsScreen.tsx לא מודעים ל-RTL; 3 מופעים בשורות 188, 292, 334; כל שאר המסכים כבר נכונים</v>
+      </c>
+      <c r="E326" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F326" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G326" t="str">
+        <v>Documentation</v>
+      </c>
+      <c r="H326" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B327" t="str">
+        <v>12:00</v>
+      </c>
+      <c r="C327" t="str">
+        <v>BACKLOG.csv</v>
+      </c>
+      <c r="D327" t="str">
+        <v>BL-081 נוסף ל-BACKLOG.csv עם עדיפות High</v>
+      </c>
+      <c r="E327" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F327" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G327" t="str">
+        <v>Documentation</v>
+      </c>
+      <c r="H327" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B328" t="str">
+        <v>12:30</v>
+      </c>
+      <c r="C328" t="str">
+        <v>src/screens/premium/ImportContactsScreen.tsx</v>
+      </c>
+      <c r="D328" t="str">
+        <v>BL-081 תוקן — 3 מופעי ArrowRight קשוחים הוחלפו ב-lang==='he' ? ArrowLeft : ArrowRight; נוסף useLang() ו-ArrowLeft לייבואים; כפתור ייבוא ממכשיר, הורד תבנית, עמודת מיפוי — כולם RTL-נכון</v>
+      </c>
+      <c r="E328" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F328" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G328" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H328" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B329" t="str">
+        <v>12:30</v>
+      </c>
+      <c r="C329" t="str">
+        <v>src/components/ContactCard.tsx</v>
+      </c>
+      <c r="D329" t="str">
+        <v>BL-075 יושם — ContactCard קיבל 3-dot overflow menu (MoreVertical); לחיצה פותחת תפריט עם עריכה + מחיקה; מחיקה פותחת Modal אישור; סגירה על-ידי outside click + Escape; aria-label contacts_moreOptions; dropdown מיוצב RTL-aware</v>
+      </c>
+      <c r="E329" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F329" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G329" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H329" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B330" t="str">
+        <v>12:30</v>
+      </c>
+      <c r="C330" t="str">
+        <v>src/i18n/index.ts</v>
+      </c>
+      <c r="D330" t="str">
+        <v>BL-075 — נוסף מפתח contacts_moreOptions ('More options' / 'אפשרויות נוספות') לשני הלוקאלים</v>
+      </c>
+      <c r="E330" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F330" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G330" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H330" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B331" t="str">
+        <v>12:30</v>
+      </c>
+      <c r="C331" t="str">
+        <v>src/index.css</v>
+      </c>
+      <c r="D331" t="str">
+        <v>BL-049 — .bottom-nav-item.active קיבל box-shadow: inset 0 2px 0 var(--color-primary); מוסיף פס אינדיקטור עליון ברור לטאב הפעיל</v>
+      </c>
+      <c r="E331" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F331" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G331" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H331" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B332" t="str">
+        <v>12:30</v>
+      </c>
+      <c r="C332" t="str">
+        <v>src/components/Navigation.tsx</v>
+      </c>
+      <c r="D332" t="str">
+        <v>BL-049 — גלו רקע לאייקון הפעיל שודרג מ-opacity-15 ל-opacity-20 לניגודיות גבוהה יותר</v>
+      </c>
+      <c r="E332" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F332" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G332" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H332" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B333" t="str">
+        <v>12:35</v>
+      </c>
+      <c r="C333" t="str">
+        <v>BACKLOG.md</v>
+      </c>
+      <c r="D333" t="str">
+        <v>BL-082 נוסף לבאקלוג — שיפור: מערכת הנקודות לא מוסברת; calculateRelationshipScore() ב-scoringSystem.ts; דרוש הסבר UX בעברית ואנגלית</v>
+      </c>
+      <c r="E333" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F333" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G333" t="str">
+        <v>Documentation</v>
+      </c>
+      <c r="H333" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B334" t="str">
+        <v>12:35</v>
+      </c>
+      <c r="C334" t="str">
+        <v>BACKLOG.md</v>
+      </c>
+      <c r="D334" t="str">
+        <v>BL-079 הורחב — כולל כעת drilldown בין Language ל-Religion ב-UI dropdowns ומקור אחד של אמת (shared config) בנוסף לתבנית ה-CSV</v>
+      </c>
+      <c r="E334" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F334" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G334" t="str">
+        <v>Documentation</v>
+      </c>
+      <c r="H334" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B335" t="str">
+        <v>12:35</v>
+      </c>
+      <c r="C335" t="str">
+        <v>BACKLOG.md</v>
+      </c>
+      <c r="D335" t="str">
+        <v>Sprint 18 סגור — BL-081/BL-075/BL-049 עודכנו ל-Done</v>
+      </c>
+      <c r="E335" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F335" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G335" t="str">
+        <v>Documentation</v>
+      </c>
+      <c r="H335" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H325"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H335"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H335"/>
+  <dimension ref="A1:H340"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -8876,9 +8876,139 @@
         <v>done</v>
       </c>
     </row>
+    <row r="336">
+      <c r="A336" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B336" t="str">
+        <v>13:30</v>
+      </c>
+      <c r="C336" t="str">
+        <v>src/data/contactConfig.ts</v>
+      </c>
+      <c r="D336" t="str">
+        <v>BL-079 — קובץ config חדש: LANGUAGE_KEYS, RELIGION_KEYS, LANGUAGE_RELIGION_ORDER (drilldown per language), LANGUAGE_DISPLAY + RELIGION_DISPLAY (EN+HE), normalizeLanguage(), normalizeReligion(), getLanguageDisplayValue(), getReligionDisplayValue() — מקור יחיד של אמת</v>
+      </c>
+      <c r="E336" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F336" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G336" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H336" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B337" t="str">
+        <v>13:30</v>
+      </c>
+      <c r="C337" t="str">
+        <v>src/services/importService.ts</v>
+      </c>
+      <c r="D337" t="str">
+        <v>BL-079 — הוחלפו cast ישיר (as Language / as Religion) ב-normalizeLanguage() ו-normalizeReligion() מ-contactConfig; מקבל raw key, EN label, ו-HE label</v>
+      </c>
+      <c r="E337" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F337" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G337" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H337" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B338" t="str">
+        <v>13:30</v>
+      </c>
+      <c r="C338" t="str">
+        <v>src/screens/premium/ImportContactsScreen.tsx</v>
+      </c>
+      <c r="D338" t="str">
+        <v>BL-079 — downloadCSVTemplate() מקבל locale param; headers ו-example row מלוקלים לפי שפת האפליקציה (EN: Name/Phone/Religion=Judaism/Language=English, HE: שם/טלפון/דת=יהדות/שפה=עברית)</v>
+      </c>
+      <c r="E338" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F338" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G338" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H338" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B339" t="str">
+        <v>13:30</v>
+      </c>
+      <c r="C339" t="str">
+        <v>src/screens/ContactFormScreen.tsx</v>
+      </c>
+      <c r="D339" t="str">
+        <v>BL-079 — RELIGION_LABELS מוחלף ב-LANGUAGE_RELIGION_ORDER מ-contactConfig; Religion dropdown מסדר אפשרויות לפי רלוונטיות לשפת הקשר (כל הדתות זמינות, רק סדר שונה)</v>
+      </c>
+      <c r="E339" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F339" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G339" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H339" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B340" t="str">
+        <v>13:35</v>
+      </c>
+      <c r="C340" t="str">
+        <v>BACKLOG.md</v>
+      </c>
+      <c r="D340" t="str">
+        <v>BL-079 עודכן ל-Done Sprint 19</v>
+      </c>
+      <c r="E340" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F340" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G340" t="str">
+        <v>Documentation</v>
+      </c>
+      <c r="H340" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H335"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H340"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H340"/>
+  <dimension ref="A1:H343"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -9006,9 +9006,87 @@
         <v>done</v>
       </c>
     </row>
+    <row r="341">
+      <c r="A341" t="str">
+        <v>2026-05-02</v>
+      </c>
+      <c r="B341" t="str">
+        <v>10:00</v>
+      </c>
+      <c r="C341" t="str">
+        <v>src/services/importService.ts</v>
+      </c>
+      <c r="D341" t="str">
+        <v>BL-076 — נוסף hebrewBirthday ל-DETECTABLE_FIELDS (לפני birthday כדי למנוע התאמה שגויה); processImport כותב hebrewBirthday לאובייקט Contact</v>
+      </c>
+      <c r="E341" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F341" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G341" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H341" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="str">
+        <v>2026-05-02</v>
+      </c>
+      <c r="B342" t="str">
+        <v>10:00</v>
+      </c>
+      <c r="C342" t="str">
+        <v>src/screens/premium/ImportContactsScreen.tsx</v>
+      </c>
+      <c r="D342" t="str">
+        <v>BL-076 — נוסף עמודת 'Hebrew Birthday (DD-MM)' / 'יום הולדת עברי (יום-חודש)' לתבנית CSV להורדה; שורת הדוגמה מציגה 14-07 כדוגמת פורמט</v>
+      </c>
+      <c r="E342" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F342" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G342" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H342" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="str">
+        <v>2026-05-02</v>
+      </c>
+      <c r="B343" t="str">
+        <v>10:00</v>
+      </c>
+      <c r="C343" t="str">
+        <v>BACKLOG.md</v>
+      </c>
+      <c r="D343" t="str">
+        <v>BL-076 עודכן ל-Done Sprint 20</v>
+      </c>
+      <c r="E343" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F343" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G343" t="str">
+        <v>Documentation</v>
+      </c>
+      <c r="H343" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H340"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H343"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H343"/>
+  <dimension ref="A1:H351"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -9084,9 +9084,217 @@
         <v>done</v>
       </c>
     </row>
+    <row r="344">
+      <c r="A344" t="str">
+        <v>2026-05-02</v>
+      </c>
+      <c r="B344" t="str">
+        <v>11:00</v>
+      </c>
+      <c r="C344" t="str">
+        <v>src/services/importService.ts</v>
+      </c>
+      <c r="D344" t="str">
+        <v>BL-084 / BUG-084 — נוסף normalizeBirthday() שמנרמלת תאריכים לפורמט YYYY-MM-DD; מונע שגיאת RangeError כאשר תאריך ה-CSV אינו בפורמט ISO</v>
+      </c>
+      <c r="E344" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F344" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G344" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H344" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="str">
+        <v>2026-05-02</v>
+      </c>
+      <c r="B345" t="str">
+        <v>11:00</v>
+      </c>
+      <c r="C345" t="str">
+        <v>src/screens/ContactDetailScreen.tsx</v>
+      </c>
+      <c r="D345" t="str">
+        <v>BL-084 / BUG-084 — נוסף !isNaN guard לפני format(new Date(contact.birthday)) כדי למנוע קריסה על תאריכים שגויים בנתונים קיימים</v>
+      </c>
+      <c r="E345" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F345" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G345" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H345" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="str">
+        <v>2026-05-02</v>
+      </c>
+      <c r="B346" t="str">
+        <v>11:00</v>
+      </c>
+      <c r="C346" t="str">
+        <v>src/i18n/index.ts</v>
+      </c>
+      <c r="D346" t="str">
+        <v>BL-082 — נוספו מפתחות score_tipTitle ו-score_tipBody ב-EN וב-HE לתיאור ציון הקשר</v>
+      </c>
+      <c r="E346" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F346" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G346" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H346" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="str">
+        <v>2026-05-02</v>
+      </c>
+      <c r="B347" t="str">
+        <v>11:00</v>
+      </c>
+      <c r="C347" t="str">
+        <v>src/components/ContactCard.tsx</v>
+      </c>
+      <c r="D347" t="str">
+        <v>BL-082 — הפיכת תג הציון ל-button ניתן ללחיצה; הוסף tooltip עם הסבר על חישוב הציון; showScoreTip state + click-outside handler</v>
+      </c>
+      <c r="E347" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F347" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G347" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H347" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="str">
+        <v>2026-05-02</v>
+      </c>
+      <c r="B348" t="str">
+        <v>11:00</v>
+      </c>
+      <c r="C348" t="str">
+        <v>src/i18n/index.ts</v>
+      </c>
+      <c r="D348" t="str">
+        <v>BL-068 — נוספו מפתחות groups_membersSection, groups_searchContacts, groups_membersSelected ב-EN וב-HE</v>
+      </c>
+      <c r="E348" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F348" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G348" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H348" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="str">
+        <v>2026-05-02</v>
+      </c>
+      <c r="B349" t="str">
+        <v>11:00</v>
+      </c>
+      <c r="C349" t="str">
+        <v>src/screens/GroupsScreen.tsx</v>
+      </c>
+      <c r="D349" t="str">
+        <v>BL-068 — נוסף contact picker ב-modal יצירת/עריכת קבוצה; selectedContactIds state; openForm מאתחל מ-group.contactIds; handleSave שומר contactIds</v>
+      </c>
+      <c r="E349" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F349" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G349" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H349" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="str">
+        <v>2026-05-02</v>
+      </c>
+      <c r="B350" t="str">
+        <v>11:00</v>
+      </c>
+      <c r="C350" t="str">
+        <v>src/i18n/index.ts</v>
+      </c>
+      <c r="D350" t="str">
+        <v>BL-069 — נוספו מפתחות contactForm_assignGroup ו-contactForm_noGroup ב-EN וב-HE</v>
+      </c>
+      <c r="E350" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F350" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G350" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H350" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="str">
+        <v>2026-05-02</v>
+      </c>
+      <c r="B351" t="str">
+        <v>11:00</v>
+      </c>
+      <c r="C351" t="str">
+        <v>src/screens/ContactFormScreen.tsx</v>
+      </c>
+      <c r="D351" t="str">
+        <v>BL-069 — נוסף group selector ב-form (מוצג רק לאנשי קשר חדשים); לאחר addContact מעדכן group.contactIds אם נבחרה קבוצה</v>
+      </c>
+      <c r="E351" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F351" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G351" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H351" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H343"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H351"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H351"/>
+  <dimension ref="A1:H357"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -9292,9 +9292,165 @@
         <v>done</v>
       </c>
     </row>
+    <row r="352">
+      <c r="A352" t="str">
+        <v>2026-05-02</v>
+      </c>
+      <c r="B352" t="str">
+        <v>12:00</v>
+      </c>
+      <c r="C352" t="str">
+        <v>BACKLOG.md</v>
+      </c>
+      <c r="D352" t="str">
+        <v>BL-050 ו-BL-052 עודכנו ל-Done — שניהם יושמו בעבר (Sprint 5) אך נשארו בטעות ב-Backlog</v>
+      </c>
+      <c r="E352" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F352" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G352" t="str">
+        <v>Documentation</v>
+      </c>
+      <c r="H352" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="str">
+        <v>2026-05-02</v>
+      </c>
+      <c r="B353" t="str">
+        <v>12:00</v>
+      </c>
+      <c r="C353" t="str">
+        <v>src/services/importService.ts</v>
+      </c>
+      <c r="D353" t="str">
+        <v>BL-092 — נוסף celebrationType ל-DETECTABLE_FIELDS; normalizeCelebrationType() ממפה ערכים (Jewish/Christian/Muslim/Druze/Secular); processImport כותב celebrationType לאיש הקשר</v>
+      </c>
+      <c r="E353" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F353" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G353" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H353" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="str">
+        <v>2026-05-02</v>
+      </c>
+      <c r="B354" t="str">
+        <v>12:00</v>
+      </c>
+      <c r="C354" t="str">
+        <v>src/services/importService.ts</v>
+      </c>
+      <c r="D354" t="str">
+        <v>BL-090 — נוסף normalizeHebrewBirthday() שמאמת פורמט DD-MM; processImport עכשיו מנרמל hebrewBirthday לפני שמירה; ערכים לא תקינים מוחזרים כ-undefined</v>
+      </c>
+      <c r="E354" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F354" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G354" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H354" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="str">
+        <v>2026-05-02</v>
+      </c>
+      <c r="B355" t="str">
+        <v>12:00</v>
+      </c>
+      <c r="C355" t="str">
+        <v>src/screens/ContactDetailScreen.tsx</v>
+      </c>
+      <c r="D355" t="str">
+        <v>BL-090 — נוסף regex guard /^\d{1,2}-\d{1,2}$/ לפני הצגת hebrewBirthday; מונע הצגת שורה ריקה על ערכים לא תקינים</v>
+      </c>
+      <c r="E355" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F355" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G355" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H355" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="str">
+        <v>2026-05-02</v>
+      </c>
+      <c r="B356" t="str">
+        <v>12:00</v>
+      </c>
+      <c r="C356" t="str">
+        <v>src/i18n/index.ts</v>
+      </c>
+      <c r="D356" t="str">
+        <v>BL-091 — נוסף מפתח settings_exportGroupWarning ב-EN וב-HE; מזהיר את המשתמש ששיוך לקבוצות לא נכלל בייצוא CSV</v>
+      </c>
+      <c r="E356" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F356" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G356" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H356" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="str">
+        <v>2026-05-02</v>
+      </c>
+      <c r="B357" t="str">
+        <v>12:00</v>
+      </c>
+      <c r="C357" t="str">
+        <v>src/screens/SettingsScreen.tsx</v>
+      </c>
+      <c r="D357" t="str">
+        <v>BL-091 — נוסף טקסט אזהרה מתחת לכפתור ייצוא CSV: 'שיוך לקבוצות לא נכלל בייצוא ה-CSV'</v>
+      </c>
+      <c r="E357" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F357" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G357" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H357" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H351"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H357"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H357"/>
+  <dimension ref="A1:H361"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -9448,9 +9448,113 @@
         <v>done</v>
       </c>
     </row>
+    <row r="358">
+      <c r="A358" t="str">
+        <v>2026-05-02</v>
+      </c>
+      <c r="B358" t="str">
+        <v>15:00</v>
+      </c>
+      <c r="C358" t="str">
+        <v>src/context/AppContext.tsx</v>
+      </c>
+      <c r="D358" t="str">
+        <v>BL-086 — תוקן deleteContact: מסיר את מזהה איש הקשר מכל הקבוצות שמכילות אותו לפני המחיקה; שומר על שלמות נתוני contactIds</v>
+      </c>
+      <c r="E358" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F358" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G358" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H358" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="str">
+        <v>2026-05-02</v>
+      </c>
+      <c r="B359" t="str">
+        <v>15:00</v>
+      </c>
+      <c r="C359" t="str">
+        <v>src/screens/ContactsScreen.tsx</v>
+      </c>
+      <c r="D359" t="str">
+        <v>BL-088 — תוקנה כותרת המשנה: מוצגות כעת 'X אנשי קשר' במקום 'X קבוצות'; שימוש במפתחות contacts_contact/contacts_contacts</v>
+      </c>
+      <c r="E359" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F359" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G359" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H359" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="str">
+        <v>2026-05-02</v>
+      </c>
+      <c r="B360" t="str">
+        <v>15:00</v>
+      </c>
+      <c r="C360" t="str">
+        <v>src/screens/ContactsScreen.tsx</v>
+      </c>
+      <c r="D360" t="str">
+        <v>BL-087 — נוסף chip סינון קבוצה פעיל: מציג שם ואמוג'י של הקבוצה כשמגיעים מ-?group=X עם כפתור ניקוי; הרשימה מסוננת בהתאם</v>
+      </c>
+      <c r="E360" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F360" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G360" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H360" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="str">
+        <v>2026-05-02</v>
+      </c>
+      <c r="B361" t="str">
+        <v>15:00</v>
+      </c>
+      <c r="C361" t="str">
+        <v>src/i18n/index.ts</v>
+      </c>
+      <c r="D361" t="str">
+        <v>Sprint 23 — נוספו מפתחות contacts_contact, contacts_contacts, contacts_filterGroup, contacts_clearFilter ב-EN וב-HE</v>
+      </c>
+      <c r="E361" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F361" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G361" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H361" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H357"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H361"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H361"/>
+  <dimension ref="A1:H370"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -9552,9 +9552,243 @@
         <v>done</v>
       </c>
     </row>
+    <row r="362">
+      <c r="A362" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="B362" t="str">
+        <v>10:00</v>
+      </c>
+      <c r="C362" t="str">
+        <v>src/i18n/index.ts</v>
+      </c>
+      <c r="D362" t="str">
+        <v>Sprint 24 — נוספו מפתחות contactDetail_groups, group_religion_filter ב-EN וב-HE; עודכן group_purpose_hint לטקסט ברור יותר (BL-089, BL-093)</v>
+      </c>
+      <c r="E362" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F362" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G362" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H362" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="B363" t="str">
+        <v>10:01</v>
+      </c>
+      <c r="C363" t="str">
+        <v>src/components/ContactCard.tsx</v>
+      </c>
+      <c r="D363" t="str">
+        <v>BL-089: הוספת chip קבוצת חברות לכרטיס איש הקשר — מציג עד 2 קבוצות עם צבע + אמוג'י; overflow +N; reverse-lookup דרך Group.contactIds</v>
+      </c>
+      <c r="E363" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F363" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G363" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H363" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="B364" t="str">
+        <v>10:02</v>
+      </c>
+      <c r="C364" t="str">
+        <v>src/screens/ContactDetailScreen.tsx</v>
+      </c>
+      <c r="D364" t="str">
+        <v>BL-089: נוסף חלק קבוצות במסך פרטי איש קשר — מציג כל הקבוצות שאיש הקשר שייך אליהן; useMemo עם id לפני return מוקדם</v>
+      </c>
+      <c r="E364" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F364" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G364" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H364" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="B365" t="str">
+        <v>10:03</v>
+      </c>
+      <c r="C365" t="str">
+        <v>src/screens/GroupsScreen.tsx</v>
+      </c>
+      <c r="D365" t="str">
+        <v>BL-093 Phase 1: נוספו chips סינון לפי דת בחלק הוספת חגים לקבוצה (Premium); מסנן את רשימת החגים לפי הדתות שנבחרו; אין בחירה אוטומטית; מתאפס בפתיחת הטופס</v>
+      </c>
+      <c r="E365" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F365" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G365" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H365" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="B366" t="str">
+        <v>12:00</v>
+      </c>
+      <c r="C366" t="str">
+        <v>src/context/AppContext.tsx</v>
+      </c>
+      <c r="D366" t="str">
+        <v>TEMP: בוטלו מגבלות פרמיום ל-MVP — canAddContact ו-canAddGroup מוגדרים כ-true ללא תלות ב-isPremium; LIMITS נשמר עם הערת eslint-disable</v>
+      </c>
+      <c r="E366" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F366" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G366" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H366" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="B367" t="str">
+        <v>12:01</v>
+      </c>
+      <c r="C367" t="str">
+        <v>src/components/PremiumBadge.tsx</v>
+      </c>
+      <c r="D367" t="str">
+        <v>TEMP: PremiumBadge ו-PremiumFeaturePrompt מחזירים null כשshowPremiumUI=false — הסתרת כל תגיות ו-prompts פרמיום ב-MVP</v>
+      </c>
+      <c r="E367" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F367" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G367" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H367" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="B368" t="str">
+        <v>12:02</v>
+      </c>
+      <c r="C368" t="str">
+        <v>src/screens/UpgradeScreen.tsx</v>
+      </c>
+      <c r="D368" t="str">
+        <v>TEMP: מסך Upgrade מפנה ל-/dashboard כשshowPremiumUI=false — מניעת גישה למסך שדרוג ב-MVP</v>
+      </c>
+      <c r="E368" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F368" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G368" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H368" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="B369" t="str">
+        <v>12:03</v>
+      </c>
+      <c r="C369" t="str">
+        <v>src/screens/PaymeScreen.tsx</v>
+      </c>
+      <c r="D369" t="str">
+        <v>TEMP: מסך PayMe מפנה ל-/dashboard כשshowPremiumUI=false — מניעת גישה למסך תשלום ב-MVP</v>
+      </c>
+      <c r="E369" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F369" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G369" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H369" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="B370" t="str">
+        <v>12:04</v>
+      </c>
+      <c r="C370" t="str">
+        <v>src/components/MediaAttachmentPicker.tsx</v>
+      </c>
+      <c r="D370" t="str">
+        <v>TEMP: שער isPremium ב-MediaAttachmentPicker הוחלף ב-(false as boolean) — צירוף מדיה זמין לכל המשתמשים ב-MVP</v>
+      </c>
+      <c r="E370" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F370" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G370" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H370" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H361"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H370"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H370"/>
+  <dimension ref="A1:H381"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -9786,9 +9786,295 @@
         <v>done</v>
       </c>
     </row>
+    <row r="371">
+      <c r="A371" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="B371" t="str">
+        <v>14:00</v>
+      </c>
+      <c r="C371" t="str">
+        <v>src/utils/holidayUtils.ts</v>
+      </c>
+      <c r="D371" t="str">
+        <v>נוצר util משותף getHolidayDisplayName(holiday, lang) — מחזיר שם חג בשפת הממשק (עברית/אנגלית). BL-094</v>
+      </c>
+      <c r="E371" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F371" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G371" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H371" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="B372" t="str">
+        <v>14:00</v>
+      </c>
+      <c r="C372" t="str">
+        <v>src/components/HolidayCard.tsx</v>
+      </c>
+      <c r="D372" t="str">
+        <v>BL-094: שם חג מוצג דרך getHolidayDisplayName() — תמיכה בשתי שפות בכרטיס חג</v>
+      </c>
+      <c r="E372" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F372" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G372" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H372" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="B373" t="str">
+        <v>14:00</v>
+      </c>
+      <c r="C373" t="str">
+        <v>src/screens/DashboardScreen.tsx</v>
+      </c>
+      <c r="D373" t="str">
+        <v>BL-094: 3 נקודות הצגת שם חג עברו ל-getHolidayDisplayName() — pending item, hero banner, group alert</v>
+      </c>
+      <c r="E373" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F373" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G373" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H373" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="B374" t="str">
+        <v>14:00</v>
+      </c>
+      <c r="C374" t="str">
+        <v>src/screens/HolidayDetailScreen.tsx</v>
+      </c>
+      <c r="D374" t="str">
+        <v>BL-094: כותרת עמוד וכותרת hero מוצגות דרך getHolidayDisplayName()</v>
+      </c>
+      <c r="E374" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F374" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G374" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H374" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="B375" t="str">
+        <v>14:00</v>
+      </c>
+      <c r="C375" t="str">
+        <v>src/screens/HolidayRemindersScreen.tsx</v>
+      </c>
+      <c r="D375" t="str">
+        <v>BL-094: שם חג בדף תזכורות חגים מוצג דרך getHolidayDisplayName()</v>
+      </c>
+      <c r="E375" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F375" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G375" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H375" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="B376" t="str">
+        <v>14:00</v>
+      </c>
+      <c r="C376" t="str">
+        <v>src/screens/GreetingEditorScreen.tsx</v>
+      </c>
+      <c r="D376" t="str">
+        <v>BL-094: dropdown בחירת חג מציג שם בשפת הממשק דרך getHolidayDisplayName()</v>
+      </c>
+      <c r="E376" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F376" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G376" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H376" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="B377" t="str">
+        <v>14:00</v>
+      </c>
+      <c r="C377" t="str">
+        <v>src/screens/GroupsScreen.tsx</v>
+      </c>
+      <c r="D377" t="str">
+        <v>BL-094: הוסר duplicate מקומי של getHolidayDisplayName; מייבא עכשיו מ-holidayUtils</v>
+      </c>
+      <c r="E377" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F377" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G377" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H377" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="B378" t="str">
+        <v>14:00</v>
+      </c>
+      <c r="C378" t="str">
+        <v>src/screens/ContactDetailScreen.tsx</v>
+      </c>
+      <c r="D378" t="str">
+        <v>BL-094: שם חג בפעולת שליחת ברכה מוצג דרך getHolidayDisplayName(). BL-085: חגים קשורים ממוינים לפי תאריך</v>
+      </c>
+      <c r="E378" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F378" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G378" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H378" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="B379" t="str">
+        <v>14:00</v>
+      </c>
+      <c r="C379" t="str">
+        <v>src/services/notificationService.ts</v>
+      </c>
+      <c r="D379" t="str">
+        <v>BL-094: שמות חגים בהתראות מוצגים בשפת המשתמש — פרמטר lang נוסף ל-fireReminders()</v>
+      </c>
+      <c r="E379" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F379" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G379" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H379" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="B380" t="str">
+        <v>14:00</v>
+      </c>
+      <c r="C380" t="str">
+        <v>src/App.tsx</v>
+      </c>
+      <c r="D380" t="str">
+        <v>BL-094: lang מ-useLang() מועבר ל-fireReminders() לתמיכה בהתראות בשפת המשתמש</v>
+      </c>
+      <c r="E380" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F380" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G380" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H380" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="B381" t="str">
+        <v>14:00</v>
+      </c>
+      <c r="C381" t="str">
+        <v>src/screens/ContactFormScreen.tsx</v>
+      </c>
+      <c r="D381" t="str">
+        <v>BL-096: נוספה אפשרות לשיוך/הסרה מקבוצות בעריכת איש קשר קיים — chips toggle UI + סנכרון בשמירה</v>
+      </c>
+      <c r="E381" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F381" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G381" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H381" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H370"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H381"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H381"/>
+  <dimension ref="A1:H387"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -10072,9 +10072,165 @@
         <v>done</v>
       </c>
     </row>
+    <row r="382">
+      <c r="A382" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="B382" t="str">
+        <v>12:00</v>
+      </c>
+      <c r="C382" t="str">
+        <v>src/components/QuickAddModal.tsx</v>
+      </c>
+      <c r="D382" t="str">
+        <v>BL-099: נוצר QuickAddModal — bottom sheet עם שדות שם + טלפון בלבד; שמירה יוצרת איש קשר עם ברירות מחדל; סגירה לאחר שמירה; קישור לטופס מלא</v>
+      </c>
+      <c r="E382" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F382" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G382" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H382" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="B383" t="str">
+        <v>12:00</v>
+      </c>
+      <c r="C383" t="str">
+        <v>src/i18n/index.ts</v>
+      </c>
+      <c r="D383" t="str">
+        <v>BL-098/099: עדכון מחרוזות empty state לניסוח רגשי/ערכי (EN+HE); נוספו 8 מפתחות quickAdd_* (title, name, phone, placeholders, save, required, fullForm) — EN+HE</v>
+      </c>
+      <c r="E383" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F383" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G383" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H383" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="B384" t="str">
+        <v>12:00</v>
+      </c>
+      <c r="C384" t="str">
+        <v>src/screens/DashboardScreen.tsx</v>
+      </c>
+      <c r="D384" t="str">
+        <v>BL-098/099: empty state ב-Dashboard משתמש ב-QuickAddModal במקום ניווט לטופס מלא; אייקון 💛; CTA מוביל להוספה מהירה</v>
+      </c>
+      <c r="E384" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F384" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G384" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H384" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="B385" t="str">
+        <v>12:00</v>
+      </c>
+      <c r="C385" t="str">
+        <v>src/screens/ContactsScreen.tsx</v>
+      </c>
+      <c r="D385" t="str">
+        <v>BL-098/099: empty state ב-ContactsScreen משתמש ב-QuickAddModal במקום ניווט לטופס מלא; FAB ממשיך לנווט לטופס מלא</v>
+      </c>
+      <c r="E385" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F385" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G385" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H385" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="B386" t="str">
+        <v>12:00</v>
+      </c>
+      <c r="C386" t="str">
+        <v>BACKLOG.md</v>
+      </c>
+      <c r="D386" t="str">
+        <v>BL-098 ו-BL-099 נוספו לבקלוג וסומנו Done — Sprint 26</v>
+      </c>
+      <c r="E386" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F386" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G386" t="str">
+        <v>Documentation</v>
+      </c>
+      <c r="H386" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="B387" t="str">
+        <v>12:00</v>
+      </c>
+      <c r="C387" t="str">
+        <v>BACKLOG.csv</v>
+      </c>
+      <c r="D387" t="str">
+        <v>BL-098 ו-BL-099 נוספו לבקלוג.csv וסומנו Done — Sprint 26</v>
+      </c>
+      <c r="E387" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F387" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G387" t="str">
+        <v>Documentation</v>
+      </c>
+      <c r="H387" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H381"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H387"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H387"/>
+  <dimension ref="A1:H396"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -10228,9 +10228,243 @@
         <v>done</v>
       </c>
     </row>
+    <row r="388">
+      <c r="A388" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="B388" t="str">
+        <v>14:00</v>
+      </c>
+      <c r="C388" t="str">
+        <v>src/components/ui/Select.tsx</v>
+      </c>
+      <c r="D388" t="str">
+        <v>BL-100: הוספת שדות disabled ו-hidden לטיפוס option ב-Select — תומך ב-placeholder שלא ניתן לבחור</v>
+      </c>
+      <c r="E388" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F388" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G388" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H388" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="B389" t="str">
+        <v>14:00</v>
+      </c>
+      <c r="C389" t="str">
+        <v>src/screens/GreetingEditorScreen.tsx</v>
+      </c>
+      <c r="D389" t="str">
+        <v>BL-100: placeholder 'בחר איש קשר' ב-dropdown ה-contact עם disabled+hidden — לא ניתן לשמור עם placeholder</v>
+      </c>
+      <c r="E389" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F389" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G389" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H389" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="B390" t="str">
+        <v>14:00</v>
+      </c>
+      <c r="C390" t="str">
+        <v>src/utils/featureGuideUtils.ts</v>
+      </c>
+      <c r="D390" t="str">
+        <v>BL-083: עזרי localStorage לפיצ'ר guide — isGuideSeen, markGuideSeen, resetGuide עם מפתח nm_guide_seen</v>
+      </c>
+      <c r="E390" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F390" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G390" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H390" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="B391" t="str">
+        <v>14:00</v>
+      </c>
+      <c r="C391" t="str">
+        <v>src/components/FeatureGuide.tsx</v>
+      </c>
+      <c r="D391" t="str">
+        <v>BL-083: קומפוננטת FeatureGuide — 3 שקפים עם אמוג'י, כותרת, גוף; כפתור דלג (X) בכל שקף; מחוונים מנוקדים; ניווט RTL-aware; CTA 'בואו נתחיל'</v>
+      </c>
+      <c r="E391" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F391" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G391" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H391" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="B392" t="str">
+        <v>14:00</v>
+      </c>
+      <c r="C392" t="str">
+        <v>src/i18n/index.ts</v>
+      </c>
+      <c r="D392" t="str">
+        <v>BL-083/BL-100: נוספו מפתחות guide_slide1_title/body, guide_slide2_title/body, guide_slide3_title/body, guide_next, guide_done, guide_viewGuide, greeting_selectContact — EN + HE</v>
+      </c>
+      <c r="E392" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F392" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G392" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H392" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="B393" t="str">
+        <v>14:00</v>
+      </c>
+      <c r="C393" t="str">
+        <v>src/screens/DashboardScreen.tsx</v>
+      </c>
+      <c r="D393" t="str">
+        <v>BL-083: חיבור FeatureGuide — state showGuide מ-isGuideSeen(); מוצג בעלייה ראשונה לאפליקציה; נסגר ב-onDone</v>
+      </c>
+      <c r="E393" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F393" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G393" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H393" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="B394" t="str">
+        <v>14:00</v>
+      </c>
+      <c r="C394" t="str">
+        <v>src/screens/SettingsScreen.tsx</v>
+      </c>
+      <c r="D394" t="str">
+        <v>BL-083: כפתור 'Feature Guide' בסעיף App info — מאפס nm_guide_seen ומנווט ל-Dashboard כדי שה-Guide יוצג מחדש</v>
+      </c>
+      <c r="E394" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F394" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G394" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H394" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="B395" t="str">
+        <v>14:00</v>
+      </c>
+      <c r="C395" t="str">
+        <v>BACKLOG.md</v>
+      </c>
+      <c r="D395" t="str">
+        <v>BL-100 ו-BL-083 סומנו Done — Sprint 27</v>
+      </c>
+      <c r="E395" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F395" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G395" t="str">
+        <v>Documentation</v>
+      </c>
+      <c r="H395" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="B396" t="str">
+        <v>14:00</v>
+      </c>
+      <c r="C396" t="str">
+        <v>BACKLOG.csv</v>
+      </c>
+      <c r="D396" t="str">
+        <v>BL-100 ו-BL-083 עודכנו ל-Done — Sprint 27</v>
+      </c>
+      <c r="E396" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F396" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G396" t="str">
+        <v>Documentation</v>
+      </c>
+      <c r="H396" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H387"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H396"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H396"/>
+  <dimension ref="A1:H403"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -10462,9 +10462,191 @@
         <v>done</v>
       </c>
     </row>
+    <row r="397">
+      <c r="A397" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="B397" t="str">
+        <v>00:00</v>
+      </c>
+      <c r="C397" t="str">
+        <v>src/config/appConfig.ts</v>
+      </c>
+      <c r="D397" t="str">
+        <v>Sprint 28 — BL-097: הוסף מפתח אחסון nm_dont_show_landing ל-storageKeys</v>
+      </c>
+      <c r="E397" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F397" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G397" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H397" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="B398" t="str">
+        <v>00:00</v>
+      </c>
+      <c r="C398" t="str">
+        <v>src/services/storageService.ts</v>
+      </c>
+      <c r="D398" t="str">
+        <v>Sprint 28 — BL-097: הוסף isDontShowLanding() ו-setDontShowLanding() לניהול דגל דף הנחיתה</v>
+      </c>
+      <c r="E398" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F398" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G398" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H398" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="B399" t="str">
+        <v>00:00</v>
+      </c>
+      <c r="C399" t="str">
+        <v>src/i18n/index.ts</v>
+      </c>
+      <c r="D399" t="str">
+        <v>Sprint 28 — BL-097: הוסף 14 מפתחות תרגום לדף הנחיתה — EN ו-HE (tagline, subtitle, CTAs, scene labels, captions)</v>
+      </c>
+      <c r="E399" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F399" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G399" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H399" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="B400" t="str">
+        <v>00:00</v>
+      </c>
+      <c r="C400" t="str">
+        <v>src/screens/LandingScreen.tsx</v>
+      </c>
+      <c r="D400" t="str">
+        <v>Sprint 28 — BL-097: נוצר דף נחיתה — ערך רגשי, 4 תמונות קשרים (זוגיות/משפחה/חברים/עבודה), 3 כפתורי CTA, דגל dontShowLanding, דילוג אוטומטי למשתמש חוזר</v>
+      </c>
+      <c r="E400" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F400" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G400" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H400" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="B401" t="str">
+        <v>00:00</v>
+      </c>
+      <c r="C401" t="str">
+        <v>src/assets/landing/</v>
+      </c>
+      <c r="D401" t="str">
+        <v>Sprint 28 — BL-097: נוספו 4 תמונות WebP אופטימליות לדף הנחיתה (Romantic/Family/Friends/work)</v>
+      </c>
+      <c r="E401" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F401" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G401" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H401" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="B402" t="str">
+        <v>00:00</v>
+      </c>
+      <c r="C402" t="str">
+        <v>src/App.tsx</v>
+      </c>
+      <c r="D402" t="str">
+        <v>Sprint 28 — BL-097: הוסף נתיב /landing ועדכן redirect שורש לבדיקת dontShowLanding לפני onboarding</v>
+      </c>
+      <c r="E402" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F402" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G402" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H402" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="B403" t="str">
+        <v>00:00</v>
+      </c>
+      <c r="C403" t="str">
+        <v>src/screens/LandingScreen.tsx</v>
+      </c>
+      <c r="D403" t="str">
+        <v>Sprint 28 — תוקן lint: הסרת ייבוא isDontShowLanding שלא היה בשימוש ב-LandingScreen</v>
+      </c>
+      <c r="E403" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F403" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G403" t="str">
+        <v>Reviewer</v>
+      </c>
+      <c r="H403" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H396"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H403"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H403"/>
+  <dimension ref="A1:H410"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -10644,9 +10644,191 @@
         <v>done</v>
       </c>
     </row>
+    <row r="404">
+      <c r="A404" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="B404" t="str">
+        <v>09:00</v>
+      </c>
+      <c r="C404" t="str">
+        <v>src/screens/LandingScreen.tsx</v>
+      </c>
+      <c r="D404" t="str">
+        <v>מיקרו-פיקס FINDING-01 — handleRegister ניווט ל-/onboarding בלי לבדוק אם אונבורדינג כבר הושלם; תוקן ל-postLandingDestination() שמנתב למסך הנכון למשתמש חוזר</v>
+      </c>
+      <c r="E404" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F404" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G404" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H404" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="B405" t="str">
+        <v>10:00</v>
+      </c>
+      <c r="C405" t="str">
+        <v>src/types/index.ts</v>
+      </c>
+      <c r="D405" t="str">
+        <v>ספרינט 29 Phase 0 — הוסף שדה userId?: string אופציונלי ל-Contact, Group, GreetingDraft; מזהה Supabase auth.uid() לשימוש עתידי; תואם לאחור עם נתוני localStorage קיימים</v>
+      </c>
+      <c r="E405" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F405" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G405" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H405" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="B406" t="str">
+        <v>10:01</v>
+      </c>
+      <c r="C406" t="str">
+        <v>src/services/storageService.ts</v>
+      </c>
+      <c r="D406" t="str">
+        <v>ספרינט 29 Phase 0 — עדכון generateId() לשימוש ב-crypto.randomUUID() עם fallback לפורמט timestamp ישן; UUID תקני לכל הישויות החדשות</v>
+      </c>
+      <c r="E406" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F406" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G406" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H406" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="B407" t="str">
+        <v>10:02</v>
+      </c>
+      <c r="C407" t="str">
+        <v>src/context/AuthContext.tsx</v>
+      </c>
+      <c r="D407" t="str">
+        <v>ספרינט 29 Phase 0 — יצירת AuthContext חדש: stub Phase 0 תמיד לא-מאומת (user: null); מכין את התשתית ל-Supabase magic link auth ב-Phase 1; מייצא AuthUser, AuthProvider, useAuth</v>
+      </c>
+      <c r="E407" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F407" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G407" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H407" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="B408" t="str">
+        <v>10:03</v>
+      </c>
+      <c r="C408" t="str">
+        <v>src/services/dataService.ts</v>
+      </c>
+      <c r="D408" t="str">
+        <v>ספרינט 29 Phase 0 — יצירת dataService חדש: ממשק async לכל פעולות CRUD (contacts, groups, drafts, settings, premium); Phase 0 = קריאות synchronous ל-localStorage; פקקי Phase 2 ל-Supabase בכל פעולת כתיבה; deleteContactCascade מטפל במחיקה אטומית של איש קשר + ניקוי קבוצות</v>
+      </c>
+      <c r="E408" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F408" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G408" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H408" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="B409" t="str">
+        <v>10:04</v>
+      </c>
+      <c r="C409" t="str">
+        <v>src/context/AppContext.tsx</v>
+      </c>
+      <c r="D409" t="str">
+        <v>ספרינט 29 Phase 0 — שידוד AppContext: כל 9 מוטציות CRUD מנותבות דרך dataService עם fire-and-forget; functional state updates (אין read-after-write); auth.user?.id מוצמד לישויות חדשות; useAuth() מיובא; ממשק AppContextValue ציבורי לא שונה — אפס שינויים בסקרינים</v>
+      </c>
+      <c r="E409" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F409" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G409" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H409" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="B410" t="str">
+        <v>10:05</v>
+      </c>
+      <c r="C410" t="str">
+        <v>src/App.tsx</v>
+      </c>
+      <c r="D410" t="str">
+        <v>ספרינט 29 Phase 0 — הוסף AuthProvider wrapper בין LanguageProvider ל-ThemeProvider; AppProvider כעת רץ בתוך AuthContext</v>
+      </c>
+      <c r="E410" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F410" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G410" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H410" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H403"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H410"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H410"/>
+  <dimension ref="A1:H418"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -10826,9 +10826,217 @@
         <v>done</v>
       </c>
     </row>
+    <row r="411">
+      <c r="A411" t="str">
+        <v>2026-05-08</v>
+      </c>
+      <c r="B411" t="str">
+        <v>12:00</v>
+      </c>
+      <c r="C411" t="str">
+        <v>src/screens/DashboardScreen.tsx</v>
+      </c>
+      <c r="D411" t="str">
+        <v>BL-113: נוסף sortedUpcomingHolidays useMemo שממיין אירועים עולים לפי תאריך; כל 4 נקודות גישה עודכנו — todayHoliday, tomorrowHoliday, nextHoliday, render slice</v>
+      </c>
+      <c r="E411" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F411" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G411" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H411" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="str">
+        <v>2026-05-08</v>
+      </c>
+      <c r="B412" t="str">
+        <v>12:10</v>
+      </c>
+      <c r="C412" t="str">
+        <v>src/context/AppContext.tsx</v>
+      </c>
+      <c r="D412" t="str">
+        <v>BL-112: נוסף useEffect עם מאזין visibilitychange; todayKey state מאלץ חישוב מחדש של dashboardData כשתאריך הלוח השנה משתנה (לאחר חצות); ניקוי listener נעשה ב-cleanup</v>
+      </c>
+      <c r="E412" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F412" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G412" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H412" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="str">
+        <v>2026-05-08</v>
+      </c>
+      <c r="B413" t="str">
+        <v>12:20</v>
+      </c>
+      <c r="C413" t="str">
+        <v>src/i18n/index.ts</v>
+      </c>
+      <c r="D413" t="str">
+        <v>BL-122+BL-120: נוספו 3 מפתחות EN+HE — landing_cta_anonymous (המשך בלי חשבון), landing_login_error_rate_limit, landing_login_error_invalid_email</v>
+      </c>
+      <c r="E413" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F413" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G413" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H413" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="str">
+        <v>2026-05-08</v>
+      </c>
+      <c r="B414" t="str">
+        <v>12:30</v>
+      </c>
+      <c r="C414" t="str">
+        <v>src/screens/LandingScreen.tsx</v>
+      </c>
+      <c r="D414" t="str">
+        <v>BL-122: נוספה פונקציה localizeAuthError שממפה שגיאות Supabase גולמיות להודעות עברית ידידותיות למשתמש; לא מוצגות שגיאות אנגלית למשתמשי עברית</v>
+      </c>
+      <c r="E414" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F414" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G414" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H414" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="str">
+        <v>2026-05-08</v>
+      </c>
+      <c r="B415" t="str">
+        <v>12:35</v>
+      </c>
+      <c r="C415" t="str">
+        <v>src/screens/LandingScreen.tsx</v>
+      </c>
+      <c r="D415" t="str">
+        <v>BL-120: כפתור המשך בלי חשבון (h-12, border) הוחלף במקום קישור אל תציג שוב הזעיר; כפתור ההדגמה הוקטן; נתיב אנונימי הפך לCTA ראשי גלוי מעל הגלילה</v>
+      </c>
+      <c r="E415" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F415" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G415" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H415" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="str">
+        <v>2026-05-08</v>
+      </c>
+      <c r="B416" t="str">
+        <v>13:00</v>
+      </c>
+      <c r="C416" t="str">
+        <v>agent_state/changelog_queue.json</v>
+      </c>
+      <c r="D416" t="str">
+        <v>ספרינט 31 — Reviewer אישר: build ✅ lint ✅ RTL ✅ i18n EN+HE ✅ ניקוי listener ✅ אין רגרסיות</v>
+      </c>
+      <c r="E416" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F416" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G416" t="str">
+        <v>Reviewer</v>
+      </c>
+      <c r="H416" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="str">
+        <v>2026-05-08</v>
+      </c>
+      <c r="B417" t="str">
+        <v>21:00</v>
+      </c>
+      <c r="C417" t="str">
+        <v>src/screens/LandingScreen.tsx</v>
+      </c>
+      <c r="D417" t="str">
+        <v>תוקן BUG-mobile: הודעת שגיאה ב-auth מוצגת בתוך wrapper עם min-h קבוע — מונע קפיצת layout; leading-relaxed + break-words לגלישת שורות בטוחה; red-600 לניגוד טוב יותר</v>
+      </c>
+      <c r="E417" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F417" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G417" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H417" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="str">
+        <v>2026-05-08</v>
+      </c>
+      <c r="B418" t="str">
+        <v>21:00</v>
+      </c>
+      <c r="C418" t="str">
+        <v>src/screens/LandingScreen.tsx</v>
+      </c>
+      <c r="D418" t="str">
+        <v>תוקן BUG-mobile: bottom spacer עודכן ל-max(2.5rem, env(safe-area-inset-bottom) + 1rem) — כפתור Cancel אינו נחסם על ידי home indicator ב-iPhone X+</v>
+      </c>
+      <c r="E418" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F418" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G418" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H418" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H410"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H418"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H418"/>
+  <dimension ref="A1:H421"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -11034,9 +11034,87 @@
         <v>done</v>
       </c>
     </row>
+    <row r="419">
+      <c r="A419" t="str">
+        <v>2026-05-09</v>
+      </c>
+      <c r="B419" t="str">
+        <v>00:00</v>
+      </c>
+      <c r="C419" t="str">
+        <v>src/screens/LandingScreen.tsx</v>
+      </c>
+      <c r="D419" t="str">
+        <v>BL-133: spacer תחתון הוגדל מ-max(2.5rem, safe-area+1rem) ל-max(5rem, safe-area+2rem) — מבטיח 80px מינימום כדי לפנות מקום מעל סרגל הניווט של דפדפן Android Chrome ו-Samsung Internet (~56px); אין שינוי ב-iOS</v>
+      </c>
+      <c r="E419" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F419" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G419" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H419" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="str">
+        <v>2026-05-09</v>
+      </c>
+      <c r="B420" t="str">
+        <v>00:00</v>
+      </c>
+      <c r="C420" t="str">
+        <v>BACKLOG.md</v>
+      </c>
+      <c r="D420" t="str">
+        <v>BL-133 נוסף לבאקלוג — Mobile browser bottom-bar overlap on landing screen; סטטוס: Done; ספרינט 31 stabilization</v>
+      </c>
+      <c r="E420" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F420" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G420" t="str">
+        <v>Documentation</v>
+      </c>
+      <c r="H420" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="str">
+        <v>2026-05-09</v>
+      </c>
+      <c r="B421" t="str">
+        <v>00:00</v>
+      </c>
+      <c r="C421" t="str">
+        <v>BACKLOG.csv</v>
+      </c>
+      <c r="D421" t="str">
+        <v>BL-133 נוסף ל-BACKLOG.csv</v>
+      </c>
+      <c r="E421" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F421" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G421" t="str">
+        <v>Documentation</v>
+      </c>
+      <c r="H421" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H418"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H421"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H421"/>
+  <dimension ref="A1:H424"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -11112,9 +11112,87 @@
         <v>done</v>
       </c>
     </row>
+    <row r="422">
+      <c r="A422" t="str">
+        <v>2026-05-09</v>
+      </c>
+      <c r="B422" t="str">
+        <v>01:00</v>
+      </c>
+      <c r="C422" t="str">
+        <v>src/screens/OnboardingScreen.tsx</v>
+      </c>
+      <c r="D422" t="str">
+        <v>BL-134: paddingBottom של bottom section הוגדל מ-p-6 (24px) ל-max(5rem, safe-area+2rem) — כפתור CTA ראשי אינו נחסם על ידי סרגל דפדפן Android Chrome / Samsung Internet</v>
+      </c>
+      <c r="E422" t="str">
+        <v>bugfix</v>
+      </c>
+      <c r="F422" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G422" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="H422" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="str">
+        <v>2026-05-09</v>
+      </c>
+      <c r="B423" t="str">
+        <v>01:00</v>
+      </c>
+      <c r="C423" t="str">
+        <v>BACKLOG.md</v>
+      </c>
+      <c r="D423" t="str">
+        <v>BL-134 נוסף לבאקלוג — Onboarding screen CTA hidden behind Android browser chrome; סטטוס: Done</v>
+      </c>
+      <c r="E423" t="str">
+        <v>feature</v>
+      </c>
+      <c r="F423" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G423" t="str">
+        <v>Documentation</v>
+      </c>
+      <c r="H423" t="str">
+        <v>done</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="str">
+        <v>2026-05-09</v>
+      </c>
+      <c r="B424" t="str">
+        <v>01:00</v>
+      </c>
+      <c r="C424" t="str">
+        <v>BACKLOG.csv</v>
+      </c>
+      <c r="D424" t="str">
+        <v>BL-134 נוסף ל-BACKLOG.csv</v>
+      </c>
+      <c r="E424" t="str">
+        <v>improvement</v>
+      </c>
+      <c r="F424" t="str">
+        <v>code_change</v>
+      </c>
+      <c r="G424" t="str">
+        <v>Documentation</v>
+      </c>
+      <c r="H424" t="str">
+        <v>done</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H421"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H424"/>
   </ignoredErrors>
 </worksheet>
 </file>